--- a/Luban/Config/Datas/#BattleMomentEffectConfig.xlsx
+++ b/Luban/Config/Datas/#BattleMomentEffectConfig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC85E5D2-1F78-429B-AC98-B387D88BF335}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6782893-EBC7-4065-BD31-06261BA3DD28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="3510" windowWidth="28800" windowHeight="15345" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="129">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -71,15 +71,470 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>改变属性</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SetDontCounter</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>不可被破招</t>
+    <t>参数表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(list#sep=,),float</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ParamList</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SetDontBeCounter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AddIngoreBeCountList</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20101</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20102</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20103</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20201</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10101</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>添加不会被破招的键(目标，键ID)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20301</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>临时增加招式的伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AddTempSkillDamageRate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,0.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20401</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SetAccumulateDamage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>伤害延后计算</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AddBuff</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,2,1,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>40101</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ChangeActionWheel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>谁添加几息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>50101</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ForceSetSkill</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>谁强制设置技能，设置技能的逻辑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>60101</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ForceChangeTarget</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>强制改变目标</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>31101</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>32101</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RemoveBuff</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>谁给谁添加,添加buffID,buff参数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,1,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>谁被移除buff,移除buffID,移除层数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11101</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AddRandomKey</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>随机获得键</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>40102</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SetActionWheelToNow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>谁直接变到当前息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11102</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GetSkillSameKey</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10102</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HealHpByDirectDamage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>根据直接伤害回复一定的比例,谁回血，回多少</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,0.3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>70101</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>设置技能期间被打了</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SetBeDamageInSkillAction</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能期间被打</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>前两息内被攻击</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是否是直接伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>80101</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AddActionTimes</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>谁获得几次行动机会</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20104</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SetDontBeCounterByPowerKilling</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>谁，设置不可破招状态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>谁，设置不可破招状态(1为true,0为false)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20105</t>
+  </si>
+  <si>
+    <t>20106</t>
+  </si>
+  <si>
+    <t>20107</t>
+  </si>
+  <si>
+    <t>20108</t>
+  </si>
+  <si>
+    <t>20109</t>
+  </si>
+  <si>
+    <t>SetDontBeCounterByArtKilling</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>谁，设置不可被武杀破招状态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>谁，设置不可被术杀破招状态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11103</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RandomAllKey</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>谁随机转化所有的键</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>键至少有几个</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11104</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RemoveAllKey</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>谁失去所有的键</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断对手的技能是否是杀式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>第一个参数(1自己，2敌人，3施法者),属性ID,值,来源</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,20001,3,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20302</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AddTempSkillDamageRateByKeyCount</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>根据当前的Key的数量增加伤害 （谁，key偏移量，值）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,-3,0.05</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ChangeSkillGangQiCostByUnitRes</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ChangeSkillXuanQiCostByUnitRes</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20402</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,0.3,0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>招式的刚炁消耗转为当前40%，至多40（谁，转为多少百分比，至多多少（0没有上限））</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>招式的玄炁消耗转为当前40%，至多40（谁，转为多少百分比，至多多少（0没有上限））</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20501</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>谁获得(双方招式一样的键)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11105</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ChangeSomeKey</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>谁转化几个键</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11106</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AddRandonKeyToDefineCount</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得随机键到指定数量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>33101</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GetTargetAllSameBuff</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>谁获取谁的所有buff状态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断玄气和刚气的多少</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AverageGangQiAndXuanQi</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10201</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>谁刚炁与玄炁取平均值更变,来源</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>90101</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamageToTarget</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>谁打，谁被打，什么类型，伤害值，伤害类型，伤害来源</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,2,1,1.5,2,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11107</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ChangeKeyMax</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>谁改变键最大值</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -87,7 +542,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -102,6 +557,19 @@
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -126,8 +594,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -444,77 +918,581 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4CF470-E9E0-44FF-BA6C-71B5C42FB7B2}">
-  <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:H52"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="28.25" customWidth="1"/>
-    <col min="4" max="4" width="26.75" customWidth="1"/>
-    <col min="5" max="5" width="32" customWidth="1"/>
-    <col min="6" max="6" width="41.25" customWidth="1"/>
+    <col min="1" max="1" width="38.25" style="1" customWidth="1"/>
+    <col min="2" max="2" width="33.5" style="1" customWidth="1"/>
+    <col min="3" max="3" width="40.875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="32" style="1" customWidth="1"/>
+    <col min="5" max="5" width="61.875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="9" style="1"/>
+    <col min="7" max="7" width="19.375" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4" t="s">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" t="s">
-        <v>13</v>
+      <c r="D4" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B5" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B6" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="D8" s="2"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B9" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B10" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B11" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B12" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B13" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B14" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B15" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H16" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B17" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B18" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B19" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B20" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B21" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B22" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B23" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B24" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B25" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B27" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="29" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B29" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="30" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B30" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="31" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B31" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="32" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B32" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="35" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B35" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="37" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B37" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="38" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B38" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="39" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B39" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="41" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B41" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="42" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B42" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="44" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B44" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="46" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B46" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="48" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B48" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="50" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B50" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="52" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B52" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>124</v>
       </c>
     </row>
   </sheetData>

--- a/Luban/Config/Datas/#BattleMomentEffectConfig.xlsx
+++ b/Luban/Config/Datas/#BattleMomentEffectConfig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6782893-EBC7-4065-BD31-06261BA3DD28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E00030CC-F6E5-4BB6-A3E0-C6435B888975}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
+    <workbookView xWindow="4995" yWindow="4455" windowWidth="28800" windowHeight="15345" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -598,11 +598,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">

--- a/Luban/Config/Datas/#BattleMomentEffectConfig.xlsx
+++ b/Luban/Config/Datas/#BattleMomentEffectConfig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E00030CC-F6E5-4BB6-A3E0-C6435B888975}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AE1978A-F33B-4126-98EB-FE0132A9912A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4995" yWindow="4455" windowWidth="28800" windowHeight="15345" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
+    <workbookView xWindow="2490" yWindow="3135" windowWidth="28800" windowHeight="15345" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="191">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -91,34 +91,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>20101</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>20102</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>20103</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>20201</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10101</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>添加不会被破招的键(目标，键ID)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>20301</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>临时增加招式的伤害</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -131,10 +107,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>20401</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>SetAccumulateDamage</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -155,14 +127,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1,2,1,1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>40101</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>ChangeActionWheel</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -171,10 +135,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>50101</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>ForceSetSkill</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -183,10 +143,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>60101</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>ForceChangeTarget</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -195,22 +151,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>31101</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>32101</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>RemoveBuff</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>谁给谁添加,添加buffID,buff参数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1,1,1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -219,10 +163,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>11101</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>AddRandomKey</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -235,10 +175,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>40102</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>SetActionWheelToNow</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -247,18 +183,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>11102</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>GetSkillSameKey</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>10102</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>HealHpByDirectDamage</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -271,10 +199,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>70101</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>设置技能期间被打了</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -295,10 +219,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>80101</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>AddActionTimes</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -307,22 +227,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>20104</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>SetDontBeCounterByPowerKilling</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>谁，设置不可破招状态</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>谁，设置不可破招状态(1为true,0为false)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>2,1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -331,21 +239,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>20105</t>
-  </si>
-  <si>
-    <t>20106</t>
-  </si>
-  <si>
-    <t>20107</t>
-  </si>
-  <si>
-    <t>20108</t>
-  </si>
-  <si>
-    <t>20109</t>
-  </si>
-  <si>
     <t>SetDontBeCounterByArtKilling</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -358,10 +251,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>11103</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>RandomAllKey</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -374,10 +263,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>11104</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>RemoveAllKey</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -394,14 +279,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1,20001,3,1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>20302</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>AddTempSkillDamageRateByKeyCount</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -422,10 +299,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>20402</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1,0.3,0</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -438,18 +311,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>20501</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>谁获得(双方招式一样的键)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>11105</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1,2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -462,10 +327,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>11106</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>AddRandonKeyToDefineCount</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -478,10 +339,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>33101</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>GetTargetAllSameBuff</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -498,10 +355,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>10201</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1,0</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -510,10 +363,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>90101</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>DamageToTarget</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -526,15 +375,393 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>11107</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>ChangeKeyMax</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>谁改变键最大值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#备注</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>100001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>200001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>300001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>400001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>500001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>600001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>700001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>800001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>900001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1000001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1100001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1100003</t>
+  </si>
+  <si>
+    <t>1100004</t>
+  </si>
+  <si>
+    <t>1100005</t>
+  </si>
+  <si>
+    <t>1100006</t>
+  </si>
+  <si>
+    <t>1400001</t>
+  </si>
+  <si>
+    <t>1500001</t>
+  </si>
+  <si>
+    <t>1600001</t>
+  </si>
+  <si>
+    <t>1700001</t>
+  </si>
+  <si>
+    <t>1800001</t>
+  </si>
+  <si>
+    <t>1900001</t>
+  </si>
+  <si>
+    <t>2000001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2100001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2200001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2300001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2400001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2500001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2600001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2700001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2800001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2900001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3000001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3100001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3200001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3300001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3400001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3500001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,1,1,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>谁给谁添加,添加buffID,层数,buff参数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,1,2,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2600002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>100002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>100003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>100004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,20114,1,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,20114,-1,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,20104,1,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,20104,-1,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SetBeCounter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>设置(谁)为被破招，配在受到行动后</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1100002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3,0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>设置自己不可被破招</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>还原自己可被破招</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>设置敌人不可被破招</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>还原敌人可被破招</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>设置施法者不可被破招</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>还原施法者可被破招</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3600001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>因招式获得的气减少,(谁,减少多少)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3700001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ChangeRecoverGangQiBySkillReduce</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ChangeRecoverXuanQiBySkillReduce</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3600002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,-100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3700002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>400002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>400003</t>
+  </si>
+  <si>
+    <t>400004</t>
+  </si>
+  <si>
+    <t>400012</t>
+  </si>
+  <si>
+    <t>1,4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3,2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3,4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>400011</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>400013</t>
+  </si>
+  <si>
+    <t>400014</t>
+  </si>
+  <si>
+    <t>400021</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>400022</t>
+  </si>
+  <si>
+    <t>400023</t>
+  </si>
+  <si>
+    <t>400024</t>
+  </si>
+  <si>
+    <t>我获得1个键</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我获得2个键</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我获得3个键</t>
+  </si>
+  <si>
+    <t>我获得4个键</t>
+  </si>
+  <si>
+    <t>对方获得1个键</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对方获得2个键</t>
+  </si>
+  <si>
+    <t>对方获得3个键</t>
+  </si>
+  <si>
+    <t>对方获得4个键</t>
+  </si>
+  <si>
+    <t>施法者获得1个键</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>施法者获得2个键</t>
+  </si>
+  <si>
+    <t>施法者获得3个键</t>
+  </si>
+  <si>
+    <t>施法者获得4个键</t>
+  </si>
+  <si>
+    <t>9999991</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9999992</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,999999,1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -918,20 +1145,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4CF470-E9E0-44FF-BA6C-71B5C42FB7B2}">
-  <dimension ref="A1:H52"/>
+  <dimension ref="A1:I98"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="38.25" style="1" customWidth="1"/>
-    <col min="2" max="2" width="33.5" style="1" customWidth="1"/>
-    <col min="3" max="3" width="40.875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="32" style="1" customWidth="1"/>
-    <col min="5" max="5" width="61.875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="9" style="1"/>
-    <col min="7" max="7" width="19.375" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="1"/>
+    <col min="2" max="3" width="33.5" style="1" customWidth="1"/>
+    <col min="4" max="4" width="40.875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="32" style="1" customWidth="1"/>
+    <col min="6" max="6" width="61.875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="9" style="1"/>
+    <col min="8" max="8" width="19.375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="25.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -939,560 +1167,963 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B4" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B5" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B6" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B7" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="E9" s="2"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B10" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="E11" s="2"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B12" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E13" s="2"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B14" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B15" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B16" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B17" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B18" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B19" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B20" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="21" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B21" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="22" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B22" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="23" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B23" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="24" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B24" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="25" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B25" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="27" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B27" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="29" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B29" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="31" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B31" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="33" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B33" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="35" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B35" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="37" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B37" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="38" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="I38" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="39" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B39" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="40" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B40" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="41" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B41" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="42" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B42" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C42" s="2"/>
+      <c r="D42" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="43" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B43" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C43" s="2"/>
+      <c r="D43" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="44" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B44" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="45" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="C45" s="2"/>
+      <c r="D45" s="2"/>
+      <c r="E45" s="2"/>
+    </row>
+    <row r="46" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B46" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C46" s="2"/>
+      <c r="D46" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="47" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="C47" s="2"/>
+      <c r="D47" s="2"/>
+      <c r="F47" s="2"/>
+    </row>
+    <row r="48" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B48" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="49" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="D49" s="2"/>
+      <c r="E49" s="2"/>
+      <c r="F49" s="2"/>
+    </row>
+    <row r="50" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B50" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C50" s="2"/>
+      <c r="D50" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="51" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="C51" s="2"/>
+      <c r="D51" s="2"/>
+      <c r="E51" s="2"/>
+      <c r="F51" s="2"/>
+    </row>
+    <row r="52" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B52" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C52" s="2"/>
+      <c r="D52" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="53" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="C53" s="2"/>
+      <c r="D53" s="2"/>
+      <c r="F53" s="2"/>
+    </row>
+    <row r="54" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B54" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C54" s="2"/>
+      <c r="D54" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="55" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="C55" s="2"/>
+      <c r="D55" s="2"/>
+      <c r="E55" s="2"/>
+      <c r="F55" s="2"/>
+    </row>
+    <row r="56" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B56" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="58" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B58" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="60" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B60" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="62" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B62" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="64" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B64" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="66" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B66" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="68" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B68" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="D68" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B5" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B6" s="1" t="s">
+      <c r="E68" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="70" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B70" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="71" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B71" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="73" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B73" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="75" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B75" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="D6" s="1" t="s">
+      <c r="D75" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="77" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B77" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="D77" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="79" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B79" s="1" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="D8" s="2"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B9" s="1" t="s">
+      <c r="D79" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="81" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B81" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="83" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B83" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="85" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B85" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="87" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B87" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D87" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="E87" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F87" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B10" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B11" s="1" t="s">
+    </row>
+    <row r="89" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B89" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D89" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="E89" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="F89" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D11" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B12" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B13" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B14" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B15" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="H16" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B17" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D17" s="1" t="s">
+    </row>
+    <row r="91" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B91" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="92" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B92" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="94" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B94" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="95" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B95" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="97" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B97" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="98" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B98" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="D98" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E17" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B18" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B19" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B20" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B21" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B22" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B23" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B24" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B25" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B27" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B29" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B30" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B31" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B32" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B35" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B37" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B38" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B39" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B41" s="1" t="s">
+      <c r="E98" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F98" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B42" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B44" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="46" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B46" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="48" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B48" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="50" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B50" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E50" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="52" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B52" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>124</v>
       </c>
     </row>
   </sheetData>

--- a/Luban/Config/Datas/#BattleMomentEffectConfig.xlsx
+++ b/Luban/Config/Datas/#BattleMomentEffectConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E78EE05-97A4-4BC8-86AB-3C3D02A94B0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58A2A468-0C4B-4758-BC25-68DCA13DB6EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1849" uniqueCount="1374">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1850" uniqueCount="1377">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -172,10 +172,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>根据直接伤害回复一定的比例,谁回血，回多少</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1,0.3</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2451,10 +2447,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1,3,2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>自己清除自身3个异常状态，若清除数量不超过3个则每少2个给予2层武增2层力增2层巧增</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -5391,6 +5383,26 @@
   </si>
   <si>
     <t>自己给目标添加昏沉20351,4层</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,3,200004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,3,200005</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自己根据直接伤害回复一定的比例</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>回多少</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -5835,7 +5847,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>5</v>
@@ -5883,1060 +5895,1060 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B8" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B9" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="E10" s="2"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B11" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B12" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E12" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>318</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B13" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B15" s="1" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E15" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>559</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>560</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
+        <v>619</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>620</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>621</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E16" s="2" t="s">
+        <v>621</v>
+      </c>
+      <c r="F16" s="1" t="s">
         <v>622</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>623</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B17" s="1" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B18" s="1" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
+        <v>736</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>738</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>740</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B20" s="1" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B21" s="1" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B22" s="1" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B23" s="1" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B24" s="1" t="s">
-        <v>1144</v>
+        <v>1142</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>1145</v>
+        <v>1143</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>1147</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B25" s="1" t="s">
-        <v>1223</v>
+        <v>1221</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B26" s="1" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>1167</v>
+        <v>1165</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>1168</v>
+        <v>1166</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>1169</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B27" s="1" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>1220</v>
+        <v>1218</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>1221</v>
+        <v>1219</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>1222</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B28" s="1" t="s">
-        <v>1226</v>
+        <v>1224</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E28" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="F28" s="1" t="s">
         <v>586</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>587</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B29" s="1" t="s">
-        <v>1354</v>
+        <v>1352</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>1355</v>
+        <v>1353</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>1350</v>
+        <v>1348</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>1356</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B30" s="1" t="s">
-        <v>1358</v>
+        <v>1356</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>1359</v>
+        <v>1357</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>1360</v>
+        <v>1358</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>1361</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" s="4" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="E31" s="2"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B32" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B33" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B34" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E34" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="F34" s="1" t="s">
         <v>234</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B35" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B36" s="1" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E38" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="F38" s="1" t="s">
         <v>430</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>431</v>
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B39" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="C39" s="1" t="s">
         <v>608</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>609</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E39" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="F39" s="1" t="s">
         <v>610</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>611</v>
       </c>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B40" s="1" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B41" s="1" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E41" s="2" t="s">
+        <v>997</v>
+      </c>
+      <c r="F41" s="1" t="s">
         <v>999</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>1001</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B42" s="1" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E42" s="2" t="s">
+        <v>998</v>
+      </c>
+      <c r="F42" s="1" t="s">
         <v>1000</v>
-      </c>
-      <c r="F42" s="1" t="s">
-        <v>1002</v>
       </c>
     </row>
     <row r="43" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B43" s="1" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="44" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B44" s="1" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B45" s="1" t="s">
-        <v>1151</v>
+        <v>1149</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>1152</v>
+        <v>1150</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>1153</v>
+        <v>1151</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>1154</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="1" t="s">
-        <v>1171</v>
+        <v>1169</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>1172</v>
+        <v>1170</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>1174</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B47" s="1" t="s">
-        <v>1227</v>
+        <v>1225</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B48" s="1" t="s">
-        <v>1228</v>
+        <v>1226</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>1229</v>
+        <v>1227</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>1231</v>
+        <v>1229</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>1230</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B49" s="1" t="s">
-        <v>1362</v>
+        <v>1360</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>1364</v>
+        <v>1362</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>1365</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A50" s="4" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="E50" s="2"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B51" s="1" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B52" s="1" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A53" s="4" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="E53" s="2"/>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B54" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E54" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="F54" s="1" t="s">
         <v>370</v>
-      </c>
-      <c r="F54" s="1" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B55" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B56" s="1" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B57" s="1" t="s">
+        <v>634</v>
+      </c>
+      <c r="C57" s="1" t="s">
         <v>636</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>638</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A58" s="4" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E58" s="2"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B59" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>1350</v>
+        <v>1348</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>1351</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A60" s="4" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E60" s="2"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B61" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>1351</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B62" s="1" t="s">
-        <v>1353</v>
+        <v>1351</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>1349</v>
+        <v>1347</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>1352</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A63" s="4" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="E63" s="2"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B64" s="1" t="s">
+        <v>666</v>
+      </c>
+      <c r="C64" s="1" t="s">
         <v>668</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>670</v>
       </c>
       <c r="D64" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E64" s="2" t="s">
+        <v>667</v>
+      </c>
+      <c r="F64" s="1" t="s">
         <v>669</v>
-      </c>
-      <c r="F64" s="1" t="s">
-        <v>671</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B65" s="1" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>1303</v>
+        <v>1301</v>
       </c>
       <c r="D65" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>1304</v>
+        <v>1302</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>1305</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A66" s="4" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="E66" s="2"/>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B67" s="1" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A68" s="4" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="E68" s="2"/>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B69" s="1" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="D69" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B70" s="1" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="D70" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A71" s="4" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="E71" s="2"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B72" s="1" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="D72" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E72" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="F72" s="1" t="s">
         <v>693</v>
-      </c>
-      <c r="F72" s="1" t="s">
-        <v>695</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B73" s="1" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.2">
@@ -6947,330 +6959,333 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B75" s="1" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E75" s="2" t="s">
+        <v>904</v>
+      </c>
+      <c r="F75" s="1" t="s">
         <v>906</v>
-      </c>
-      <c r="F75" s="1" t="s">
-        <v>908</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B76" s="1" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E76" s="2" t="s">
+        <v>905</v>
+      </c>
+      <c r="F76" s="1" t="s">
         <v>907</v>
-      </c>
-      <c r="F76" s="1" t="s">
-        <v>909</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A77" s="4" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="E77" s="2"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B78" s="1" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="D78" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="D79" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A80" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="E80" s="2"/>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B81" s="1" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="D81" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E81" s="2" t="s">
+        <v>916</v>
+      </c>
+      <c r="F81" s="1" t="s">
         <v>918</v>
-      </c>
-      <c r="F81" s="1" t="s">
-        <v>920</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B82" s="1" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="D82" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E82" s="2" t="s">
+        <v>917</v>
+      </c>
+      <c r="F82" s="1" t="s">
         <v>919</v>
-      </c>
-      <c r="F82" s="1" t="s">
-        <v>921</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A83" s="4" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="E83" s="2"/>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B84" s="1" t="s">
+        <v>920</v>
+      </c>
+      <c r="C84" s="1" t="s">
         <v>922</v>
-      </c>
-      <c r="C84" s="1" t="s">
-        <v>924</v>
       </c>
       <c r="D84" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E84" s="2" t="s">
+        <v>924</v>
+      </c>
+      <c r="F84" s="1" t="s">
         <v>926</v>
-      </c>
-      <c r="F84" s="1" t="s">
-        <v>928</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B85" s="1" t="s">
+        <v>921</v>
+      </c>
+      <c r="C85" s="1" t="s">
         <v>923</v>
-      </c>
-      <c r="C85" s="1" t="s">
-        <v>925</v>
       </c>
       <c r="D85" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E85" s="2" t="s">
+        <v>925</v>
+      </c>
+      <c r="F85" s="1" t="s">
         <v>927</v>
-      </c>
-      <c r="F85" s="1" t="s">
-        <v>929</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A86" s="4" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="E86" s="2"/>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B87" s="1" t="s">
+        <v>930</v>
+      </c>
+      <c r="C87" s="1" t="s">
         <v>932</v>
-      </c>
-      <c r="C87" s="1" t="s">
-        <v>934</v>
       </c>
       <c r="D87" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B88" s="1" t="s">
+        <v>931</v>
+      </c>
+      <c r="C88" s="1" t="s">
         <v>933</v>
-      </c>
-      <c r="C88" s="1" t="s">
-        <v>935</v>
       </c>
       <c r="D88" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A89" s="4" t="s">
-        <v>1240</v>
+        <v>1238</v>
       </c>
       <c r="E89" s="2"/>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B90" s="1" t="s">
+        <v>1239</v>
+      </c>
+      <c r="C90" s="1" t="s">
         <v>1241</v>
-      </c>
-      <c r="C90" s="1" t="s">
-        <v>1243</v>
       </c>
       <c r="D90" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E90" s="2" t="s">
+        <v>1243</v>
+      </c>
+      <c r="F90" s="1" t="s">
         <v>1245</v>
-      </c>
-      <c r="F90" s="1" t="s">
-        <v>1247</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B91" s="1" t="s">
+        <v>1240</v>
+      </c>
+      <c r="C91" s="1" t="s">
         <v>1242</v>
-      </c>
-      <c r="C91" s="1" t="s">
-        <v>1244</v>
       </c>
       <c r="D91" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E91" s="2" t="s">
+        <v>1244</v>
+      </c>
+      <c r="F91" s="1" t="s">
         <v>1246</v>
-      </c>
-      <c r="F91" s="1" t="s">
-        <v>1248</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A92" s="4" t="s">
-        <v>1250</v>
+        <v>1248</v>
       </c>
       <c r="E92" s="2"/>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B93" s="1" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="D93" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>1253</v>
+        <v>1251</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A94" s="4" t="s">
-        <v>1255</v>
+        <v>1253</v>
       </c>
       <c r="E94" s="2"/>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B95" s="1" t="s">
-        <v>1256</v>
+        <v>1254</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>1257</v>
+        <v>1255</v>
       </c>
       <c r="D95" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A96" s="3" t="s">
+        <v>1374</v>
+      </c>
       <c r="E96" s="2"/>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B97" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>35</v>
+        <v>1375</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>34</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A98" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E98" s="2"/>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B99" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E99" s="1" t="s">
         <v>30</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>1336</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A100" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E100" s="2"/>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B101" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D101" s="1" t="s">
         <v>29</v>
@@ -7279,32 +7294,32 @@
         <v>22</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I101" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B102" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D102" s="1" t="s">
         <v>29</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I102" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B103" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D103" s="1" t="s">
         <v>29</v>
@@ -7313,326 +7328,326 @@
         <v>30</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B104" s="1" t="s">
-        <v>1357</v>
+        <v>1355</v>
       </c>
       <c r="D104" s="1" t="s">
         <v>29</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B105" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="D105" s="1" t="s">
         <v>29</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B106" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D106" s="1" t="s">
         <v>29</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B107" s="1" t="s">
-        <v>1211</v>
+        <v>1209</v>
       </c>
       <c r="D107" s="1" t="s">
         <v>29</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>1212</v>
+        <v>1210</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B108" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D108" s="1" t="s">
         <v>29</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B109" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D109" s="1" t="s">
         <v>29</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B110" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D110" s="1" t="s">
         <v>29</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B111" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D111" s="1" t="s">
         <v>29</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B112" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D112" s="1" t="s">
         <v>29</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="113" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B113" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D113" s="1" t="s">
         <v>29</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="114" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B114" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D114" s="1" t="s">
         <v>29</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I114" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="115" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B115" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D115" s="1" t="s">
         <v>29</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I115" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="116" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B116" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D116" s="1" t="s">
         <v>29</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="117" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B117" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D117" s="1" t="s">
         <v>29</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="118" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B118" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D118" s="1" t="s">
         <v>29</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="119" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B119" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D119" s="1" t="s">
         <v>29</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="120" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B120" s="1" t="s">
-        <v>1178</v>
+        <v>1176</v>
       </c>
       <c r="D120" s="1" t="s">
         <v>29</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>1184</v>
+        <v>1182</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>1190</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="121" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B121" s="1" t="s">
-        <v>1179</v>
+        <v>1177</v>
       </c>
       <c r="D121" s="1" t="s">
         <v>29</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>1185</v>
+        <v>1183</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>1191</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="122" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B122" s="1" t="s">
-        <v>1180</v>
+        <v>1178</v>
       </c>
       <c r="D122" s="1" t="s">
         <v>29</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>1186</v>
+        <v>1184</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>1192</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="123" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B123" s="1" t="s">
-        <v>1181</v>
+        <v>1179</v>
       </c>
       <c r="D123" s="1" t="s">
         <v>29</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>1187</v>
+        <v>1185</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>1193</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="124" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B124" s="1" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="D124" s="1" t="s">
         <v>29</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>1194</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="125" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B125" s="1" t="s">
-        <v>1183</v>
+        <v>1181</v>
       </c>
       <c r="D125" s="1" t="s">
         <v>29</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>1189</v>
+        <v>1187</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>1195</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="128" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B128" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D128" s="1" t="s">
         <v>33</v>
@@ -7641,461 +7656,461 @@
         <v>20</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I128" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B129" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D129" s="1" t="s">
         <v>33</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="I129" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B130" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D130" s="1" t="s">
         <v>33</v>
       </c>
       <c r="E130" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="F130" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="F130" s="1" t="s">
-        <v>145</v>
-      </c>
       <c r="I130" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A131" s="3" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B132" s="1" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="I132" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B133" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E133" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="I133" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B134" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="I134" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B135" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="I135" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B136" s="1" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B137" s="1" t="s">
-        <v>1235</v>
+        <v>1233</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>1236</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A138" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B139" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E139" s="1" t="s">
         <v>20</v>
       </c>
       <c r="F139" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I139" s="1" t="s">
         <v>50</v>
-      </c>
-      <c r="I139" s="1" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B140" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="D140" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E140" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="F140" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="D140" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E140" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="F140" s="1" t="s">
-        <v>392</v>
-      </c>
       <c r="I140" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B141" s="1" t="s">
+        <v>774</v>
+      </c>
+      <c r="D141" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E141" s="1" t="s">
+        <v>775</v>
+      </c>
+      <c r="F141" s="1" t="s">
         <v>776</v>
-      </c>
-      <c r="D141" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E141" s="1" t="s">
-        <v>777</v>
-      </c>
-      <c r="F141" s="1" t="s">
-        <v>778</v>
       </c>
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A142" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B143" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E143" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B144" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B145" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B146" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B147" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A148" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B149" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B150" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E150" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B151" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B152" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B153" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B154" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B155" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B156" s="1" t="s">
-        <v>1249</v>
+        <v>1247</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B157" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B158" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B159" s="1" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A163" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B164" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D164" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E164" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F164" s="1" t="s">
         <v>67</v>
-      </c>
-      <c r="E164" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F164" s="1" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.2">
       <c r="I165" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B166" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D166" s="1" t="s">
         <v>14</v>
@@ -8104,92 +8119,92 @@
         <v>22</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I166" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B167" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D167" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I167" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B168" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E168" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B169" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E169" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B170" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E170" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B171" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E171" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A172" s="3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" s="2"/>
@@ -8197,178 +8212,178 @@
     </row>
     <row r="173" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B173" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E173" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F173" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B174" s="1" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E174" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F174" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B175" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E175" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E175" s="2" t="s">
-        <v>44</v>
-      </c>
       <c r="F175" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B176" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F176" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B177" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E177" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F177" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B178" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E178" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B179" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E179" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B180" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E180" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B181" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E181" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F181" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B182" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F182" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B183" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E183" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F183" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B184" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E184" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F184" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.2">
@@ -8381,7 +8396,7 @@
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B186" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D186" s="1" t="s">
         <v>15</v>
@@ -8390,26 +8405,26 @@
         <v>22</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B187" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D187" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B188" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D188" s="1" t="s">
         <v>15</v>
@@ -8418,358 +8433,358 @@
         <v>30</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B189" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D189" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B190" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D190" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B191" s="1" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D191" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B192" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D192" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B193" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D193" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F193" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B194" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D194" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F194" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B195" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D195" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F195" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B196" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D196" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F196" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B197" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D197" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F197" s="1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A198" s="3" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B199" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="F199" s="1" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B200" s="1" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="F200" s="1" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B201" s="1" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="F201" s="1" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B202" s="1" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="F202" s="1" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B203" s="1" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="F203" s="1" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B204" s="1" t="s">
+        <v>1032</v>
+      </c>
+      <c r="D204" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E204" s="1" t="s">
+        <v>1033</v>
+      </c>
+      <c r="F204" s="1" t="s">
         <v>1034</v>
-      </c>
-      <c r="D204" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="E204" s="1" t="s">
-        <v>1035</v>
-      </c>
-      <c r="F204" s="1" t="s">
-        <v>1036</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A205" s="3" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B206" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="F206" s="1" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B207" s="1" t="s">
-        <v>1137</v>
+        <v>1135</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E207" s="1" t="s">
+        <v>752</v>
+      </c>
+      <c r="F207" s="1" t="s">
         <v>754</v>
-      </c>
-      <c r="F207" s="1" t="s">
-        <v>756</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B208" s="1" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E208" s="1" t="s">
+        <v>753</v>
+      </c>
+      <c r="F208" s="1" t="s">
         <v>755</v>
-      </c>
-      <c r="F208" s="1" t="s">
-        <v>757</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B209" s="1" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="F209" s="1" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B210" s="1" t="s">
+        <v>836</v>
+      </c>
+      <c r="D210" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E210" s="1" t="s">
+        <v>837</v>
+      </c>
+      <c r="F210" s="1" t="s">
         <v>838</v>
-      </c>
-      <c r="D210" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="E210" s="1" t="s">
-        <v>839</v>
-      </c>
-      <c r="F210" s="1" t="s">
-        <v>840</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B211" s="1" t="s">
+        <v>862</v>
+      </c>
+      <c r="D211" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E211" s="1" t="s">
+        <v>863</v>
+      </c>
+      <c r="F211" s="1" t="s">
         <v>864</v>
-      </c>
-      <c r="D211" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="E211" s="1" t="s">
-        <v>865</v>
-      </c>
-      <c r="F211" s="1" t="s">
-        <v>866</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B212" s="1" t="s">
+        <v>884</v>
+      </c>
+      <c r="D212" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E212" s="1" t="s">
+        <v>885</v>
+      </c>
+      <c r="F212" s="1" t="s">
         <v>886</v>
-      </c>
-      <c r="D212" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="E212" s="1" t="s">
-        <v>887</v>
-      </c>
-      <c r="F212" s="1" t="s">
-        <v>888</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B213" s="1" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
       <c r="F213" s="1" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B214" s="1" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="F214" s="1" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B216" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D216" s="1" t="s">
         <v>18</v>
@@ -8783,2379 +8798,2379 @@
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A217" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B218" s="1" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="D218" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="F218" s="1" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B219" s="1" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="D219" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="F219" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B220" s="1" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D220" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B221" s="1" t="s">
+        <v>1276</v>
+      </c>
+      <c r="D221" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E221" s="1" t="s">
         <v>1278</v>
       </c>
-      <c r="D221" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E221" s="1" t="s">
-        <v>1280</v>
-      </c>
       <c r="F221" s="1" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B222" s="1" t="s">
+        <v>591</v>
+      </c>
+      <c r="D222" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E222" s="1" t="s">
         <v>592</v>
       </c>
-      <c r="D222" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E222" s="1" t="s">
+      <c r="F222" s="1" t="s">
         <v>593</v>
-      </c>
-      <c r="F222" s="1" t="s">
-        <v>594</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B223" s="1" t="s">
+        <v>1288</v>
+      </c>
+      <c r="D223" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E223" s="1" t="s">
+        <v>1289</v>
+      </c>
+      <c r="F223" s="1" t="s">
         <v>1290</v>
-      </c>
-      <c r="D223" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E223" s="1" t="s">
-        <v>1291</v>
-      </c>
-      <c r="F223" s="1" t="s">
-        <v>1292</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B224" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="D224" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="F224" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="225" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B225" s="1" t="s">
+        <v>989</v>
+      </c>
+      <c r="D225" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E225" s="1" t="s">
         <v>991</v>
       </c>
-      <c r="D225" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E225" s="1" t="s">
-        <v>993</v>
-      </c>
       <c r="F225" s="1" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
     </row>
     <row r="226" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B226" s="1" t="s">
+        <v>1097</v>
+      </c>
+      <c r="D226" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E226" s="1" t="s">
+        <v>1098</v>
+      </c>
+      <c r="F226" s="1" t="s">
         <v>1099</v>
-      </c>
-      <c r="D226" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E226" s="1" t="s">
-        <v>1100</v>
-      </c>
-      <c r="F226" s="1" t="s">
-        <v>1101</v>
       </c>
     </row>
     <row r="227" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B227" s="1" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="D227" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E227" s="1" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="F227" s="1" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
     </row>
     <row r="228" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B228" s="1" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="D228" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E228" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="F228" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="229" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B229" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="D229" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E229" s="1" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="F229" s="1" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="230" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B230" s="1" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="D230" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F230" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="231" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B231" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="D231" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E231" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="F231" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="232" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B232" s="1" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="D232" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="F232" s="1" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="233" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B233" s="1" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="D233" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="F233" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="234" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B234" s="1" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="D234" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F234" s="1" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="235" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B235" s="1" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D235" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E235" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="F235" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="236" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B236" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D236" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E236" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="F236" s="1" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="237" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B237" s="1" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="D237" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E237" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="F237" s="1" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="238" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B238" s="1" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D238" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E238" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="F238" s="1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="239" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B239" s="1" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="D239" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E239" s="1" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="F239" s="1" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="240" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B240" s="1" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D240" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E240" s="1" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="F240" s="1" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="241" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B241" s="1" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="D241" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E241" s="1" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="F241" s="1" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="242" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B242" s="1" t="s">
+        <v>1173</v>
+      </c>
+      <c r="D242" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E242" s="1" t="s">
+        <v>1174</v>
+      </c>
+      <c r="F242" s="1" t="s">
         <v>1175</v>
-      </c>
-      <c r="D242" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E242" s="1" t="s">
-        <v>1176</v>
-      </c>
-      <c r="F242" s="1" t="s">
-        <v>1177</v>
       </c>
     </row>
     <row r="243" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B243" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="D243" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E243" s="1" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="F243" s="1" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="244" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B244" s="1" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="D244" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E244" s="1" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="F244" s="1" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="245" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B245" s="1" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="D245" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E245" s="1" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="F245" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="246" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B246" s="1" t="s">
+        <v>674</v>
+      </c>
+      <c r="D246" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E246" s="1" t="s">
+        <v>675</v>
+      </c>
+      <c r="F246" s="1" t="s">
         <v>676</v>
-      </c>
-      <c r="D246" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E246" s="1" t="s">
-        <v>677</v>
-      </c>
-      <c r="F246" s="1" t="s">
-        <v>678</v>
       </c>
     </row>
     <row r="247" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B247" s="1" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="D247" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="F247" s="1" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="248" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B248" s="1" t="s">
+        <v>1291</v>
+      </c>
+      <c r="D248" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E248" s="1" t="s">
+        <v>1292</v>
+      </c>
+      <c r="F248" s="1" t="s">
         <v>1293</v>
-      </c>
-      <c r="D248" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E248" s="1" t="s">
-        <v>1294</v>
-      </c>
-      <c r="F248" s="1" t="s">
-        <v>1295</v>
       </c>
     </row>
     <row r="249" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B249" s="1" t="s">
+        <v>1273</v>
+      </c>
+      <c r="D249" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E249" s="1" t="s">
+        <v>1274</v>
+      </c>
+      <c r="F249" s="1" t="s">
         <v>1275</v>
-      </c>
-      <c r="D249" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E249" s="1" t="s">
-        <v>1276</v>
-      </c>
-      <c r="F249" s="1" t="s">
-        <v>1277</v>
       </c>
     </row>
     <row r="250" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B250" s="1" t="s">
+        <v>1051</v>
+      </c>
+      <c r="D250" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E250" s="1" t="s">
+        <v>1052</v>
+      </c>
+      <c r="F250" s="1" t="s">
         <v>1053</v>
-      </c>
-      <c r="D250" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E250" s="1" t="s">
-        <v>1054</v>
-      </c>
-      <c r="F250" s="1" t="s">
-        <v>1055</v>
       </c>
     </row>
     <row r="251" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B251" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="D251" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E251" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="F251" s="1" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="252" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B252" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="D252" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E252" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="F252" s="1" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="253" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B253" s="1" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="D253" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E253" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="F253" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="254" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B254" s="1" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="D254" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E254" s="1" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="F254" s="1" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
     </row>
     <row r="255" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B255" s="1" t="s">
+        <v>977</v>
+      </c>
+      <c r="D255" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E255" s="1" t="s">
+        <v>978</v>
+      </c>
+      <c r="F255" s="1" t="s">
         <v>979</v>
-      </c>
-      <c r="D255" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E255" s="1" t="s">
-        <v>980</v>
-      </c>
-      <c r="F255" s="1" t="s">
-        <v>981</v>
       </c>
     </row>
     <row r="256" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B256" s="1" t="s">
+        <v>1279</v>
+      </c>
+      <c r="D256" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E256" s="1" t="s">
+        <v>1280</v>
+      </c>
+      <c r="F256" s="1" t="s">
         <v>1281</v>
-      </c>
-      <c r="D256" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E256" s="1" t="s">
-        <v>1282</v>
-      </c>
-      <c r="F256" s="1" t="s">
-        <v>1283</v>
       </c>
     </row>
     <row r="257" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B257" s="1" t="s">
+        <v>1136</v>
+      </c>
+      <c r="D257" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E257" s="1" t="s">
+        <v>1137</v>
+      </c>
+      <c r="F257" s="1" t="s">
         <v>1138</v>
-      </c>
-      <c r="D257" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E257" s="1" t="s">
-        <v>1139</v>
-      </c>
-      <c r="F257" s="1" t="s">
-        <v>1140</v>
       </c>
     </row>
     <row r="258" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B258" s="1" t="s">
+        <v>1139</v>
+      </c>
+      <c r="D258" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E258" s="1" t="s">
+        <v>1140</v>
+      </c>
+      <c r="F258" s="1" t="s">
         <v>1141</v>
-      </c>
-      <c r="D258" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E258" s="1" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F258" s="1" t="s">
-        <v>1143</v>
       </c>
     </row>
     <row r="259" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B259" s="1" t="s">
+        <v>1294</v>
+      </c>
+      <c r="D259" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E259" s="1" t="s">
+        <v>1295</v>
+      </c>
+      <c r="F259" s="1" t="s">
         <v>1296</v>
-      </c>
-      <c r="D259" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E259" s="1" t="s">
-        <v>1297</v>
-      </c>
-      <c r="F259" s="1" t="s">
-        <v>1298</v>
       </c>
     </row>
     <row r="260" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B260" s="1" t="s">
+        <v>1022</v>
+      </c>
+      <c r="D260" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E260" s="1" t="s">
+        <v>1023</v>
+      </c>
+      <c r="F260" s="1" t="s">
         <v>1024</v>
-      </c>
-      <c r="D260" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E260" s="1" t="s">
-        <v>1025</v>
-      </c>
-      <c r="F260" s="1" t="s">
-        <v>1026</v>
       </c>
     </row>
     <row r="261" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B261" s="1" t="s">
+        <v>1297</v>
+      </c>
+      <c r="D261" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E261" s="1" t="s">
+        <v>1298</v>
+      </c>
+      <c r="F261" s="1" t="s">
         <v>1299</v>
-      </c>
-      <c r="D261" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E261" s="1" t="s">
-        <v>1300</v>
-      </c>
-      <c r="F261" s="1" t="s">
-        <v>1301</v>
       </c>
     </row>
     <row r="262" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B262" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="D262" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E262" s="1" t="s">
         <v>595</v>
       </c>
-      <c r="D262" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E262" s="1" t="s">
+      <c r="F262" s="1" t="s">
         <v>596</v>
-      </c>
-      <c r="F262" s="1" t="s">
-        <v>597</v>
       </c>
     </row>
     <row r="263" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B263" s="1" t="s">
+        <v>646</v>
+      </c>
+      <c r="D263" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E263" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="F263" s="1" t="s">
         <v>648</v>
-      </c>
-      <c r="D263" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E263" s="1" t="s">
-        <v>649</v>
-      </c>
-      <c r="F263" s="1" t="s">
-        <v>650</v>
       </c>
     </row>
     <row r="264" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B264" s="1" t="s">
+        <v>1083</v>
+      </c>
+      <c r="D264" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E264" s="1" t="s">
+        <v>1084</v>
+      </c>
+      <c r="F264" s="1" t="s">
         <v>1085</v>
-      </c>
-      <c r="D264" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E264" s="1" t="s">
-        <v>1086</v>
-      </c>
-      <c r="F264" s="1" t="s">
-        <v>1087</v>
       </c>
     </row>
     <row r="265" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B265" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="D265" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E265" s="1" t="s">
         <v>630</v>
       </c>
-      <c r="D265" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E265" s="1" t="s">
+      <c r="F265" s="1" t="s">
         <v>631</v>
-      </c>
-      <c r="F265" s="1" t="s">
-        <v>632</v>
       </c>
     </row>
     <row r="266" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B266" s="1" t="s">
+        <v>1335</v>
+      </c>
+      <c r="D266" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E266" s="1" t="s">
+        <v>1336</v>
+      </c>
+      <c r="F266" s="1" t="s">
         <v>1337</v>
-      </c>
-      <c r="D266" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E266" s="1" t="s">
-        <v>1338</v>
-      </c>
-      <c r="F266" s="1" t="s">
-        <v>1339</v>
       </c>
     </row>
     <row r="267" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B267" s="1" t="s">
+        <v>1146</v>
+      </c>
+      <c r="D267" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E267" s="1" t="s">
+        <v>1147</v>
+      </c>
+      <c r="F267" s="1" t="s">
         <v>1148</v>
-      </c>
-      <c r="D267" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E267" s="1" t="s">
-        <v>1149</v>
-      </c>
-      <c r="F267" s="1" t="s">
-        <v>1150</v>
       </c>
     </row>
     <row r="268" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B268" s="1" t="s">
+        <v>649</v>
+      </c>
+      <c r="D268" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E268" s="1" t="s">
+        <v>650</v>
+      </c>
+      <c r="F268" s="1" t="s">
         <v>651</v>
-      </c>
-      <c r="D268" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E268" s="1" t="s">
-        <v>652</v>
-      </c>
-      <c r="F268" s="1" t="s">
-        <v>653</v>
       </c>
     </row>
     <row r="269" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B269" s="1" t="s">
+        <v>1364</v>
+      </c>
+      <c r="D269" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E269" s="1" t="s">
+        <v>1365</v>
+      </c>
+      <c r="F269" s="1" t="s">
         <v>1366</v>
-      </c>
-      <c r="D269" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E269" s="1" t="s">
-        <v>1367</v>
-      </c>
-      <c r="F269" s="1" t="s">
-        <v>1368</v>
       </c>
     </row>
     <row r="270" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B270" s="1" t="s">
+        <v>1019</v>
+      </c>
+      <c r="D270" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E270" s="1" t="s">
+        <v>1020</v>
+      </c>
+      <c r="F270" s="1" t="s">
         <v>1021</v>
-      </c>
-      <c r="D270" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E270" s="1" t="s">
-        <v>1022</v>
-      </c>
-      <c r="F270" s="1" t="s">
-        <v>1023</v>
       </c>
     </row>
     <row r="271" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B271" s="1" t="s">
+        <v>770</v>
+      </c>
+      <c r="D271" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E271" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="F271" s="1" t="s">
         <v>772</v>
-      </c>
-      <c r="D271" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E271" s="1" t="s">
-        <v>773</v>
-      </c>
-      <c r="F271" s="1" t="s">
-        <v>774</v>
       </c>
     </row>
     <row r="272" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B272" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="D272" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E272" s="1" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="F272" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="273" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B273" s="1" t="s">
+        <v>817</v>
+      </c>
+      <c r="D273" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E273" s="1" t="s">
+        <v>818</v>
+      </c>
+      <c r="F273" s="1" t="s">
         <v>819</v>
-      </c>
-      <c r="D273" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E273" s="1" t="s">
-        <v>820</v>
-      </c>
-      <c r="F273" s="1" t="s">
-        <v>821</v>
       </c>
     </row>
     <row r="274" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B274" s="1" t="s">
+        <v>1115</v>
+      </c>
+      <c r="D274" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E274" s="1" t="s">
+        <v>1116</v>
+      </c>
+      <c r="F274" s="1" t="s">
         <v>1117</v>
-      </c>
-      <c r="D274" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E274" s="1" t="s">
-        <v>1118</v>
-      </c>
-      <c r="F274" s="1" t="s">
-        <v>1119</v>
       </c>
     </row>
     <row r="275" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B275" s="1" t="s">
+        <v>1048</v>
+      </c>
+      <c r="D275" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E275" s="1" t="s">
+        <v>1049</v>
+      </c>
+      <c r="F275" s="1" t="s">
         <v>1050</v>
-      </c>
-      <c r="D275" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E275" s="1" t="s">
-        <v>1051</v>
-      </c>
-      <c r="F275" s="1" t="s">
-        <v>1052</v>
       </c>
     </row>
     <row r="276" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B276" s="1" t="s">
+        <v>1206</v>
+      </c>
+      <c r="D276" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E276" s="1" t="s">
+        <v>1207</v>
+      </c>
+      <c r="F276" s="1" t="s">
         <v>1208</v>
-      </c>
-      <c r="D276" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E276" s="1" t="s">
-        <v>1209</v>
-      </c>
-      <c r="F276" s="1" t="s">
-        <v>1210</v>
       </c>
     </row>
     <row r="277" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B277" s="1" t="s">
+        <v>1344</v>
+      </c>
+      <c r="D277" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E277" s="1" t="s">
+        <v>1345</v>
+      </c>
+      <c r="F277" s="1" t="s">
         <v>1346</v>
-      </c>
-      <c r="D277" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E277" s="1" t="s">
-        <v>1347</v>
-      </c>
-      <c r="F277" s="1" t="s">
-        <v>1348</v>
       </c>
     </row>
     <row r="278" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B278" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="D278" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E278" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="F278" s="1" t="s">
         <v>1114</v>
-      </c>
-      <c r="D278" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E278" s="1" t="s">
-        <v>1115</v>
-      </c>
-      <c r="F278" s="1" t="s">
-        <v>1116</v>
       </c>
     </row>
     <row r="279" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B279" s="1" t="s">
+        <v>1330</v>
+      </c>
+      <c r="D279" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E279" s="1" t="s">
+        <v>1331</v>
+      </c>
+      <c r="F279" s="1" t="s">
         <v>1332</v>
-      </c>
-      <c r="D279" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E279" s="1" t="s">
-        <v>1333</v>
-      </c>
-      <c r="F279" s="1" t="s">
-        <v>1334</v>
       </c>
     </row>
     <row r="280" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B280" s="1" t="s">
+        <v>986</v>
+      </c>
+      <c r="D280" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E280" s="1" t="s">
+        <v>987</v>
+      </c>
+      <c r="F280" s="1" t="s">
         <v>988</v>
-      </c>
-      <c r="D280" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E280" s="1" t="s">
-        <v>989</v>
-      </c>
-      <c r="F280" s="1" t="s">
-        <v>990</v>
       </c>
     </row>
     <row r="281" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B281" s="1" t="s">
+        <v>1194</v>
+      </c>
+      <c r="D281" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E281" s="1" t="s">
+        <v>1195</v>
+      </c>
+      <c r="F281" s="1" t="s">
         <v>1196</v>
-      </c>
-      <c r="D281" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E281" s="1" t="s">
-        <v>1197</v>
-      </c>
-      <c r="F281" s="1" t="s">
-        <v>1198</v>
       </c>
     </row>
     <row r="282" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B282" s="1" t="s">
+        <v>1261</v>
+      </c>
+      <c r="D282" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E282" s="1" t="s">
+        <v>1262</v>
+      </c>
+      <c r="F282" s="1" t="s">
         <v>1263</v>
-      </c>
-      <c r="D282" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E282" s="1" t="s">
-        <v>1264</v>
-      </c>
-      <c r="F282" s="1" t="s">
-        <v>1265</v>
       </c>
     </row>
     <row r="283" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B283" s="1" t="s">
+        <v>1016</v>
+      </c>
+      <c r="D283" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E283" s="1" t="s">
+        <v>1017</v>
+      </c>
+      <c r="F283" s="1" t="s">
         <v>1018</v>
-      </c>
-      <c r="D283" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E283" s="1" t="s">
-        <v>1019</v>
-      </c>
-      <c r="F283" s="1" t="s">
-        <v>1020</v>
       </c>
     </row>
     <row r="284" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B284" s="1" t="s">
+        <v>810</v>
+      </c>
+      <c r="D284" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E284" s="1" t="s">
+        <v>811</v>
+      </c>
+      <c r="F284" s="1" t="s">
         <v>812</v>
-      </c>
-      <c r="D284" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E284" s="1" t="s">
-        <v>813</v>
-      </c>
-      <c r="F284" s="1" t="s">
-        <v>814</v>
       </c>
     </row>
     <row r="285" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B285" s="1" t="s">
+        <v>963</v>
+      </c>
+      <c r="D285" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E285" s="1" t="s">
+        <v>964</v>
+      </c>
+      <c r="F285" s="1" t="s">
         <v>965</v>
-      </c>
-      <c r="D285" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E285" s="1" t="s">
-        <v>966</v>
-      </c>
-      <c r="F285" s="1" t="s">
-        <v>967</v>
       </c>
     </row>
     <row r="286" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B286" s="1" t="s">
+        <v>1126</v>
+      </c>
+      <c r="D286" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E286" s="1" t="s">
+        <v>1127</v>
+      </c>
+      <c r="F286" s="1" t="s">
         <v>1128</v>
-      </c>
-      <c r="D286" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E286" s="1" t="s">
-        <v>1129</v>
-      </c>
-      <c r="F286" s="1" t="s">
-        <v>1130</v>
       </c>
     </row>
     <row r="287" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B287" s="1" t="s">
+        <v>1130</v>
+      </c>
+      <c r="D287" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E287" s="1" t="s">
+        <v>1131</v>
+      </c>
+      <c r="F287" s="1" t="s">
         <v>1132</v>
-      </c>
-      <c r="D287" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E287" s="1" t="s">
-        <v>1133</v>
-      </c>
-      <c r="F287" s="1" t="s">
-        <v>1134</v>
       </c>
     </row>
     <row r="288" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B288" s="1" t="s">
+        <v>1091</v>
+      </c>
+      <c r="D288" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E288" s="1" t="s">
+        <v>1092</v>
+      </c>
+      <c r="F288" s="1" t="s">
         <v>1093</v>
-      </c>
-      <c r="D288" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E288" s="1" t="s">
-        <v>1094</v>
-      </c>
-      <c r="F288" s="1" t="s">
-        <v>1095</v>
       </c>
     </row>
     <row r="289" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B289" s="1" t="s">
+        <v>1070</v>
+      </c>
+      <c r="D289" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E289" s="1" t="s">
+        <v>1071</v>
+      </c>
+      <c r="F289" s="1" t="s">
         <v>1072</v>
-      </c>
-      <c r="D289" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E289" s="1" t="s">
-        <v>1073</v>
-      </c>
-      <c r="F289" s="1" t="s">
-        <v>1074</v>
       </c>
     </row>
     <row r="290" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B290" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D290" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E290" s="1" t="s">
+        <v>1039</v>
+      </c>
+      <c r="F290" s="1" t="s">
         <v>1040</v>
-      </c>
-      <c r="D290" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E290" s="1" t="s">
-        <v>1041</v>
-      </c>
-      <c r="F290" s="1" t="s">
-        <v>1042</v>
       </c>
     </row>
     <row r="291" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B291" s="1" t="s">
+        <v>1197</v>
+      </c>
+      <c r="D291" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E291" s="1" t="s">
+        <v>1198</v>
+      </c>
+      <c r="F291" s="1" t="s">
         <v>1199</v>
-      </c>
-      <c r="D291" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E291" s="1" t="s">
-        <v>1200</v>
-      </c>
-      <c r="F291" s="1" t="s">
-        <v>1201</v>
       </c>
     </row>
     <row r="292" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B292" s="1" t="s">
+        <v>1200</v>
+      </c>
+      <c r="D292" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E292" s="1" t="s">
+        <v>1201</v>
+      </c>
+      <c r="F292" s="1" t="s">
         <v>1202</v>
-      </c>
-      <c r="D292" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E292" s="1" t="s">
-        <v>1203</v>
-      </c>
-      <c r="F292" s="1" t="s">
-        <v>1204</v>
       </c>
     </row>
     <row r="293" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B293" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="D293" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E293" s="1" t="s">
+        <v>1095</v>
+      </c>
+      <c r="F293" s="1" t="s">
         <v>1096</v>
-      </c>
-      <c r="D293" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E293" s="1" t="s">
-        <v>1097</v>
-      </c>
-      <c r="F293" s="1" t="s">
-        <v>1098</v>
       </c>
     </row>
     <row r="294" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B294" s="1" t="s">
+        <v>1054</v>
+      </c>
+      <c r="D294" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E294" s="1" t="s">
+        <v>1055</v>
+      </c>
+      <c r="F294" s="1" t="s">
         <v>1056</v>
-      </c>
-      <c r="D294" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E294" s="1" t="s">
-        <v>1057</v>
-      </c>
-      <c r="F294" s="1" t="s">
-        <v>1058</v>
       </c>
     </row>
     <row r="295" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B295" s="1" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="D295" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E295" s="1" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="F295" s="1" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="296" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B296" s="1" t="s">
+        <v>848</v>
+      </c>
+      <c r="D296" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E296" s="1" t="s">
+        <v>849</v>
+      </c>
+      <c r="F296" s="1" t="s">
         <v>850</v>
-      </c>
-      <c r="D296" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E296" s="1" t="s">
-        <v>851</v>
-      </c>
-      <c r="F296" s="1" t="s">
-        <v>852</v>
       </c>
     </row>
     <row r="297" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B297" s="1" t="s">
+        <v>794</v>
+      </c>
+      <c r="D297" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E297" s="1" t="s">
         <v>796</v>
       </c>
-      <c r="D297" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E297" s="1" t="s">
-        <v>798</v>
-      </c>
       <c r="F297" s="1" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
     </row>
     <row r="298" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B298" s="1" t="s">
-        <v>1218</v>
+        <v>1216</v>
       </c>
       <c r="D298" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E298" s="1" t="s">
-        <v>1219</v>
+        <v>1217</v>
       </c>
       <c r="F298" s="1" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="299" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B299" s="1" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="D299" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E299" s="1" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="F299" s="1" t="s">
-        <v>1217</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="300" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B300" s="1" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="D300" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E300" s="1" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="F300" s="1" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="301" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B301" s="1" t="s">
+        <v>795</v>
+      </c>
+      <c r="D301" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E301" s="1" t="s">
         <v>797</v>
       </c>
-      <c r="D301" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E301" s="1" t="s">
-        <v>799</v>
-      </c>
       <c r="F301" s="1" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
     </row>
     <row r="302" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B302" s="1" t="s">
+        <v>1309</v>
+      </c>
+      <c r="D302" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E302" s="1" t="s">
+        <v>1310</v>
+      </c>
+      <c r="F302" s="1" t="s">
         <v>1311</v>
-      </c>
-      <c r="D302" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E302" s="1" t="s">
-        <v>1312</v>
-      </c>
-      <c r="F302" s="1" t="s">
-        <v>1313</v>
       </c>
     </row>
     <row r="303" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B303" s="1" t="s">
+        <v>826</v>
+      </c>
+      <c r="D303" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E303" s="1" t="s">
+        <v>827</v>
+      </c>
+      <c r="F303" s="1" t="s">
         <v>828</v>
-      </c>
-      <c r="D303" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E303" s="1" t="s">
-        <v>829</v>
-      </c>
-      <c r="F303" s="1" t="s">
-        <v>830</v>
       </c>
     </row>
     <row r="304" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B304" s="1" t="s">
+        <v>875</v>
+      </c>
+      <c r="D304" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E304" s="1" t="s">
+        <v>876</v>
+      </c>
+      <c r="F304" s="1" t="s">
         <v>877</v>
-      </c>
-      <c r="D304" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E304" s="1" t="s">
-        <v>878</v>
-      </c>
-      <c r="F304" s="1" t="s">
-        <v>879</v>
       </c>
     </row>
     <row r="305" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B305" s="1" t="s">
+        <v>1067</v>
+      </c>
+      <c r="D305" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E305" s="1" t="s">
+        <v>1068</v>
+      </c>
+      <c r="F305" s="1" t="s">
         <v>1069</v>
-      </c>
-      <c r="D305" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E305" s="1" t="s">
-        <v>1070</v>
-      </c>
-      <c r="F305" s="1" t="s">
-        <v>1071</v>
       </c>
     </row>
     <row r="306" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B306" s="1" t="s">
+        <v>1060</v>
+      </c>
+      <c r="D306" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E306" s="1" t="s">
+        <v>1061</v>
+      </c>
+      <c r="F306" s="1" t="s">
         <v>1062</v>
-      </c>
-      <c r="D306" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E306" s="1" t="s">
-        <v>1063</v>
-      </c>
-      <c r="F306" s="1" t="s">
-        <v>1064</v>
       </c>
     </row>
     <row r="307" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B307" s="1" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D307" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E307" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="F307" s="1" t="s">
         <v>1037</v>
-      </c>
-      <c r="D307" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E307" s="1" t="s">
-        <v>1038</v>
-      </c>
-      <c r="F307" s="1" t="s">
-        <v>1039</v>
       </c>
     </row>
     <row r="308" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B308" s="1" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="D308" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E308" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="F308" s="1" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="309" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B309" s="1" t="s">
+        <v>1029</v>
+      </c>
+      <c r="D309" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E309" s="1" t="s">
+        <v>1122</v>
+      </c>
+      <c r="F309" s="1" t="s">
         <v>1031</v>
-      </c>
-      <c r="D309" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E309" s="1" t="s">
-        <v>1124</v>
-      </c>
-      <c r="F309" s="1" t="s">
-        <v>1033</v>
       </c>
     </row>
     <row r="310" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B310" s="1" t="s">
+        <v>1121</v>
+      </c>
+      <c r="D310" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E310" s="1" t="s">
+        <v>1030</v>
+      </c>
+      <c r="F310" s="1" t="s">
         <v>1123</v>
-      </c>
-      <c r="D310" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E310" s="1" t="s">
-        <v>1032</v>
-      </c>
-      <c r="F310" s="1" t="s">
-        <v>1125</v>
       </c>
     </row>
     <row r="311" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B311" s="1" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="D311" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E311" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="F311" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="312" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B312" s="1" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="D312" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E312" s="1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="F312" s="1" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="313" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B313" s="1" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="D313" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E313" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="F313" s="1" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="314" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B314" s="1" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="D314" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E314" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="F314" s="1" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="315" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B315" s="1" t="s">
+        <v>814</v>
+      </c>
+      <c r="D315" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E315" s="1" t="s">
+        <v>815</v>
+      </c>
+      <c r="F315" s="1" t="s">
         <v>816</v>
-      </c>
-      <c r="D315" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E315" s="1" t="s">
-        <v>817</v>
-      </c>
-      <c r="F315" s="1" t="s">
-        <v>818</v>
       </c>
     </row>
     <row r="316" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B316" s="1" t="s">
+        <v>1264</v>
+      </c>
+      <c r="D316" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E316" s="1" t="s">
+        <v>1265</v>
+      </c>
+      <c r="F316" s="1" t="s">
         <v>1266</v>
-      </c>
-      <c r="D316" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E316" s="1" t="s">
-        <v>1267</v>
-      </c>
-      <c r="F316" s="1" t="s">
-        <v>1268</v>
       </c>
     </row>
     <row r="317" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B317" s="1" t="s">
+        <v>1258</v>
+      </c>
+      <c r="D317" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E317" s="1" t="s">
+        <v>1259</v>
+      </c>
+      <c r="F317" s="1" t="s">
         <v>1260</v>
-      </c>
-      <c r="D317" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E317" s="1" t="s">
-        <v>1261</v>
-      </c>
-      <c r="F317" s="1" t="s">
-        <v>1262</v>
       </c>
     </row>
     <row r="318" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B318" s="1" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="D318" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E318" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="F318" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="319" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B319" s="1" t="s">
-        <v>1307</v>
+        <v>1305</v>
       </c>
       <c r="D319" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E319" s="1" t="s">
+        <v>1306</v>
+      </c>
+      <c r="F319" s="1" t="s">
         <v>1308</v>
-      </c>
-      <c r="F319" s="1" t="s">
-        <v>1310</v>
       </c>
     </row>
     <row r="320" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B320" s="1" t="s">
+        <v>1327</v>
+      </c>
+      <c r="D320" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E320" s="1" t="s">
+        <v>1328</v>
+      </c>
+      <c r="F320" s="1" t="s">
         <v>1329</v>
-      </c>
-      <c r="D320" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E320" s="1" t="s">
-        <v>1330</v>
-      </c>
-      <c r="F320" s="1" t="s">
-        <v>1331</v>
       </c>
     </row>
     <row r="321" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B321" s="1" t="s">
-        <v>1306</v>
+        <v>1304</v>
       </c>
       <c r="D321" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E321" s="1" t="s">
-        <v>1335</v>
+        <v>1333</v>
       </c>
       <c r="F321" s="1" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="322" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B322" s="1" t="s">
+        <v>784</v>
+      </c>
+      <c r="D322" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E322" s="1" t="s">
+        <v>785</v>
+      </c>
+      <c r="F322" s="1" t="s">
         <v>786</v>
-      </c>
-      <c r="D322" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E322" s="1" t="s">
-        <v>787</v>
-      </c>
-      <c r="F322" s="1" t="s">
-        <v>788</v>
       </c>
     </row>
     <row r="323" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B323" s="1" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="D323" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E323" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="F323" s="1" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="324" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B324" s="1" t="s">
+        <v>787</v>
+      </c>
+      <c r="D324" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E324" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="F324" s="1" t="s">
         <v>789</v>
-      </c>
-      <c r="D324" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E324" s="1" t="s">
-        <v>790</v>
-      </c>
-      <c r="F324" s="1" t="s">
-        <v>791</v>
       </c>
     </row>
     <row r="325" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B325" s="1" t="s">
+        <v>800</v>
+      </c>
+      <c r="D325" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E325" s="1" t="s">
         <v>802</v>
       </c>
-      <c r="D325" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E325" s="1" t="s">
-        <v>804</v>
-      </c>
       <c r="F325" s="1" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
     </row>
     <row r="326" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B326" s="1" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="D326" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E326" s="1" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="F326" s="1" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
     </row>
     <row r="327" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B327" s="1" t="s">
+        <v>887</v>
+      </c>
+      <c r="D327" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E327" s="1" t="s">
+        <v>888</v>
+      </c>
+      <c r="F327" s="1" t="s">
         <v>889</v>
-      </c>
-      <c r="D327" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E327" s="1" t="s">
-        <v>890</v>
-      </c>
-      <c r="F327" s="1" t="s">
-        <v>891</v>
       </c>
     </row>
     <row r="328" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B328" s="1" t="s">
+        <v>1118</v>
+      </c>
+      <c r="D328" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E328" s="1" t="s">
+        <v>1119</v>
+      </c>
+      <c r="F328" s="1" t="s">
         <v>1120</v>
-      </c>
-      <c r="D328" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E328" s="1" t="s">
-        <v>1121</v>
-      </c>
-      <c r="F328" s="1" t="s">
-        <v>1122</v>
       </c>
     </row>
     <row r="329" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B329" s="1" t="s">
+        <v>1086</v>
+      </c>
+      <c r="D329" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E329" s="1" t="s">
+        <v>1087</v>
+      </c>
+      <c r="F329" s="1" t="s">
         <v>1088</v>
-      </c>
-      <c r="D329" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E329" s="1" t="s">
-        <v>1089</v>
-      </c>
-      <c r="F329" s="1" t="s">
-        <v>1090</v>
       </c>
     </row>
     <row r="330" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B330" s="1" t="s">
+        <v>1103</v>
+      </c>
+      <c r="D330" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E330" s="1" t="s">
+        <v>1104</v>
+      </c>
+      <c r="F330" s="1" t="s">
         <v>1105</v>
-      </c>
-      <c r="D330" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E330" s="1" t="s">
-        <v>1106</v>
-      </c>
-      <c r="F330" s="1" t="s">
-        <v>1107</v>
       </c>
     </row>
     <row r="331" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B331" s="1" t="s">
+        <v>1057</v>
+      </c>
+      <c r="D331" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E331" s="1" t="s">
+        <v>1058</v>
+      </c>
+      <c r="F331" s="1" t="s">
         <v>1059</v>
-      </c>
-      <c r="D331" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E331" s="1" t="s">
-        <v>1060</v>
-      </c>
-      <c r="F331" s="1" t="s">
-        <v>1061</v>
       </c>
     </row>
     <row r="332" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B332" s="1" t="s">
+        <v>1282</v>
+      </c>
+      <c r="D332" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E332" s="1" t="s">
         <v>1284</v>
       </c>
-      <c r="D332" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E332" s="1" t="s">
-        <v>1286</v>
-      </c>
       <c r="F332" s="1" t="s">
-        <v>1285</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="333" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B333" s="1" t="s">
+        <v>1285</v>
+      </c>
+      <c r="D333" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E333" s="1" t="s">
+        <v>1286</v>
+      </c>
+      <c r="F333" s="1" t="s">
         <v>1287</v>
-      </c>
-      <c r="D333" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E333" s="1" t="s">
-        <v>1288</v>
-      </c>
-      <c r="F333" s="1" t="s">
-        <v>1289</v>
       </c>
     </row>
     <row r="334" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B334" s="1" t="s">
+        <v>777</v>
+      </c>
+      <c r="D334" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E334" s="1" t="s">
+        <v>778</v>
+      </c>
+      <c r="F334" s="1" t="s">
         <v>779</v>
-      </c>
-      <c r="D334" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E334" s="1" t="s">
-        <v>780</v>
-      </c>
-      <c r="F334" s="1" t="s">
-        <v>781</v>
       </c>
     </row>
     <row r="335" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B335" s="1" t="s">
+        <v>854</v>
+      </c>
+      <c r="D335" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E335" s="1" t="s">
+        <v>855</v>
+      </c>
+      <c r="F335" s="1" t="s">
         <v>856</v>
-      </c>
-      <c r="D335" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E335" s="1" t="s">
-        <v>857</v>
-      </c>
-      <c r="F335" s="1" t="s">
-        <v>858</v>
       </c>
     </row>
     <row r="336" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B336" s="1" t="s">
+        <v>1153</v>
+      </c>
+      <c r="D336" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E336" s="1" t="s">
+        <v>1154</v>
+      </c>
+      <c r="F336" s="1" t="s">
         <v>1155</v>
-      </c>
-      <c r="D336" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E336" s="1" t="s">
-        <v>1156</v>
-      </c>
-      <c r="F336" s="1" t="s">
-        <v>1157</v>
       </c>
     </row>
     <row r="337" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B337" s="1" t="s">
+        <v>820</v>
+      </c>
+      <c r="D337" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E337" s="1" t="s">
+        <v>821</v>
+      </c>
+      <c r="F337" s="1" t="s">
         <v>822</v>
-      </c>
-      <c r="D337" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E337" s="1" t="s">
-        <v>823</v>
-      </c>
-      <c r="F337" s="1" t="s">
-        <v>824</v>
       </c>
     </row>
     <row r="338" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B338" s="1" t="s">
+        <v>1100</v>
+      </c>
+      <c r="D338" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E338" s="1" t="s">
+        <v>1101</v>
+      </c>
+      <c r="F338" s="1" t="s">
         <v>1102</v>
-      </c>
-      <c r="D338" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E338" s="1" t="s">
-        <v>1103</v>
-      </c>
-      <c r="F338" s="1" t="s">
-        <v>1104</v>
       </c>
     </row>
     <row r="339" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B339" s="1" t="s">
+        <v>1212</v>
+      </c>
+      <c r="D339" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E339" s="1" t="s">
+        <v>1213</v>
+      </c>
+      <c r="F339" s="1" t="s">
         <v>1214</v>
-      </c>
-      <c r="D339" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E339" s="1" t="s">
-        <v>1215</v>
-      </c>
-      <c r="F339" s="1" t="s">
-        <v>1216</v>
       </c>
     </row>
     <row r="340" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B340" s="1" t="s">
+        <v>992</v>
+      </c>
+      <c r="D340" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E340" s="1" t="s">
+        <v>993</v>
+      </c>
+      <c r="F340" s="1" t="s">
         <v>994</v>
-      </c>
-      <c r="D340" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E340" s="1" t="s">
-        <v>995</v>
-      </c>
-      <c r="F340" s="1" t="s">
-        <v>996</v>
       </c>
     </row>
     <row r="341" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B341" s="1" t="s">
+        <v>894</v>
+      </c>
+      <c r="D341" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E341" s="1" t="s">
+        <v>895</v>
+      </c>
+      <c r="F341" s="1" t="s">
         <v>896</v>
-      </c>
-      <c r="D341" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E341" s="1" t="s">
-        <v>897</v>
-      </c>
-      <c r="F341" s="1" t="s">
-        <v>898</v>
       </c>
     </row>
     <row r="342" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B342" s="1" t="s">
+        <v>1321</v>
+      </c>
+      <c r="D342" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E342" s="1" t="s">
+        <v>1322</v>
+      </c>
+      <c r="F342" s="1" t="s">
         <v>1323</v>
-      </c>
-      <c r="D342" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E342" s="1" t="s">
-        <v>1324</v>
-      </c>
-      <c r="F342" s="1" t="s">
-        <v>1325</v>
       </c>
     </row>
     <row r="343" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B343" s="1" t="s">
+        <v>983</v>
+      </c>
+      <c r="D343" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E343" s="1" t="s">
+        <v>984</v>
+      </c>
+      <c r="F343" s="1" t="s">
         <v>985</v>
-      </c>
-      <c r="D343" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E343" s="1" t="s">
-        <v>986</v>
-      </c>
-      <c r="F343" s="1" t="s">
-        <v>987</v>
       </c>
     </row>
     <row r="344" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B344" s="1" t="s">
+        <v>839</v>
+      </c>
+      <c r="D344" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E344" s="1" t="s">
+        <v>840</v>
+      </c>
+      <c r="F344" s="1" t="s">
         <v>841</v>
-      </c>
-      <c r="D344" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E344" s="1" t="s">
-        <v>842</v>
-      </c>
-      <c r="F344" s="1" t="s">
-        <v>843</v>
       </c>
     </row>
     <row r="345" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B345" s="1" t="s">
+        <v>1077</v>
+      </c>
+      <c r="D345" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E345" s="1" t="s">
+        <v>1078</v>
+      </c>
+      <c r="F345" s="1" t="s">
         <v>1079</v>
-      </c>
-      <c r="D345" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E345" s="1" t="s">
-        <v>1080</v>
-      </c>
-      <c r="F345" s="1" t="s">
-        <v>1081</v>
       </c>
     </row>
     <row r="346" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B346" s="1" t="s">
+        <v>1080</v>
+      </c>
+      <c r="D346" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E346" s="1" t="s">
+        <v>1081</v>
+      </c>
+      <c r="F346" s="1" t="s">
         <v>1082</v>
-      </c>
-      <c r="D346" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E346" s="1" t="s">
-        <v>1083</v>
-      </c>
-      <c r="F346" s="1" t="s">
-        <v>1084</v>
       </c>
     </row>
     <row r="347" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B347" s="1" t="s">
-        <v>1314</v>
+        <v>1312</v>
       </c>
       <c r="D347" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E347" s="1" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="F347" s="1" t="s">
-        <v>1319</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="348" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B348" s="1" t="s">
+        <v>1318</v>
+      </c>
+      <c r="D348" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E348" s="1" t="s">
+        <v>1319</v>
+      </c>
+      <c r="F348" s="1" t="s">
         <v>1320</v>
-      </c>
-      <c r="D348" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E348" s="1" t="s">
-        <v>1321</v>
-      </c>
-      <c r="F348" s="1" t="s">
-        <v>1322</v>
       </c>
     </row>
     <row r="349" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B349" s="1" t="s">
+        <v>1314</v>
+      </c>
+      <c r="D349" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E349" s="1" t="s">
+        <v>1315</v>
+      </c>
+      <c r="F349" s="1" t="s">
         <v>1316</v>
-      </c>
-      <c r="D349" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E349" s="1" t="s">
-        <v>1317</v>
-      </c>
-      <c r="F349" s="1" t="s">
-        <v>1318</v>
       </c>
     </row>
     <row r="350" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B350" s="1" t="s">
+        <v>1369</v>
+      </c>
+      <c r="D350" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E350" s="1" t="s">
+        <v>1370</v>
+      </c>
+      <c r="F350" s="1" t="s">
         <v>1371</v>
-      </c>
-      <c r="D350" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E350" s="1" t="s">
-        <v>1372</v>
-      </c>
-      <c r="F350" s="1" t="s">
-        <v>1373</v>
       </c>
     </row>
     <row r="351" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B351" s="1" t="s">
+        <v>1156</v>
+      </c>
+      <c r="D351" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E351" s="1" t="s">
         <v>1158</v>
       </c>
-      <c r="D351" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E351" s="1" t="s">
-        <v>1160</v>
-      </c>
       <c r="F351" s="1" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="352" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B352" s="1" t="s">
+        <v>1041</v>
+      </c>
+      <c r="D352" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E352" s="1" t="s">
+        <v>1042</v>
+      </c>
+      <c r="F352" s="1" t="s">
         <v>1043</v>
-      </c>
-      <c r="D352" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E352" s="1" t="s">
-        <v>1044</v>
-      </c>
-      <c r="F352" s="1" t="s">
-        <v>1045</v>
       </c>
     </row>
     <row r="353" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B353" s="1" t="s">
+        <v>1159</v>
+      </c>
+      <c r="D353" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E353" s="1" t="s">
+        <v>1160</v>
+      </c>
+      <c r="F353" s="1" t="s">
         <v>1161</v>
-      </c>
-      <c r="D353" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E353" s="1" t="s">
-        <v>1162</v>
-      </c>
-      <c r="F353" s="1" t="s">
-        <v>1163</v>
       </c>
     </row>
     <row r="354" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B354" s="1" t="s">
+        <v>1045</v>
+      </c>
+      <c r="D354" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E354" s="1" t="s">
+        <v>1046</v>
+      </c>
+      <c r="F354" s="1" t="s">
         <v>1047</v>
-      </c>
-      <c r="D354" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E354" s="1" t="s">
-        <v>1048</v>
-      </c>
-      <c r="F354" s="1" t="s">
-        <v>1049</v>
       </c>
     </row>
     <row r="355" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B355" s="1" t="s">
+        <v>1162</v>
+      </c>
+      <c r="D355" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E355" s="1" t="s">
+        <v>1163</v>
+      </c>
+      <c r="F355" s="1" t="s">
         <v>1164</v>
-      </c>
-      <c r="D355" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E355" s="1" t="s">
-        <v>1165</v>
-      </c>
-      <c r="F355" s="1" t="s">
-        <v>1166</v>
       </c>
     </row>
     <row r="356" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B356" s="1" t="s">
+        <v>1106</v>
+      </c>
+      <c r="D356" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E356" s="1" t="s">
+        <v>1107</v>
+      </c>
+      <c r="F356" s="1" t="s">
         <v>1108</v>
-      </c>
-      <c r="D356" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E356" s="1" t="s">
-        <v>1109</v>
-      </c>
-      <c r="F356" s="1" t="s">
-        <v>1110</v>
       </c>
     </row>
     <row r="357" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B357" s="1" t="s">
+        <v>1267</v>
+      </c>
+      <c r="D357" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E357" s="1" t="s">
         <v>1269</v>
       </c>
-      <c r="D357" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E357" s="1" t="s">
+      <c r="F357" s="1" t="s">
         <v>1271</v>
-      </c>
-      <c r="F357" s="1" t="s">
-        <v>1273</v>
       </c>
     </row>
     <row r="358" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B358" s="1" t="s">
+        <v>1268</v>
+      </c>
+      <c r="D358" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E358" s="1" t="s">
         <v>1270</v>
       </c>
-      <c r="D358" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E358" s="1" t="s">
+      <c r="F358" s="1" t="s">
         <v>1272</v>
-      </c>
-      <c r="F358" s="1" t="s">
-        <v>1274</v>
       </c>
     </row>
     <row r="359" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B359" s="1" t="s">
+        <v>614</v>
+      </c>
+      <c r="D359" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E359" s="1" t="s">
         <v>615</v>
       </c>
-      <c r="D359" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E359" s="1" t="s">
+      <c r="F359" s="1" t="s">
         <v>616</v>
-      </c>
-      <c r="F359" s="1" t="s">
-        <v>617</v>
       </c>
     </row>
     <row r="360" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B360" s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D360" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E360" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="F360" s="1" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="361" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B361" s="1" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="D361" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E361" s="1" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F361" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="362" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B362" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="D362" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E362" s="1" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="F362" s="1" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="363" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B363" s="1" t="s">
+        <v>611</v>
+      </c>
+      <c r="D363" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E363" s="1" t="s">
         <v>612</v>
       </c>
-      <c r="D363" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E363" s="1" t="s">
+      <c r="F363" s="1" t="s">
         <v>613</v>
-      </c>
-      <c r="F363" s="1" t="s">
-        <v>614</v>
       </c>
     </row>
     <row r="364" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B364" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="D364" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E364" s="1" t="s">
         <v>700</v>
       </c>
-      <c r="D364" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E364" s="1" t="s">
-        <v>702</v>
-      </c>
       <c r="F364" s="1" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
     </row>
     <row r="365" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B365" s="1" t="s">
+        <v>701</v>
+      </c>
+      <c r="D365" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E365" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="F365" s="1" t="s">
         <v>703</v>
-      </c>
-      <c r="D365" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E365" s="1" t="s">
-        <v>704</v>
-      </c>
-      <c r="F365" s="1" t="s">
-        <v>705</v>
       </c>
     </row>
     <row r="366" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B366" s="1" t="s">
+        <v>714</v>
+      </c>
+      <c r="D366" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E366" s="1" t="s">
+        <v>715</v>
+      </c>
+      <c r="F366" s="1" t="s">
         <v>716</v>
-      </c>
-      <c r="D366" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E366" s="1" t="s">
-        <v>717</v>
-      </c>
-      <c r="F366" s="1" t="s">
-        <v>718</v>
       </c>
     </row>
     <row r="367" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B367" s="1" t="s">
+        <v>725</v>
+      </c>
+      <c r="D367" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E367" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="F367" s="1" t="s">
         <v>727</v>
-      </c>
-      <c r="D367" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E367" s="1" t="s">
-        <v>728</v>
-      </c>
-      <c r="F367" s="1" t="s">
-        <v>729</v>
       </c>
     </row>
     <row r="368" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B368" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="D368" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E368" s="1" t="s">
+        <v>733</v>
+      </c>
+      <c r="F368" s="1" t="s">
         <v>734</v>
-      </c>
-      <c r="D368" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E368" s="1" t="s">
-        <v>735</v>
-      </c>
-      <c r="F368" s="1" t="s">
-        <v>736</v>
       </c>
     </row>
     <row r="369" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B369" s="1" t="s">
+        <v>833</v>
+      </c>
+      <c r="D369" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E369" s="1" t="s">
+        <v>834</v>
+      </c>
+      <c r="F369" s="1" t="s">
         <v>835</v>
-      </c>
-      <c r="D369" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E369" s="1" t="s">
-        <v>836</v>
-      </c>
-      <c r="F369" s="1" t="s">
-        <v>837</v>
       </c>
     </row>
     <row r="370" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B370" s="1" t="s">
+        <v>859</v>
+      </c>
+      <c r="D370" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E370" s="1" t="s">
+        <v>860</v>
+      </c>
+      <c r="F370" s="1" t="s">
         <v>861</v>
-      </c>
-      <c r="D370" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E370" s="1" t="s">
-        <v>862</v>
-      </c>
-      <c r="F370" s="1" t="s">
-        <v>863</v>
       </c>
     </row>
     <row r="371" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B371" s="1" t="s">
+        <v>1235</v>
+      </c>
+      <c r="D371" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E371" s="1" t="s">
+        <v>1236</v>
+      </c>
+      <c r="F371" s="1" t="s">
         <v>1237</v>
-      </c>
-      <c r="D371" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E371" s="1" t="s">
-        <v>1238</v>
-      </c>
-      <c r="F371" s="1" t="s">
-        <v>1239</v>
       </c>
     </row>
     <row r="372" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B372" s="1" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="D372" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E372" s="1" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="F372" s="1" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
     </row>
     <row r="373" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B373" s="1" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="D373" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E373" s="1" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
       <c r="F373" s="1" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
     </row>
     <row r="374" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B374" s="1" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
       <c r="D374" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E374" s="1" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="F374" s="2" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
     </row>
     <row r="375" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B375" s="1" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="D375" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E375" s="1" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="F375" s="2" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
     </row>
     <row r="376" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B376" s="1" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="D376" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E376" s="1" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="F376" s="2" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
     </row>
     <row r="377" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B377" s="1" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="D377" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E377" s="1" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="F377" s="2" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
     </row>
     <row r="378" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A378" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="379" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B379" s="1" t="s">
-        <v>1205</v>
+        <v>1203</v>
       </c>
       <c r="D379" s="1" t="s">
         <v>28</v>
       </c>
       <c r="E379" s="1" t="s">
-        <v>1206</v>
+        <v>1204</v>
       </c>
       <c r="F379" s="1" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="380" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B380" s="1" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="D380" s="1" t="s">
         <v>28</v>
       </c>
       <c r="E380" s="1" t="s">
-        <v>1112</v>
+        <v>1110</v>
       </c>
       <c r="F380" s="1" t="s">
-        <v>1113</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="381" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B381" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D381" s="1" t="s">
         <v>28</v>
       </c>
       <c r="E381" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="F381" s="1" t="s">
         <v>508</v>
-      </c>
-      <c r="F381" s="1" t="s">
-        <v>509</v>
       </c>
     </row>
     <row r="382" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B382" s="1" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D382" s="1" t="s">
         <v>28</v>
       </c>
       <c r="E382" s="1" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="F382" s="1" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="383" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B383" s="1" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="D383" s="1" t="s">
         <v>28</v>
       </c>
       <c r="E383" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="F383" s="1" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="384" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B384" s="1" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="D384" s="1" t="s">
         <v>28</v>
       </c>
       <c r="E384" s="1" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="F384" s="1" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="386" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A386" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="387" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B387" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D387" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E387" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F387" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="388" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B388" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D388" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E388" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F388" s="1" t="s">
         <v>180</v>
-      </c>
-      <c r="D388" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E388" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="F388" s="1" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="389" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A389" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="390" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B390" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D390" s="1" t="s">
         <v>23</v>
@@ -11164,26 +11179,26 @@
         <v>22</v>
       </c>
       <c r="F390" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="391" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B391" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D391" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E391" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F391" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="392" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B392" s="1" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
       <c r="D392" s="1" t="s">
         <v>23</v>
@@ -11192,269 +11207,269 @@
         <v>30</v>
       </c>
       <c r="F392" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="393" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B393" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D393" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E393" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F393" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="394" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B394" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D394" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E394" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F394" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="395" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B395" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D395" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E395" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F395" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="396" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B396" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D396" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E396" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F396" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="397" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B397" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D397" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E397" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F397" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="398" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B398" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D398" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E398" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F398" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="399" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B399" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D399" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E399" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F399" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="400" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B400" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D400" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E400" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F400" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="401" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B401" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D401" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E401" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F401" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="402" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B402" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D402" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E402" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F402" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="403" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B403" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D403" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E403" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F403" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="404" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B404" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D404" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E404" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F404" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="405" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B405" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D405" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E405" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F405" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="406" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B406" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D406" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E406" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F406" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="407" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B407" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D407" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E407" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F407" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="408" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B408" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D408" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E408" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F408" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="409" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B409" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D409" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E409" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F409" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="410" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A410" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="411" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B411" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D411" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E411" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F411" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="413" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B413" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D413" s="1" t="s">
         <v>31</v>
@@ -11468,7 +11483,7 @@
     </row>
     <row r="415" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B415" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D415" s="1" t="s">
         <v>24</v>
@@ -11482,7 +11497,7 @@
     </row>
     <row r="417" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B417" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D417" s="1" t="s">
         <v>26</v>
@@ -11496,899 +11511,899 @@
     </row>
     <row r="419" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B419" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D419" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E419" s="1" t="s">
         <v>20</v>
       </c>
       <c r="F419" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="420" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A420" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="421" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B421" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D421" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E421" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F421" s="1" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="422" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B422" s="1" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D422" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E422" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F422" s="1" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="424" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B424" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D424" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E424" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F424" s="1" t="s">
         <v>64</v>
-      </c>
-      <c r="E424" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="F424" s="1" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="426" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A426" s="3" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="427" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B427" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="D427" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="D427" s="1" t="s">
+      <c r="E427" s="1" t="s">
+        <v>1338</v>
+      </c>
+      <c r="F427" s="1" t="s">
         <v>153</v>
-      </c>
-      <c r="E427" s="1" t="s">
-        <v>1340</v>
-      </c>
-      <c r="F427" s="1" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="428" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B428" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D428" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="E428" s="1" t="s">
+        <v>1339</v>
+      </c>
+      <c r="F428" s="1" t="s">
         <v>156</v>
-      </c>
-      <c r="E428" s="1" t="s">
-        <v>1341</v>
-      </c>
-      <c r="F428" s="1" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="429" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B429" s="1" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="D429" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E429" s="1" t="s">
-        <v>1342</v>
+        <v>1340</v>
       </c>
       <c r="F429" s="1" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
     </row>
     <row r="430" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B430" s="1" t="s">
+        <v>872</v>
+      </c>
+      <c r="D430" s="1" t="s">
+        <v>873</v>
+      </c>
+      <c r="E430" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F430" s="1" t="s">
         <v>874</v>
-      </c>
-      <c r="D430" s="1" t="s">
-        <v>875</v>
-      </c>
-      <c r="E430" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F430" s="1" t="s">
-        <v>876</v>
       </c>
     </row>
     <row r="431" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B431" s="1" t="s">
+        <v>1341</v>
+      </c>
+      <c r="D431" s="1" t="s">
+        <v>873</v>
+      </c>
+      <c r="E431" s="1" t="s">
+        <v>1342</v>
+      </c>
+      <c r="F431" s="1" t="s">
         <v>1343</v>
-      </c>
-      <c r="D431" s="1" t="s">
-        <v>875</v>
-      </c>
-      <c r="E431" s="1" t="s">
-        <v>1344</v>
-      </c>
-      <c r="F431" s="1" t="s">
-        <v>1345</v>
       </c>
     </row>
     <row r="432" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A432" s="3" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="433" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B433" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D433" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E433" s="1" t="s">
         <v>20</v>
       </c>
       <c r="F433" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="434" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B434" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D434" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E434" s="1" t="s">
         <v>20</v>
       </c>
       <c r="F434" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="435" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A435" s="3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="436" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B436" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="D436" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="D436" s="1" t="s">
-        <v>295</v>
-      </c>
       <c r="E436" s="1" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="F436" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="437" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B437" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D437" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E437" s="1" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="F437" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="438" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A438" s="3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="439" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B439" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="D439" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="D439" s="1" t="s">
-        <v>346</v>
-      </c>
       <c r="E439" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="F439" s="1" t="s">
         <v>350</v>
-      </c>
-      <c r="F439" s="1" t="s">
-        <v>351</v>
       </c>
     </row>
     <row r="440" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B440" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D440" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E440" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="F440" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="441" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B441" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D441" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E441" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F441" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="442" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B442" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D442" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E442" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F442" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="443" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B443" s="1" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="D443" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E443" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F443" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="444" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B444" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="D444" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E444" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F444" s="1" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="445" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B445" s="1" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="D445" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E445" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F445" s="1" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="446" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B446" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D446" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E446" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F446" s="1" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="447" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A447" s="3" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="448" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B448" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="D448" s="1" t="s">
         <v>433</v>
-      </c>
-      <c r="D448" s="1" t="s">
-        <v>434</v>
       </c>
       <c r="E448" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F448" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="449" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B449" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="D449" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E449" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F449" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="450" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A450" s="3" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="451" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B451" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="D451" s="1" t="s">
         <v>598</v>
       </c>
-      <c r="D451" s="1" t="s">
+      <c r="E451" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F451" s="1" t="s">
         <v>599</v>
-      </c>
-      <c r="E451" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="F451" s="1" t="s">
-        <v>600</v>
       </c>
     </row>
     <row r="452" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B452" s="1" t="s">
+        <v>662</v>
+      </c>
+      <c r="D452" s="1" t="s">
         <v>664</v>
       </c>
-      <c r="D452" s="1" t="s">
-        <v>666</v>
-      </c>
       <c r="F452" s="1" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
     </row>
     <row r="453" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B453" s="1" t="s">
+        <v>956</v>
+      </c>
+      <c r="D453" s="1" t="s">
+        <v>957</v>
+      </c>
+      <c r="F453" s="1" t="s">
         <v>958</v>
-      </c>
-      <c r="D453" s="1" t="s">
-        <v>959</v>
-      </c>
-      <c r="F453" s="1" t="s">
-        <v>960</v>
       </c>
     </row>
     <row r="454" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A454" s="3" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="455" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B455" s="1" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="D455" s="1" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="E455" s="1" t="s">
-        <v>357</v>
+        <v>1372</v>
       </c>
       <c r="F455" s="6" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="456" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B456" s="1" t="s">
+        <v>632</v>
+      </c>
+      <c r="D456" s="1" t="s">
+        <v>623</v>
+      </c>
+      <c r="E456" s="1" t="s">
+        <v>1373</v>
+      </c>
+      <c r="F456" s="6" t="s">
         <v>633</v>
-      </c>
-      <c r="D456" s="1" t="s">
-        <v>624</v>
-      </c>
-      <c r="E456" s="1" t="s">
-        <v>634</v>
-      </c>
-      <c r="F456" s="6" t="s">
-        <v>635</v>
       </c>
     </row>
     <row r="457" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A457" s="3" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="458" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B458" s="1" t="s">
-        <v>1135</v>
+        <v>1133</v>
       </c>
       <c r="D458" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="E458" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F458" s="1" t="s">
-        <v>1136</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="459" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B459" s="1" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="D459" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="E459" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F459" s="1" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
     </row>
     <row r="460" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B460" s="1" t="s">
+        <v>625</v>
+      </c>
+      <c r="D460" s="1" t="s">
         <v>626</v>
       </c>
-      <c r="D460" s="1" t="s">
+      <c r="E460" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F460" s="1" t="s">
         <v>627</v>
-      </c>
-      <c r="E460" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F460" s="1" t="s">
-        <v>628</v>
       </c>
     </row>
     <row r="461" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B461" s="1" t="s">
-        <v>1369</v>
+        <v>1367</v>
       </c>
       <c r="D461" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="E461" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F461" s="1" t="s">
-        <v>1370</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="462" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B462" s="1" t="s">
-        <v>1326</v>
+        <v>1324</v>
       </c>
       <c r="D462" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="E462" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F462" s="1" t="s">
-        <v>1327</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="463" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A463" s="3" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
     </row>
     <row r="464" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B464" s="1" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="D464" s="1" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="E464" s="1" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="F464" s="6" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
     </row>
     <row r="465" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B465" s="1" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="D465" s="1" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="E465" s="1" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="F465" s="6" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
     </row>
     <row r="466" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A466" s="3" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="F466" s="6"/>
     </row>
     <row r="467" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B467" s="1" t="s">
+        <v>719</v>
+      </c>
+      <c r="D467" s="1" t="s">
+        <v>720</v>
+      </c>
+      <c r="E467" s="1" t="s">
         <v>721</v>
       </c>
-      <c r="D467" s="1" t="s">
+      <c r="F467" s="6" t="s">
         <v>722</v>
-      </c>
-      <c r="E467" s="1" t="s">
-        <v>723</v>
-      </c>
-      <c r="F467" s="6" t="s">
-        <v>724</v>
       </c>
     </row>
     <row r="468" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B468" s="1" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="D468" s="1" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="E468" s="1" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="F468" s="6" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
     </row>
     <row r="469" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A469" s="3" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="F469" s="6"/>
     </row>
     <row r="470" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B470" s="1" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="D470" s="1" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="E470" s="1" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="F470" s="6" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
     </row>
     <row r="471" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B471" s="1" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="D471" s="1" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="E471" s="1" t="s">
+        <v>899</v>
+      </c>
+      <c r="F471" s="6" t="s">
         <v>901</v>
-      </c>
-      <c r="F471" s="6" t="s">
-        <v>903</v>
       </c>
     </row>
     <row r="472" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A472" s="3" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="F472" s="6"/>
     </row>
     <row r="473" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B473" s="1" t="s">
+        <v>758</v>
+      </c>
+      <c r="D473" s="1" t="s">
         <v>760</v>
       </c>
-      <c r="D473" s="1" t="s">
-        <v>762</v>
-      </c>
       <c r="E473" s="1" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="F473" s="6" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
     </row>
     <row r="474" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B474" s="1" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D474" s="1" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="E474" s="1" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="F474" s="6" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
     </row>
     <row r="475" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B475" s="1" t="s">
+        <v>764</v>
+      </c>
+      <c r="D475" s="1" t="s">
+        <v>760</v>
+      </c>
+      <c r="E475" s="1" t="s">
         <v>766</v>
       </c>
-      <c r="D475" s="1" t="s">
-        <v>762</v>
-      </c>
-      <c r="E475" s="1" t="s">
-        <v>768</v>
-      </c>
       <c r="F475" s="6" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
     </row>
     <row r="476" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B476" s="1" t="s">
+        <v>980</v>
+      </c>
+      <c r="D476" s="1" t="s">
+        <v>760</v>
+      </c>
+      <c r="E476" s="1" t="s">
+        <v>981</v>
+      </c>
+      <c r="F476" s="6" t="s">
         <v>982</v>
-      </c>
-      <c r="D476" s="1" t="s">
-        <v>762</v>
-      </c>
-      <c r="E476" s="1" t="s">
-        <v>983</v>
-      </c>
-      <c r="F476" s="6" t="s">
-        <v>984</v>
       </c>
     </row>
     <row r="477" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A477" s="3" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="F477" s="6"/>
     </row>
     <row r="478" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B478" s="1" t="s">
+        <v>761</v>
+      </c>
+      <c r="D478" s="1" t="s">
+        <v>762</v>
+      </c>
+      <c r="E478" s="1" t="s">
         <v>763</v>
       </c>
-      <c r="D478" s="1" t="s">
-        <v>764</v>
-      </c>
-      <c r="E478" s="1" t="s">
-        <v>765</v>
-      </c>
       <c r="F478" s="6" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
     </row>
     <row r="479" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B479" s="1" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="D479" s="1" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="E479" s="1" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="F479" s="6" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="480" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B480" s="1" t="s">
+        <v>1009</v>
+      </c>
+      <c r="D480" s="1" t="s">
+        <v>762</v>
+      </c>
+      <c r="E480" s="1" t="s">
+        <v>766</v>
+      </c>
+      <c r="F480" s="6" t="s">
         <v>1011</v>
-      </c>
-      <c r="D480" s="1" t="s">
-        <v>764</v>
-      </c>
-      <c r="E480" s="1" t="s">
-        <v>768</v>
-      </c>
-      <c r="F480" s="6" t="s">
-        <v>1013</v>
       </c>
     </row>
     <row r="481" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B481" s="1" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="D481" s="1" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="E481" s="1" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="F481" s="6" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="482" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A482" s="3" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="F482" s="6"/>
     </row>
     <row r="483" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B483" s="1" t="s">
-        <v>1126</v>
+        <v>1124</v>
       </c>
       <c r="D483" s="1" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="E483" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F483" s="6" t="s">
-        <v>1127</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="484" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B484" s="1" t="s">
+        <v>806</v>
+      </c>
+      <c r="D484" s="1" t="s">
         <v>808</v>
       </c>
-      <c r="D484" s="1" t="s">
-        <v>810</v>
-      </c>
       <c r="E484" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F484" s="6" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
     </row>
     <row r="485" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B485" s="1" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
       <c r="D485" s="1" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="E485" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F485" s="6" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="486" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B486" s="1" t="s">
-        <v>1233</v>
+        <v>1231</v>
       </c>
       <c r="D486" s="1" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="E486" s="1" t="s">
-        <v>1184</v>
+        <v>1182</v>
       </c>
       <c r="F486" s="6" t="s">
-        <v>1234</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="487" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B487" s="1" t="s">
-        <v>1232</v>
+        <v>1230</v>
       </c>
       <c r="D487" s="1" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="E487" s="1" t="s">
-        <v>1185</v>
+        <v>1183</v>
       </c>
       <c r="F487" s="6" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="488" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A488" s="3" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="F488" s="6"/>
     </row>
     <row r="489" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B489" s="1" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="D489" s="1" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="E489" s="1" t="s">
         <v>20</v>
       </c>
       <c r="F489" s="6" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
     </row>
     <row r="490" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A490" s="3" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="F490" s="6"/>
     </row>
     <row r="491" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B491" s="1" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="D491" s="1" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="E491" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F491" s="6" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
     </row>
     <row r="492" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A492" s="3" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="F492" s="6"/>
     </row>
     <row r="493" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B493" s="1" t="s">
+        <v>966</v>
+      </c>
+      <c r="D493" s="1" t="s">
+        <v>967</v>
+      </c>
+      <c r="E493" s="1" t="s">
+        <v>969</v>
+      </c>
+      <c r="F493" s="6" t="s">
         <v>968</v>
-      </c>
-      <c r="D493" s="1" t="s">
-        <v>969</v>
-      </c>
-      <c r="E493" s="1" t="s">
-        <v>971</v>
-      </c>
-      <c r="F493" s="6" t="s">
-        <v>970</v>
       </c>
     </row>
     <row r="494" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A494" s="3" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="495" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B495" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="D495" s="5" t="s">
         <v>589</v>
-      </c>
-      <c r="D495" s="5" t="s">
-        <v>590</v>
       </c>
       <c r="E495" s="1" t="s">
         <v>20</v>
       </c>
       <c r="F495" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="496" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A496" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="497" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B497" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D497" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F497" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
   </sheetData>

--- a/Luban/Config/Datas/#BattleMomentEffectConfig.xlsx
+++ b/Luban/Config/Datas/#BattleMomentEffectConfig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58A2A468-0C4B-4758-BC25-68DCA13DB6EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{243C2555-B4A8-49E1-A787-1DF06ABD3391}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1850" uniqueCount="1377">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1904" uniqueCount="1425">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -600,10 +600,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>HealHpByDirectDamagePct</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1,20031,15,3</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2411,18 +2407,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>清理异常buff几个</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4400102</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ClearAbnormalBuff</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>自己清理2个异常buff</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2522,10 +2506,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>4400101</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>自己清理1个异常buff</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -3002,10 +2982,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>每有一个键该招式威力增加5的百分比</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>700004</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -3661,78 +3637,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>117000101</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1,1,70001,1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>目标回玄气-20</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>117100101</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1,1,71001,1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>本次交锋不会被破招</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>117100201</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>117100301</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>117100401</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>117100001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1,1,71000,1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1,1,71002,1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1,1,71003,1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1,1,71004,1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>本次交锋不会被被未带有↑类留劲状态的敌手破招</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>本次交锋不会被被未带有↓类留劲状态的敌手破招</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>本次交锋不会被被未带有←类留劲状态的敌手破招</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>本次交锋不会被被未带有→类留劲状态的敌手破招</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>4220001</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -4440,10 +4348,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>4400100</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>自己清理所有异常buff</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -5194,10 +5098,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>4400700</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>全部人清理所有异常buff</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -5366,10 +5266,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>4400202</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>目标清理2个异常buff</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -5394,15 +5290,311 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>自己根据直接伤害回复一定的比例</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>回多少</t>
+    <t>112001103</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,1,20011,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自己给自己添加缓速20011,3层</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5600001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RemoveKey</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>消耗一些键(目标，键组)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>消耗2个→键和1个←键</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,4,4,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>122021101</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,2,20211,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自己给目标添加法式禁20211,1层</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>122020102</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自己给目标添加技式禁20201,2层</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,2,20201,2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>112034102</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,1,20341,2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自己给自己添加毒瘴20341,2层</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>142034102</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,4,20341,2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自己给交锋者添加毒瘴20341,2层</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ChangeHpByAttackDamage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>200002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>201001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ChangeHpByHitDamage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>（攻击方调用）目标根据直接伤害回复一定的比例(目标，是否回复，百分比)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>（受击方调用）目标根据直接伤害回复一定的比例(目标，是否回复，百分比)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,1,0.3,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击方调用，自己回复伤害的30%的生命值，来源招式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>受击方调用，自己回复伤害的30%的生命值，来源招式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,1,1,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击方调用，自己回复伤害的100%的生命值，来源招式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TransferBuff</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>转移buff(调用方，添加方，buff种类，buff数量)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,2,2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,2,2,2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5701222</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5701223</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自己转移给对方2个异常buff</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自己转移给对方3个异常buff</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,2,2,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5701220</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,2,2,0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自己转移给对方全部异常buff</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ClearBuffByType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>清理buff几个</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,2,2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7,2,0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4401200</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4401201</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4401202</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4402202</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4407200</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4402101</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,1,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标清理1个增益buff</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>根据buff层数移除随机键</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5800001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RemoveRandomBuffByBuffLayerCount</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,20081</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标根据伤口层数移除等同数量的键</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>107003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标防-15%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标，防百分比变量，-15%，招式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,20104,0.15,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4402102</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,1,2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标清理2个增益buff</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5901222</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自己施加给对方2个异常buff</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AddHasBuff</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>施加已有buff(调用方，添加方，buff种类，buff数量)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>122013102</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,2,20131,2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自己给目标添加武衰20131,2层</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>200003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,0,0.5,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击方调用，自己扣除伤害的50%的生命值，来源招式</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -5488,7 +5680,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5508,6 +5700,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -5824,7 +6019,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4CF470-E9E0-44FF-BA6C-71B5C42FB7B2}">
-  <dimension ref="A1:I497"/>
+  <dimension ref="A1:I514"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="29.75" style="1" customWidth="1"/>
@@ -5895,13 +6090,13 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E5" s="2"/>
     </row>
@@ -5916,10 +6111,10 @@
         <v>10</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5933,10 +6128,10 @@
         <v>10</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
@@ -5950,10 +6145,10 @@
         <v>10</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
@@ -5967,3216 +6162,3211 @@
         <v>10</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="E10" s="2"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B11" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B12" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E12" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>317</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B13" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B15" s="1" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E15" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>558</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>559</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>619</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>620</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E16" s="2" t="s">
+        <v>620</v>
+      </c>
+      <c r="F16" s="1" t="s">
         <v>621</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>622</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B17" s="1" t="s">
-        <v>657</v>
+        <v>652</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>658</v>
+        <v>653</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>659</v>
+        <v>654</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>660</v>
+        <v>655</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B18" s="1" t="s">
-        <v>746</v>
+        <v>741</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>737</v>
+        <v>732</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E18" s="2" t="s">
+        <v>735</v>
+      </c>
+      <c r="F18" s="1" t="s">
         <v>740</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>745</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
-        <v>736</v>
+        <v>731</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>738</v>
+        <v>733</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>741</v>
+        <v>736</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>744</v>
+        <v>739</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B20" s="1" t="s">
-        <v>842</v>
+        <v>836</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>739</v>
+        <v>734</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>743</v>
+        <v>738</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B21" s="1" t="s">
-        <v>843</v>
+        <v>837</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>844</v>
+        <v>838</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>845</v>
+        <v>839</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>846</v>
+        <v>840</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B22" s="1" t="s">
-        <v>865</v>
+        <v>859</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>866</v>
+        <v>860</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>867</v>
+        <v>861</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>868</v>
+        <v>862</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B23" s="1" t="s">
-        <v>959</v>
+        <v>936</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>960</v>
+        <v>937</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>961</v>
+        <v>938</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>962</v>
+        <v>939</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B24" s="1" t="s">
-        <v>1142</v>
+        <v>1118</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>1143</v>
+        <v>1119</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>1144</v>
+        <v>1120</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>1145</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B25" s="1" t="s">
-        <v>1221</v>
+        <v>1197</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>869</v>
+        <v>863</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>870</v>
+        <v>864</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>871</v>
+        <v>865</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B26" s="1" t="s">
-        <v>1222</v>
+        <v>1198</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>1165</v>
+        <v>1141</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>1166</v>
+        <v>1142</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>1167</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B27" s="1" t="s">
-        <v>1223</v>
+        <v>1199</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>1218</v>
+        <v>1194</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>1219</v>
+        <v>1195</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>1220</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B28" s="1" t="s">
-        <v>1224</v>
+        <v>1200</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E28" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="F28" s="1" t="s">
         <v>585</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>586</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B29" s="1" t="s">
-        <v>1352</v>
+        <v>1327</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>1353</v>
+        <v>1328</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>1348</v>
+        <v>1323</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>1354</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B30" s="1" t="s">
-        <v>1356</v>
+        <v>1331</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>1357</v>
+        <v>1332</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>1358</v>
+        <v>1333</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>1359</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" s="4" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="E31" s="2"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B32" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B33" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B34" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E34" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="F34" s="1" t="s">
         <v>233</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B35" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B36" s="1" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E38" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="F38" s="1" t="s">
         <v>429</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B39" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="C39" s="1" t="s">
         <v>607</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>608</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E39" s="2" t="s">
+        <v>608</v>
+      </c>
+      <c r="F39" s="1" t="s">
         <v>609</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>610</v>
       </c>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B40" s="1" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B41" s="1" t="s">
-        <v>1001</v>
+        <v>978</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>995</v>
+        <v>972</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>997</v>
+        <v>974</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>999</v>
+        <v>976</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B42" s="1" t="s">
-        <v>1002</v>
+        <v>979</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>996</v>
+        <v>973</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>998</v>
+        <v>975</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>1000</v>
+        <v>977</v>
       </c>
     </row>
     <row r="43" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B43" s="1" t="s">
-        <v>1063</v>
+        <v>1040</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>1064</v>
+        <v>1041</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>1065</v>
+        <v>1042</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>1066</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="44" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B44" s="1" t="s">
-        <v>1073</v>
+        <v>1050</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>1074</v>
+        <v>1051</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>1075</v>
+        <v>1052</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>1076</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B45" s="1" t="s">
-        <v>1149</v>
+        <v>1125</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>1150</v>
+        <v>1126</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>1151</v>
+        <v>1127</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>1152</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="1" t="s">
-        <v>1169</v>
+        <v>1145</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>1170</v>
+        <v>1146</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>1171</v>
+        <v>1147</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>1172</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B47" s="1" t="s">
-        <v>1225</v>
+        <v>1201</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>940</v>
+        <v>932</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>897</v>
+        <v>891</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>898</v>
+        <v>892</v>
       </c>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B48" s="1" t="s">
-        <v>1226</v>
+        <v>1202</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>1227</v>
+        <v>1203</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>1229</v>
+        <v>1205</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>1228</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B49" s="1" t="s">
-        <v>1360</v>
+        <v>1335</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>1361</v>
+        <v>1336</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>1362</v>
+        <v>1337</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>1363</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A50" s="4" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="E50" s="2"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B51" s="1" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B52" s="1" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A53" s="4" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="E53" s="2"/>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B54" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E54" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="F54" s="1" t="s">
         <v>369</v>
-      </c>
-      <c r="F54" s="1" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B55" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B56" s="1" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>639</v>
+        <v>635</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B57" s="1" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A58" s="4" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="E58" s="2"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B59" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>1348</v>
+        <v>1323</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>1349</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A60" s="4" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E60" s="2"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B61" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>1349</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B62" s="1" t="s">
-        <v>1351</v>
+        <v>1326</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>1347</v>
+        <v>1322</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>1075</v>
+        <v>1052</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>1350</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A63" s="4" t="s">
-        <v>665</v>
+        <v>660</v>
       </c>
       <c r="E63" s="2"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B64" s="1" t="s">
-        <v>666</v>
+        <v>661</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>668</v>
+        <v>663</v>
       </c>
       <c r="D64" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>667</v>
+        <v>662</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>669</v>
+        <v>664</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B65" s="1" t="s">
-        <v>1300</v>
+        <v>1276</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>1301</v>
+        <v>1277</v>
       </c>
       <c r="D65" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>1302</v>
+        <v>1278</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>1303</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A66" s="4" t="s">
-        <v>670</v>
-      </c>
-      <c r="E66" s="2"/>
+      <c r="B66" s="1" t="s">
+        <v>1408</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>1411</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>1410</v>
+      </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B67" s="1" t="s">
-        <v>671</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>677</v>
-      </c>
-      <c r="D67" s="1" t="s">
+      <c r="A67" s="4" t="s">
+        <v>665</v>
+      </c>
+      <c r="E67" s="2"/>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B68" s="1" t="s">
+        <v>666</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>672</v>
+      </c>
+      <c r="D68" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E67" s="2" t="s">
-        <v>672</v>
-      </c>
-      <c r="F67" s="1" t="s">
-        <v>673</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A68" s="4" t="s">
-        <v>680</v>
-      </c>
-      <c r="E68" s="2"/>
+      <c r="E68" s="2" t="s">
+        <v>667</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>668</v>
+      </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B69" s="1" t="s">
-        <v>681</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>689</v>
-      </c>
-      <c r="D69" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E69" s="2" t="s">
-        <v>682</v>
-      </c>
-      <c r="F69" s="1" t="s">
-        <v>683</v>
-      </c>
+      <c r="A69" s="4" t="s">
+        <v>675</v>
+      </c>
+      <c r="E69" s="2"/>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B70" s="1" t="s">
-        <v>686</v>
+        <v>676</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>690</v>
+        <v>684</v>
       </c>
       <c r="D70" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>684</v>
+        <v>677</v>
       </c>
       <c r="F70" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B71" s="1" t="s">
+        <v>681</v>
+      </c>
+      <c r="C71" s="1" t="s">
         <v>685</v>
       </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A71" s="4" t="s">
-        <v>687</v>
-      </c>
-      <c r="E71" s="2"/>
+      <c r="D71" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>679</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>680</v>
+      </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B72" s="1" t="s">
-        <v>688</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>692</v>
-      </c>
-      <c r="D72" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E72" s="2" t="s">
-        <v>691</v>
-      </c>
-      <c r="F72" s="1" t="s">
-        <v>693</v>
-      </c>
+      <c r="A72" s="4" t="s">
+        <v>682</v>
+      </c>
+      <c r="E72" s="2"/>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B73" s="1" t="s">
-        <v>694</v>
+        <v>683</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>695</v>
+        <v>687</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>696</v>
+        <v>686</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>697</v>
+        <v>688</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A74" s="4" t="s">
+      <c r="B74" s="1" t="s">
+        <v>689</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>690</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A75" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E74" s="2"/>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B75" s="1" t="s">
-        <v>902</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>857</v>
-      </c>
-      <c r="D75" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E75" s="2" t="s">
-        <v>904</v>
-      </c>
-      <c r="F75" s="1" t="s">
-        <v>906</v>
-      </c>
+      <c r="E75" s="2"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B76" s="1" t="s">
-        <v>903</v>
+        <v>896</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>858</v>
+        <v>851</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>905</v>
+        <v>898</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>907</v>
+        <v>900</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A77" s="4" t="s">
-        <v>878</v>
-      </c>
-      <c r="E77" s="2"/>
+      <c r="B77" s="1" t="s">
+        <v>897</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>852</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>899</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>901</v>
+      </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B78" s="1" t="s">
-        <v>908</v>
-      </c>
-      <c r="C78" s="6" t="s">
-        <v>829</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E78" s="2" t="s">
-        <v>910</v>
-      </c>
-      <c r="F78" s="1" t="s">
-        <v>913</v>
-      </c>
+      <c r="A78" s="4" t="s">
+        <v>872</v>
+      </c>
+      <c r="E78" s="2"/>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
-        <v>909</v>
+        <v>902</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>830</v>
+        <v>823</v>
       </c>
       <c r="D79" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>911</v>
+        <v>904</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>912</v>
+        <v>907</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A80" s="4" t="s">
-        <v>879</v>
-      </c>
-      <c r="E80" s="2"/>
+      <c r="B80" s="1" t="s">
+        <v>903</v>
+      </c>
+      <c r="C80" s="6" t="s">
+        <v>824</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>905</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>906</v>
+      </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B81" s="1" t="s">
-        <v>914</v>
-      </c>
-      <c r="C81" s="6" t="s">
-        <v>831</v>
-      </c>
-      <c r="D81" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E81" s="2" t="s">
-        <v>916</v>
-      </c>
-      <c r="F81" s="1" t="s">
-        <v>918</v>
-      </c>
+      <c r="A81" s="4" t="s">
+        <v>873</v>
+      </c>
+      <c r="E81" s="2"/>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B82" s="1" t="s">
-        <v>915</v>
+        <v>908</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>832</v>
+        <v>825</v>
       </c>
       <c r="D82" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>917</v>
+        <v>910</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>919</v>
+        <v>912</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A83" s="4" t="s">
-        <v>929</v>
-      </c>
-      <c r="E83" s="2"/>
+      <c r="B83" s="1" t="s">
+        <v>909</v>
+      </c>
+      <c r="C83" s="6" t="s">
+        <v>826</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>911</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>913</v>
+      </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B84" s="1" t="s">
-        <v>920</v>
-      </c>
-      <c r="C84" s="1" t="s">
-        <v>922</v>
-      </c>
-      <c r="D84" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E84" s="2" t="s">
-        <v>924</v>
-      </c>
-      <c r="F84" s="1" t="s">
-        <v>926</v>
-      </c>
+      <c r="A84" s="4" t="s">
+        <v>923</v>
+      </c>
+      <c r="E84" s="2"/>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B85" s="1" t="s">
-        <v>921</v>
+        <v>914</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>923</v>
+        <v>916</v>
       </c>
       <c r="D85" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>925</v>
+        <v>918</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>927</v>
+        <v>920</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A86" s="4" t="s">
-        <v>928</v>
-      </c>
-      <c r="E86" s="2"/>
+      <c r="B86" s="1" t="s">
+        <v>915</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>917</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>919</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>921</v>
+      </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B87" s="1" t="s">
-        <v>930</v>
-      </c>
-      <c r="C87" s="1" t="s">
-        <v>932</v>
-      </c>
-      <c r="D87" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E87" s="2" t="s">
-        <v>936</v>
-      </c>
-      <c r="F87" s="1" t="s">
-        <v>934</v>
-      </c>
+      <c r="A87" s="4" t="s">
+        <v>922</v>
+      </c>
+      <c r="E87" s="2"/>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B88" s="1" t="s">
-        <v>931</v>
+        <v>924</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>933</v>
+        <v>926</v>
       </c>
       <c r="D88" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>937</v>
+        <v>930</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>935</v>
+        <v>928</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A89" s="4" t="s">
-        <v>1238</v>
-      </c>
-      <c r="E89" s="2"/>
+      <c r="B89" s="1" t="s">
+        <v>925</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>927</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>931</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>929</v>
+      </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B90" s="1" t="s">
-        <v>1239</v>
-      </c>
-      <c r="C90" s="1" t="s">
-        <v>1241</v>
-      </c>
-      <c r="D90" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E90" s="2" t="s">
-        <v>1243</v>
-      </c>
-      <c r="F90" s="1" t="s">
-        <v>1245</v>
-      </c>
+      <c r="A90" s="4" t="s">
+        <v>1214</v>
+      </c>
+      <c r="E90" s="2"/>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B91" s="1" t="s">
-        <v>1240</v>
+        <v>1215</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>1242</v>
+        <v>1217</v>
       </c>
       <c r="D91" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>1244</v>
+        <v>1219</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>1246</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A92" s="4" t="s">
-        <v>1248</v>
-      </c>
-      <c r="E92" s="2"/>
+      <c r="B92" s="1" t="s">
+        <v>1216</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>1218</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>1220</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>1222</v>
+      </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B93" s="1" t="s">
-        <v>1249</v>
-      </c>
-      <c r="C93" s="1" t="s">
-        <v>1250</v>
-      </c>
-      <c r="D93" s="1" t="s">
+      <c r="A93" s="4" t="s">
+        <v>1224</v>
+      </c>
+      <c r="E93" s="2"/>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B94" s="1" t="s">
+        <v>1225</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>1226</v>
+      </c>
+      <c r="D94" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E93" s="2" t="s">
-        <v>1251</v>
-      </c>
-      <c r="F93" s="1" t="s">
-        <v>1252</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A94" s="4" t="s">
-        <v>1253</v>
-      </c>
-      <c r="E94" s="2"/>
+      <c r="E94" s="2" t="s">
+        <v>1227</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>1228</v>
+      </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B95" s="1" t="s">
-        <v>1254</v>
-      </c>
-      <c r="C95" s="1" t="s">
-        <v>1255</v>
-      </c>
-      <c r="D95" s="1" t="s">
+      <c r="A95" s="4" t="s">
+        <v>1229</v>
+      </c>
+      <c r="E95" s="2"/>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B96" s="1" t="s">
+        <v>1230</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>1231</v>
+      </c>
+      <c r="D96" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E95" s="2" t="s">
-        <v>1257</v>
-      </c>
-      <c r="F95" s="1" t="s">
-        <v>1256</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A96" s="3" t="s">
+      <c r="E96" s="2" t="s">
+        <v>1233</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>1232</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A97" s="3" t="s">
+        <v>1372</v>
+      </c>
+      <c r="E97" s="2"/>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B98" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>1368</v>
+      </c>
+      <c r="E98" s="2" t="s">
         <v>1374</v>
       </c>
-      <c r="E96" s="2"/>
-    </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B97" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="D97" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="E97" s="2" t="s">
+      <c r="F98" s="6" t="s">
         <v>1375</v>
       </c>
-      <c r="F97" s="1" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A98" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E98" s="2"/>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B99" s="1" t="s">
-        <v>71</v>
+        <v>1369</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="E99" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F99" s="1" t="s">
-        <v>1334</v>
+        <v>1368</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>1377</v>
+      </c>
+      <c r="F99" s="6" t="s">
+        <v>1378</v>
       </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A100" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="E100" s="2"/>
+      <c r="B100" s="1" t="s">
+        <v>1422</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>1368</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>1423</v>
+      </c>
+      <c r="F100" s="6" t="s">
+        <v>1424</v>
+      </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B101" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="D101" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E101" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F101" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="I101" s="1" t="s">
-        <v>37</v>
-      </c>
+      <c r="A101" s="3" t="s">
+        <v>1373</v>
+      </c>
+      <c r="E101" s="2"/>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B102" s="1" t="s">
-        <v>106</v>
+        <v>1370</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E102" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="F102" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="I102" s="1" t="s">
-        <v>37</v>
+        <v>1371</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>1374</v>
+      </c>
+      <c r="F102" s="6" t="s">
+        <v>1376</v>
       </c>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B103" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="D103" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E103" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F103" s="1" t="s">
-        <v>133</v>
-      </c>
+      <c r="A103" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E103" s="2"/>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B104" s="1" t="s">
-        <v>1355</v>
+        <v>71</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>108</v>
+        <v>30</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>300</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B105" s="1" t="s">
-        <v>427</v>
-      </c>
-      <c r="D105" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E105" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="F105" s="1" t="s">
-        <v>301</v>
-      </c>
+      <c r="A105" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="E105" s="2"/>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B106" s="1" t="s">
-        <v>315</v>
+        <v>72</v>
       </c>
       <c r="D106" s="1" t="s">
         <v>29</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>299</v>
+        <v>22</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>302</v>
+        <v>122</v>
+      </c>
+      <c r="I106" s="1" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B107" s="1" t="s">
-        <v>1209</v>
+        <v>106</v>
       </c>
       <c r="D107" s="1" t="s">
         <v>29</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>1210</v>
+        <v>53</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>1211</v>
+        <v>123</v>
+      </c>
+      <c r="I107" s="1" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B108" s="1" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="D108" s="1" t="s">
         <v>29</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B109" s="1" t="s">
-        <v>107</v>
+        <v>1330</v>
       </c>
       <c r="D109" s="1" t="s">
         <v>29</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>125</v>
+        <v>299</v>
       </c>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B110" s="1" t="s">
-        <v>116</v>
+        <v>426</v>
       </c>
       <c r="D110" s="1" t="s">
         <v>29</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>110</v>
+        <v>160</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>126</v>
+        <v>300</v>
       </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B111" s="1" t="s">
-        <v>117</v>
+        <v>314</v>
       </c>
       <c r="D111" s="1" t="s">
         <v>29</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>111</v>
+        <v>298</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>127</v>
+        <v>301</v>
       </c>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B112" s="1" t="s">
-        <v>303</v>
+        <v>1185</v>
       </c>
       <c r="D112" s="1" t="s">
         <v>29</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>307</v>
+        <v>1186</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>311</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="113" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B113" s="1" t="s">
-        <v>304</v>
+        <v>115</v>
       </c>
       <c r="D113" s="1" t="s">
         <v>29</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>308</v>
+        <v>43</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>312</v>
+        <v>124</v>
       </c>
     </row>
     <row r="114" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B114" s="1" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="D114" s="1" t="s">
         <v>29</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>44</v>
+        <v>109</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="I114" s="1" t="s">
-        <v>37</v>
+        <v>125</v>
       </c>
     </row>
     <row r="115" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B115" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D115" s="1" t="s">
         <v>29</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="I115" s="1" t="s">
-        <v>37</v>
+        <v>126</v>
       </c>
     </row>
     <row r="116" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B116" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D116" s="1" t="s">
         <v>29</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="117" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B117" s="1" t="s">
-        <v>121</v>
+        <v>302</v>
       </c>
       <c r="D117" s="1" t="s">
         <v>29</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>114</v>
+        <v>306</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>131</v>
+        <v>310</v>
       </c>
     </row>
     <row r="118" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B118" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D118" s="1" t="s">
         <v>29</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="119" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B119" s="1" t="s">
-        <v>306</v>
+        <v>118</v>
       </c>
       <c r="D119" s="1" t="s">
         <v>29</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>310</v>
+        <v>44</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>314</v>
+        <v>128</v>
+      </c>
+      <c r="I119" s="1" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="120" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B120" s="1" t="s">
-        <v>1176</v>
+        <v>119</v>
       </c>
       <c r="D120" s="1" t="s">
         <v>29</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>1182</v>
+        <v>112</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>1188</v>
+        <v>129</v>
+      </c>
+      <c r="I120" s="1" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="121" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B121" s="1" t="s">
-        <v>1177</v>
+        <v>120</v>
       </c>
       <c r="D121" s="1" t="s">
         <v>29</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>1183</v>
+        <v>113</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>1189</v>
+        <v>130</v>
       </c>
     </row>
     <row r="122" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B122" s="1" t="s">
-        <v>1178</v>
+        <v>121</v>
       </c>
       <c r="D122" s="1" t="s">
         <v>29</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>1184</v>
+        <v>114</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>1190</v>
+        <v>131</v>
       </c>
     </row>
     <row r="123" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B123" s="1" t="s">
-        <v>1179</v>
+        <v>304</v>
       </c>
       <c r="D123" s="1" t="s">
         <v>29</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>1185</v>
+        <v>308</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>1191</v>
+        <v>312</v>
       </c>
     </row>
     <row r="124" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B124" s="1" t="s">
-        <v>1180</v>
+        <v>305</v>
       </c>
       <c r="D124" s="1" t="s">
         <v>29</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>1186</v>
+        <v>309</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>1192</v>
+        <v>313</v>
       </c>
     </row>
     <row r="125" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B125" s="1" t="s">
-        <v>1181</v>
+        <v>1152</v>
       </c>
       <c r="D125" s="1" t="s">
         <v>29</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>1187</v>
+        <v>1158</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>1193</v>
+        <v>1164</v>
+      </c>
+    </row>
+    <row r="126" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B126" s="1" t="s">
+        <v>1153</v>
+      </c>
+      <c r="D126" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E126" s="1" t="s">
+        <v>1159</v>
+      </c>
+      <c r="F126" s="1" t="s">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="127" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B127" s="1" t="s">
+        <v>1154</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E127" s="1" t="s">
+        <v>1160</v>
+      </c>
+      <c r="F127" s="1" t="s">
+        <v>1166</v>
       </c>
     </row>
     <row r="128" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B128" s="1" t="s">
-        <v>73</v>
+        <v>1155</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>20</v>
+        <v>1161</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="I128" s="1" t="s">
-        <v>38</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B129" s="1" t="s">
-        <v>140</v>
+        <v>1156</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>142</v>
+        <v>1162</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>555</v>
-      </c>
-      <c r="I129" s="1" t="s">
-        <v>38</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B130" s="1" t="s">
-        <v>141</v>
+        <v>1157</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>143</v>
+        <v>1163</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="I130" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A131" s="3" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B132" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="D132" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E132" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="F132" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="I132" s="1" t="s">
-        <v>39</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B133" s="1" t="s">
-        <v>326</v>
+        <v>73</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>330</v>
+        <v>139</v>
       </c>
       <c r="I133" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B134" s="1" t="s">
-        <v>323</v>
+        <v>140</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>327</v>
+        <v>142</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>331</v>
+        <v>554</v>
       </c>
       <c r="I134" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B135" s="1" t="s">
-        <v>324</v>
+        <v>141</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>328</v>
+        <v>143</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>332</v>
+        <v>144</v>
       </c>
       <c r="I135" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B136" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="D136" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E136" s="1" t="s">
-        <v>329</v>
-      </c>
-      <c r="F136" s="1" t="s">
-        <v>333</v>
+      <c r="A136" s="3" t="s">
+        <v>321</v>
       </c>
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B137" s="1" t="s">
-        <v>1233</v>
+        <v>324</v>
       </c>
       <c r="D137" s="1" t="s">
         <v>46</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>98</v>
+        <v>61</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>1234</v>
+        <v>333</v>
+      </c>
+      <c r="I137" s="1" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A138" s="3" t="s">
-        <v>388</v>
+      <c r="B138" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="D138" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E138" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F138" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="I138" s="1" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B139" s="1" t="s">
-        <v>74</v>
+        <v>322</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>20</v>
+        <v>326</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>49</v>
+        <v>330</v>
       </c>
       <c r="I139" s="1" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B140" s="1" t="s">
-        <v>390</v>
+        <v>323</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>142</v>
+        <v>327</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>391</v>
+        <v>331</v>
       </c>
       <c r="I140" s="1" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B141" s="1" t="s">
-        <v>774</v>
+        <v>334</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>775</v>
+        <v>328</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>776</v>
+        <v>332</v>
       </c>
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A142" s="3" t="s">
-        <v>55</v>
+      <c r="B142" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="D142" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E142" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="F142" s="1" t="s">
+        <v>1210</v>
       </c>
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B143" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="D143" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E143" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F143" s="1" t="s">
-        <v>389</v>
+      <c r="A143" s="3" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B144" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D144" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E144" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F144" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I144" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B145" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="D145" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E145" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="F145" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="I145" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B146" s="1" t="s">
+        <v>768</v>
+      </c>
+      <c r="D146" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E146" s="1" t="s">
+        <v>769</v>
+      </c>
+      <c r="F146" s="1" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A147" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B148" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D148" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E148" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F148" s="1" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B149" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="D149" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E149" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="F149" s="1" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B150" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="D144" s="1" t="s">
+      <c r="D150" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="E144" s="1" t="s">
+      <c r="E150" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="F144" s="1" t="s">
+      <c r="F150" s="1" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B145" s="1" t="s">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B151" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="D145" s="1" t="s">
+      <c r="D151" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="E145" s="1" t="s">
+      <c r="E151" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="F145" s="1" t="s">
+      <c r="F151" s="1" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B146" s="1" t="s">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B152" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="D146" s="1" t="s">
+      <c r="D152" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="E146" s="1" t="s">
-        <v>329</v>
-      </c>
-      <c r="F146" s="1" t="s">
+      <c r="E152" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="F152" s="1" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B147" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="D147" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E147" s="1" t="s">
-        <v>398</v>
-      </c>
-      <c r="F147" s="1" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A148" s="3" t="s">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A153" s="3" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B149" s="1" t="s">
-        <v>421</v>
-      </c>
-      <c r="D149" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E149" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="F149" s="1" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B150" s="1" t="s">
-        <v>422</v>
-      </c>
-      <c r="D150" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E150" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F150" s="1" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B151" s="1" t="s">
-        <v>423</v>
-      </c>
-      <c r="D151" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E151" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="F151" s="1" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B152" s="1" t="s">
-        <v>404</v>
-      </c>
-      <c r="D152" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E152" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="F152" s="1" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B153" s="1" t="s">
-        <v>405</v>
-      </c>
-      <c r="D153" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E153" s="1" t="s">
-        <v>329</v>
-      </c>
-      <c r="F153" s="1" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B154" s="1" t="s">
-        <v>407</v>
+        <v>420</v>
       </c>
       <c r="D154" s="1" t="s">
         <v>56</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>398</v>
+        <v>61</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.2">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B155" s="1" t="s">
-        <v>408</v>
+        <v>421</v>
       </c>
       <c r="D155" s="1" t="s">
         <v>56</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>410</v>
+        <v>22</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.2">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B156" s="1" t="s">
-        <v>1247</v>
+        <v>422</v>
       </c>
       <c r="D156" s="1" t="s">
         <v>56</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>412</v>
+        <v>53</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.2">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B157" s="1" t="s">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="D157" s="1" t="s">
         <v>56</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>415</v>
+        <v>327</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.2">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B158" s="1" t="s">
-        <v>414</v>
+        <v>404</v>
       </c>
       <c r="D158" s="1" t="s">
         <v>56</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>417</v>
+        <v>328</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.2">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B159" s="1" t="s">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="D159" s="1" t="s">
         <v>56</v>
       </c>
       <c r="E159" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="F159" s="1" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B160" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="D160" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E160" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="F160" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="F159" s="1" t="s">
-        <v>426</v>
+    </row>
+    <row r="161" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B161" s="1" t="s">
+        <v>1223</v>
+      </c>
+      <c r="D161" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E161" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="F161" s="1" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B162" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="D162" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E162" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="F162" s="1" t="s">
+        <v>423</v>
       </c>
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A163" s="3" t="s">
-        <v>67</v>
+      <c r="B163" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="D163" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E163" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="F163" s="1" t="s">
+        <v>424</v>
       </c>
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B164" s="1" t="s">
-        <v>76</v>
+        <v>415</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>53</v>
+        <v>418</v>
       </c>
       <c r="F164" s="1" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="168" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A168" s="3" t="s">
         <v>67</v>
-      </c>
-    </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="I165" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B166" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="D166" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E166" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F166" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="I166" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B167" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="D167" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E167" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="F167" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="I167" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B168" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C168" s="2"/>
-      <c r="D168" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E168" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F168" s="1" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B169" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="C169" s="2"/>
+        <v>76</v>
+      </c>
       <c r="D169" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E169" s="2" t="s">
-        <v>98</v>
+        <v>66</v>
+      </c>
+      <c r="E169" s="1" t="s">
+        <v>53</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>103</v>
+        <v>67</v>
       </c>
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B170" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="C170" s="2"/>
-      <c r="D170" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E170" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="F170" s="1" t="s">
-        <v>104</v>
+      <c r="I170" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B171" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="C171" s="2"/>
-      <c r="D171" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D171" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E171" s="2" t="s">
-        <v>99</v>
+      <c r="E171" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>105</v>
+        <v>100</v>
+      </c>
+      <c r="I171" s="1" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A172" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="C172" s="2"/>
-      <c r="D172" s="2"/>
-      <c r="E172" s="2"/>
+      <c r="B172" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D172" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E172" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F172" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="I172" s="1" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="173" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B173" s="1" t="s">
-        <v>237</v>
+        <v>78</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E173" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F173" s="2" t="s">
-        <v>249</v>
+        <v>14</v>
+      </c>
+      <c r="E173" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F173" s="1" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B174" s="1" t="s">
-        <v>556</v>
-      </c>
-      <c r="D174" s="2" t="s">
-        <v>42</v>
+        <v>79</v>
+      </c>
+      <c r="C174" s="2"/>
+      <c r="D174" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="E174" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="F174" s="2" t="s">
-        <v>250</v>
+        <v>98</v>
+      </c>
+      <c r="F174" s="1" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B175" s="1" t="s">
-        <v>238</v>
+        <v>80</v>
       </c>
       <c r="C175" s="2"/>
-      <c r="D175" s="2" t="s">
-        <v>42</v>
+      <c r="D175" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="E175" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F175" s="2" t="s">
-        <v>251</v>
+        <v>44</v>
+      </c>
+      <c r="F175" s="1" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B176" s="1" t="s">
-        <v>239</v>
+        <v>81</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E176" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="F176" s="2" t="s">
-        <v>252</v>
+        <v>14</v>
+      </c>
+      <c r="E176" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="F176" s="1" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B177" s="1" t="s">
-        <v>240</v>
+      <c r="A177" s="3" t="s">
+        <v>241</v>
       </c>
       <c r="C177" s="2"/>
-      <c r="D177" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E177" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="F177" s="2" t="s">
-        <v>253</v>
-      </c>
+      <c r="D177" s="2"/>
+      <c r="E177" s="2"/>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B178" s="1" t="s">
-        <v>241</v>
-      </c>
+        <v>236</v>
+      </c>
+      <c r="C178" s="2"/>
       <c r="D178" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E178" s="2" t="s">
-        <v>99</v>
+      <c r="E178" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B179" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="C179" s="2"/>
+        <v>555</v>
+      </c>
       <c r="D179" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E179" s="1" t="s">
-        <v>22</v>
+        <v>42</v>
+      </c>
+      <c r="E179" s="2" t="s">
+        <v>61</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B180" s="1" t="s">
-        <v>244</v>
-      </c>
+        <v>237</v>
+      </c>
+      <c r="C180" s="2"/>
       <c r="D180" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E180" s="2" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B181" s="1" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E181" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
+      </c>
+      <c r="E181" s="1" t="s">
+        <v>98</v>
       </c>
       <c r="F181" s="2" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B182" s="1" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E182" s="1" t="s">
-        <v>98</v>
+        <v>42</v>
+      </c>
+      <c r="E182" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="F182" s="2" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B183" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="C183" s="2"/>
+        <v>240</v>
+      </c>
       <c r="D183" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E183" s="2" t="s">
-        <v>44</v>
+        <v>99</v>
       </c>
       <c r="F183" s="2" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B184" s="1" t="s">
-        <v>248</v>
-      </c>
+        <v>242</v>
+      </c>
+      <c r="C184" s="2"/>
       <c r="D184" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E184" s="2" t="s">
-        <v>99</v>
+      <c r="E184" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="F184" s="2" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A185" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D185" s="2"/>
-      <c r="E185" s="2"/>
-      <c r="F185" s="2"/>
+      <c r="B185" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="D185" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E185" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F185" s="2" t="s">
+        <v>255</v>
+      </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B186" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="D186" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E186" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F186" s="1" t="s">
-        <v>261</v>
+        <v>244</v>
+      </c>
+      <c r="C186" s="2"/>
+      <c r="D186" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E186" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F186" s="2" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B187" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="D187" s="1" t="s">
-        <v>15</v>
+        <v>245</v>
+      </c>
+      <c r="C187" s="2"/>
+      <c r="D187" s="2" t="s">
+        <v>45</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="F187" s="1" t="s">
-        <v>265</v>
+        <v>98</v>
+      </c>
+      <c r="F187" s="2" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B188" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="D188" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E188" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F188" s="1" t="s">
-        <v>266</v>
+        <v>246</v>
+      </c>
+      <c r="C188" s="2"/>
+      <c r="D188" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E188" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F188" s="2" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B189" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="D189" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E189" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="F189" s="1" t="s">
-        <v>267</v>
+        <v>247</v>
+      </c>
+      <c r="D189" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E189" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="F189" s="2" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B190" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="D190" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E190" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F190" s="1" t="s">
-        <v>276</v>
-      </c>
+      <c r="A190" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D190" s="2"/>
+      <c r="E190" s="2"/>
+      <c r="F190" s="2"/>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B191" s="1" t="s">
-        <v>269</v>
+        <v>82</v>
       </c>
       <c r="D191" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>109</v>
+        <v>22</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>277</v>
+        <v>260</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B192" s="1" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="D192" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>110</v>
+        <v>53</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>278</v>
+        <v>264</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B193" s="1" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="D193" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>111</v>
+        <v>30</v>
       </c>
       <c r="F193" s="1" t="s">
-        <v>279</v>
+        <v>265</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B194" s="1" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="D194" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>44</v>
+        <v>108</v>
       </c>
       <c r="F194" s="1" t="s">
-        <v>280</v>
+        <v>266</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B195" s="1" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="D195" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>112</v>
+        <v>43</v>
       </c>
       <c r="F195" s="1" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B196" s="1" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="D196" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="F196" s="1" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B197" s="1" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="D197" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="F197" s="1" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A198" s="3" t="s">
-        <v>750</v>
+      <c r="B198" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="D198" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E198" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="F198" s="1" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B199" s="1" t="s">
-        <v>83</v>
+        <v>271</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>51</v>
+        <v>15</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>863</v>
+        <v>44</v>
       </c>
       <c r="F199" s="1" t="s">
-        <v>748</v>
+        <v>279</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B200" s="1" t="s">
-        <v>1006</v>
+        <v>272</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>51</v>
+        <v>15</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>751</v>
+        <v>112</v>
       </c>
       <c r="F200" s="1" t="s">
-        <v>1003</v>
+        <v>280</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B201" s="1" t="s">
-        <v>1007</v>
+        <v>273</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>51</v>
+        <v>15</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>752</v>
+        <v>113</v>
       </c>
       <c r="F201" s="1" t="s">
-        <v>1004</v>
+        <v>281</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B202" s="1" t="s">
-        <v>1008</v>
+        <v>274</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>51</v>
+        <v>15</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>753</v>
+        <v>114</v>
       </c>
       <c r="F202" s="1" t="s">
-        <v>1005</v>
+        <v>282</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B203" s="1" t="s">
-        <v>1014</v>
-      </c>
-      <c r="D203" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="E203" s="1" t="s">
-        <v>837</v>
-      </c>
-      <c r="F203" s="1" t="s">
-        <v>1015</v>
+      <c r="A203" s="3" t="s">
+        <v>745</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B204" s="1" t="s">
-        <v>1032</v>
+        <v>83</v>
       </c>
       <c r="D204" s="1" t="s">
         <v>51</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>1033</v>
+        <v>857</v>
       </c>
       <c r="F204" s="1" t="s">
-        <v>1034</v>
+        <v>743</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A205" s="3" t="s">
-        <v>749</v>
+      <c r="B205" s="1" t="s">
+        <v>983</v>
+      </c>
+      <c r="D205" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E205" s="1" t="s">
+        <v>746</v>
+      </c>
+      <c r="F205" s="1" t="s">
+        <v>980</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B206" s="1" t="s">
-        <v>84</v>
+        <v>984</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>751</v>
+        <v>747</v>
       </c>
       <c r="F206" s="1" t="s">
-        <v>747</v>
+        <v>981</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B207" s="1" t="s">
-        <v>1135</v>
+        <v>985</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
       <c r="F207" s="1" t="s">
-        <v>754</v>
+        <v>982</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B208" s="1" t="s">
-        <v>847</v>
+        <v>991</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>753</v>
+        <v>831</v>
       </c>
       <c r="F208" s="1" t="s">
-        <v>755</v>
+        <v>992</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B209" s="1" t="s">
-        <v>825</v>
+        <v>1009</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>823</v>
+        <v>1010</v>
       </c>
       <c r="F209" s="1" t="s">
-        <v>824</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B210" s="1" t="s">
-        <v>836</v>
-      </c>
-      <c r="D210" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="E210" s="1" t="s">
-        <v>837</v>
-      </c>
-      <c r="F210" s="1" t="s">
-        <v>838</v>
+      <c r="A210" s="3" t="s">
+        <v>744</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B211" s="1" t="s">
-        <v>862</v>
+        <v>84</v>
       </c>
       <c r="D211" s="1" t="s">
         <v>52</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>863</v>
+        <v>746</v>
       </c>
       <c r="F211" s="1" t="s">
-        <v>864</v>
+        <v>742</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B212" s="1" t="s">
-        <v>884</v>
+        <v>1111</v>
       </c>
       <c r="D212" s="1" t="s">
         <v>52</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>885</v>
+        <v>747</v>
       </c>
       <c r="F212" s="1" t="s">
-        <v>886</v>
+        <v>749</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B213" s="1" t="s">
-        <v>976</v>
+        <v>841</v>
       </c>
       <c r="D213" s="1" t="s">
         <v>52</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>974</v>
+        <v>748</v>
       </c>
       <c r="F213" s="1" t="s">
-        <v>975</v>
+        <v>750</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B214" s="1" t="s">
-        <v>1089</v>
+        <v>819</v>
       </c>
       <c r="D214" s="1" t="s">
         <v>52</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>1033</v>
+        <v>817</v>
       </c>
       <c r="F214" s="1" t="s">
-        <v>1090</v>
+        <v>818</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B215" s="1" t="s">
+        <v>830</v>
+      </c>
+      <c r="D215" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E215" s="1" t="s">
+        <v>831</v>
+      </c>
+      <c r="F215" s="1" t="s">
+        <v>832</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B216" s="1" t="s">
-        <v>85</v>
+        <v>856</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>20</v>
+        <v>857</v>
       </c>
       <c r="F216" s="1" t="s">
-        <v>19</v>
+        <v>858</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A217" s="3" t="s">
-        <v>177</v>
+      <c r="B217" s="1" t="s">
+        <v>878</v>
+      </c>
+      <c r="D217" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E217" s="1" t="s">
+        <v>879</v>
+      </c>
+      <c r="F217" s="1" t="s">
+        <v>880</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B218" s="1" t="s">
-        <v>443</v>
+        <v>953</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>474</v>
+        <v>951</v>
       </c>
       <c r="F218" s="1" t="s">
-        <v>449</v>
+        <v>952</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B219" s="1" t="s">
-        <v>543</v>
+        <v>1066</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>475</v>
+        <v>1010</v>
       </c>
       <c r="F219" s="1" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B220" s="1" t="s">
-        <v>548</v>
-      </c>
-      <c r="D220" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E220" s="1" t="s">
-        <v>476</v>
-      </c>
-      <c r="F220" s="1" t="s">
-        <v>451</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B221" s="1" t="s">
-        <v>1276</v>
+        <v>85</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>1278</v>
+        <v>20</v>
       </c>
       <c r="F221" s="1" t="s">
-        <v>1277</v>
+        <v>19</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B222" s="1" t="s">
-        <v>591</v>
-      </c>
-      <c r="D222" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E222" s="1" t="s">
-        <v>592</v>
-      </c>
-      <c r="F222" s="1" t="s">
-        <v>593</v>
+      <c r="A222" s="3" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B223" s="1" t="s">
-        <v>1288</v>
+        <v>442</v>
       </c>
       <c r="D223" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E223" s="1" t="s">
-        <v>1289</v>
+        <v>473</v>
       </c>
       <c r="F223" s="1" t="s">
-        <v>1290</v>
+        <v>448</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B224" s="1" t="s">
-        <v>515</v>
+        <v>542</v>
       </c>
       <c r="D224" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>514</v>
+        <v>474</v>
       </c>
       <c r="F224" s="1" t="s">
-        <v>477</v>
+        <v>449</v>
       </c>
     </row>
     <row r="225" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B225" s="1" t="s">
-        <v>989</v>
+        <v>547</v>
       </c>
       <c r="D225" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>991</v>
+        <v>475</v>
       </c>
       <c r="F225" s="1" t="s">
-        <v>990</v>
+        <v>450</v>
       </c>
     </row>
     <row r="226" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B226" s="1" t="s">
-        <v>1097</v>
+        <v>1252</v>
       </c>
       <c r="D226" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>1098</v>
+        <v>1254</v>
       </c>
       <c r="F226" s="1" t="s">
-        <v>1099</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="227" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B227" s="1" t="s">
-        <v>656</v>
+        <v>590</v>
       </c>
       <c r="D227" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E227" s="1" t="s">
-        <v>654</v>
+        <v>591</v>
       </c>
       <c r="F227" s="1" t="s">
-        <v>655</v>
+        <v>592</v>
       </c>
     </row>
     <row r="228" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B228" s="1" t="s">
-        <v>516</v>
+        <v>1264</v>
       </c>
       <c r="D228" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E228" s="1" t="s">
-        <v>478</v>
+        <v>1265</v>
       </c>
       <c r="F228" s="1" t="s">
-        <v>452</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="229" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B229" s="1" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="D229" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E229" s="1" t="s">
-        <v>479</v>
+        <v>513</v>
       </c>
       <c r="F229" s="1" t="s">
-        <v>542</v>
+        <v>476</v>
       </c>
     </row>
     <row r="230" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B230" s="1" t="s">
-        <v>518</v>
+        <v>966</v>
       </c>
       <c r="D230" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>484</v>
+        <v>968</v>
       </c>
       <c r="F230" s="1" t="s">
-        <v>453</v>
+        <v>967</v>
       </c>
     </row>
     <row r="231" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B231" s="1" t="s">
-        <v>519</v>
+        <v>1074</v>
       </c>
       <c r="D231" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E231" s="1" t="s">
-        <v>480</v>
+        <v>1075</v>
       </c>
       <c r="F231" s="1" t="s">
-        <v>454</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="232" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B232" s="1" t="s">
-        <v>520</v>
+        <v>651</v>
       </c>
       <c r="D232" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>481</v>
+        <v>649</v>
       </c>
       <c r="F232" s="1" t="s">
-        <v>455</v>
+        <v>650</v>
       </c>
     </row>
     <row r="233" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B233" s="1" t="s">
-        <v>547</v>
+        <v>515</v>
       </c>
       <c r="D233" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="F233" s="1" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
     </row>
     <row r="234" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B234" s="1" t="s">
-        <v>550</v>
+        <v>516</v>
       </c>
       <c r="D234" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="F234" s="1" t="s">
-        <v>457</v>
+        <v>541</v>
       </c>
     </row>
     <row r="235" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B235" s="1" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="D235" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E235" s="1" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="F235" s="1" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
     </row>
     <row r="236" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B236" s="1" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="D236" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E236" s="1" t="s">
-        <v>486</v>
+        <v>479</v>
       </c>
       <c r="F236" s="1" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
     </row>
     <row r="237" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B237" s="1" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="D237" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E237" s="1" t="s">
-        <v>487</v>
+        <v>480</v>
       </c>
       <c r="F237" s="1" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
     </row>
     <row r="238" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B238" s="1" t="s">
-        <v>524</v>
+        <v>546</v>
       </c>
       <c r="D238" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E238" s="1" t="s">
-        <v>488</v>
+        <v>481</v>
       </c>
       <c r="F238" s="1" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
     </row>
     <row r="239" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B239" s="1" t="s">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="D239" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E239" s="1" t="s">
-        <v>489</v>
+        <v>482</v>
       </c>
       <c r="F239" s="1" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
     </row>
     <row r="240" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B240" s="1" t="s">
-        <v>546</v>
+        <v>520</v>
       </c>
       <c r="D240" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E240" s="1" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="F240" s="1" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
     </row>
     <row r="241" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B241" s="1" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="D241" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E241" s="1" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="F241" s="1" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
     </row>
     <row r="242" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B242" s="1" t="s">
-        <v>1173</v>
+        <v>522</v>
       </c>
       <c r="D242" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E242" s="1" t="s">
-        <v>1174</v>
+        <v>486</v>
       </c>
       <c r="F242" s="1" t="s">
-        <v>1175</v>
+        <v>459</v>
       </c>
     </row>
     <row r="243" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B243" s="1" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="D243" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E243" s="1" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="F243" s="1" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
     </row>
     <row r="244" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B244" s="1" t="s">
-        <v>527</v>
+        <v>543</v>
       </c>
       <c r="D244" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E244" s="1" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="F244" s="1" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
     </row>
     <row r="245" spans="2:6" x14ac:dyDescent="0.2">
@@ -9187,3223 +9377,3429 @@
         <v>21</v>
       </c>
       <c r="E245" s="1" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="F245" s="1" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
     </row>
     <row r="246" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B246" s="1" t="s">
-        <v>674</v>
+        <v>524</v>
       </c>
       <c r="D246" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E246" s="1" t="s">
-        <v>675</v>
+        <v>490</v>
       </c>
       <c r="F246" s="1" t="s">
-        <v>676</v>
+        <v>463</v>
       </c>
     </row>
     <row r="247" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B247" s="1" t="s">
-        <v>528</v>
+        <v>1149</v>
       </c>
       <c r="D247" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>495</v>
+        <v>1150</v>
       </c>
       <c r="F247" s="1" t="s">
-        <v>468</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="248" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B248" s="1" t="s">
-        <v>1291</v>
+        <v>525</v>
       </c>
       <c r="D248" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E248" s="1" t="s">
-        <v>1292</v>
+        <v>491</v>
       </c>
       <c r="F248" s="1" t="s">
-        <v>1293</v>
+        <v>464</v>
       </c>
     </row>
     <row r="249" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B249" s="1" t="s">
-        <v>1273</v>
+        <v>526</v>
       </c>
       <c r="D249" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E249" s="1" t="s">
-        <v>1274</v>
+        <v>492</v>
       </c>
       <c r="F249" s="1" t="s">
-        <v>1275</v>
+        <v>465</v>
       </c>
     </row>
     <row r="250" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B250" s="1" t="s">
-        <v>1051</v>
+        <v>544</v>
       </c>
       <c r="D250" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E250" s="1" t="s">
-        <v>1052</v>
+        <v>493</v>
       </c>
       <c r="F250" s="1" t="s">
-        <v>1053</v>
+        <v>466</v>
       </c>
     </row>
     <row r="251" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B251" s="1" t="s">
-        <v>529</v>
+        <v>669</v>
       </c>
       <c r="D251" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E251" s="1" t="s">
-        <v>496</v>
+        <v>670</v>
       </c>
       <c r="F251" s="1" t="s">
-        <v>469</v>
+        <v>671</v>
       </c>
     </row>
     <row r="252" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B252" s="1" t="s">
-        <v>601</v>
+        <v>527</v>
       </c>
       <c r="D252" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E252" s="1" t="s">
-        <v>603</v>
+        <v>494</v>
       </c>
       <c r="F252" s="1" t="s">
-        <v>605</v>
+        <v>467</v>
       </c>
     </row>
     <row r="253" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B253" s="1" t="s">
-        <v>602</v>
+        <v>1267</v>
       </c>
       <c r="D253" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E253" s="1" t="s">
-        <v>604</v>
+        <v>1268</v>
       </c>
       <c r="F253" s="1" t="s">
-        <v>606</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="254" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B254" s="1" t="s">
-        <v>973</v>
+        <v>1249</v>
       </c>
       <c r="D254" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E254" s="1" t="s">
-        <v>971</v>
+        <v>1250</v>
       </c>
       <c r="F254" s="1" t="s">
-        <v>972</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="255" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B255" s="1" t="s">
-        <v>977</v>
+        <v>1028</v>
       </c>
       <c r="D255" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E255" s="1" t="s">
-        <v>978</v>
+        <v>1029</v>
       </c>
       <c r="F255" s="1" t="s">
-        <v>979</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="256" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B256" s="1" t="s">
-        <v>1279</v>
+        <v>528</v>
       </c>
       <c r="D256" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E256" s="1" t="s">
-        <v>1280</v>
+        <v>495</v>
       </c>
       <c r="F256" s="1" t="s">
-        <v>1281</v>
+        <v>468</v>
       </c>
     </row>
     <row r="257" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B257" s="1" t="s">
-        <v>1136</v>
+        <v>600</v>
       </c>
       <c r="D257" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E257" s="1" t="s">
-        <v>1137</v>
+        <v>602</v>
       </c>
       <c r="F257" s="1" t="s">
-        <v>1138</v>
+        <v>604</v>
       </c>
     </row>
     <row r="258" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B258" s="1" t="s">
-        <v>1139</v>
+        <v>601</v>
       </c>
       <c r="D258" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E258" s="1" t="s">
-        <v>1140</v>
+        <v>603</v>
       </c>
       <c r="F258" s="1" t="s">
-        <v>1141</v>
+        <v>605</v>
       </c>
     </row>
     <row r="259" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B259" s="1" t="s">
-        <v>1294</v>
+        <v>950</v>
       </c>
       <c r="D259" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>1295</v>
+        <v>948</v>
       </c>
       <c r="F259" s="1" t="s">
-        <v>1296</v>
+        <v>949</v>
       </c>
     </row>
     <row r="260" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B260" s="1" t="s">
-        <v>1022</v>
+        <v>954</v>
       </c>
       <c r="D260" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E260" s="1" t="s">
-        <v>1023</v>
+        <v>955</v>
       </c>
       <c r="F260" s="1" t="s">
-        <v>1024</v>
+        <v>956</v>
       </c>
     </row>
     <row r="261" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B261" s="1" t="s">
-        <v>1297</v>
+        <v>1255</v>
       </c>
       <c r="D261" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E261" s="1" t="s">
-        <v>1298</v>
+        <v>1256</v>
       </c>
       <c r="F261" s="1" t="s">
-        <v>1299</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="262" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B262" s="1" t="s">
-        <v>594</v>
+        <v>1112</v>
       </c>
       <c r="D262" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E262" s="1" t="s">
-        <v>595</v>
+        <v>1113</v>
       </c>
       <c r="F262" s="1" t="s">
-        <v>596</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="263" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B263" s="1" t="s">
-        <v>646</v>
+        <v>1115</v>
       </c>
       <c r="D263" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E263" s="1" t="s">
-        <v>647</v>
+        <v>1116</v>
       </c>
       <c r="F263" s="1" t="s">
-        <v>648</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="264" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B264" s="1" t="s">
-        <v>1083</v>
+        <v>1270</v>
       </c>
       <c r="D264" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E264" s="1" t="s">
-        <v>1084</v>
+        <v>1271</v>
       </c>
       <c r="F264" s="1" t="s">
-        <v>1085</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="265" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B265" s="1" t="s">
-        <v>629</v>
+        <v>999</v>
       </c>
       <c r="D265" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E265" s="1" t="s">
-        <v>630</v>
+        <v>1000</v>
       </c>
       <c r="F265" s="1" t="s">
-        <v>631</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="266" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B266" s="1" t="s">
-        <v>1335</v>
+        <v>1273</v>
       </c>
       <c r="D266" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E266" s="1" t="s">
-        <v>1336</v>
+        <v>1274</v>
       </c>
       <c r="F266" s="1" t="s">
-        <v>1337</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="267" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B267" s="1" t="s">
-        <v>1146</v>
+        <v>593</v>
       </c>
       <c r="D267" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E267" s="1" t="s">
-        <v>1147</v>
+        <v>594</v>
       </c>
       <c r="F267" s="1" t="s">
-        <v>1148</v>
+        <v>595</v>
       </c>
     </row>
     <row r="268" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B268" s="1" t="s">
-        <v>649</v>
+        <v>642</v>
       </c>
       <c r="D268" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E268" s="1" t="s">
-        <v>650</v>
+        <v>643</v>
       </c>
       <c r="F268" s="1" t="s">
-        <v>651</v>
+        <v>644</v>
       </c>
     </row>
     <row r="269" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B269" s="1" t="s">
-        <v>1364</v>
+        <v>1060</v>
       </c>
       <c r="D269" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E269" s="1" t="s">
-        <v>1365</v>
+        <v>1061</v>
       </c>
       <c r="F269" s="1" t="s">
-        <v>1366</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="270" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B270" s="1" t="s">
-        <v>1019</v>
+        <v>625</v>
       </c>
       <c r="D270" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E270" s="1" t="s">
-        <v>1020</v>
+        <v>626</v>
       </c>
       <c r="F270" s="1" t="s">
-        <v>1021</v>
+        <v>627</v>
       </c>
     </row>
     <row r="271" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B271" s="1" t="s">
-        <v>770</v>
+        <v>1310</v>
       </c>
       <c r="D271" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E271" s="1" t="s">
-        <v>771</v>
+        <v>1311</v>
       </c>
       <c r="F271" s="1" t="s">
-        <v>772</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="272" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B272" s="1" t="s">
-        <v>530</v>
+        <v>1122</v>
       </c>
       <c r="D272" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E272" s="1" t="s">
-        <v>497</v>
+        <v>1123</v>
       </c>
       <c r="F272" s="1" t="s">
-        <v>470</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="273" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B273" s="1" t="s">
-        <v>817</v>
+        <v>645</v>
       </c>
       <c r="D273" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E273" s="1" t="s">
-        <v>818</v>
+        <v>646</v>
       </c>
       <c r="F273" s="1" t="s">
-        <v>819</v>
+        <v>647</v>
       </c>
     </row>
     <row r="274" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B274" s="1" t="s">
-        <v>1115</v>
+        <v>1339</v>
       </c>
       <c r="D274" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E274" s="1" t="s">
-        <v>1116</v>
+        <v>1340</v>
       </c>
       <c r="F274" s="1" t="s">
-        <v>1117</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="275" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B275" s="1" t="s">
-        <v>1048</v>
+        <v>996</v>
       </c>
       <c r="D275" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E275" s="1" t="s">
-        <v>1049</v>
+        <v>997</v>
       </c>
       <c r="F275" s="1" t="s">
-        <v>1050</v>
+        <v>998</v>
       </c>
     </row>
     <row r="276" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B276" s="1" t="s">
-        <v>1206</v>
+        <v>765</v>
       </c>
       <c r="D276" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E276" s="1" t="s">
-        <v>1207</v>
+        <v>766</v>
       </c>
       <c r="F276" s="1" t="s">
-        <v>1208</v>
+        <v>767</v>
       </c>
     </row>
     <row r="277" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B277" s="1" t="s">
-        <v>1344</v>
+        <v>1348</v>
       </c>
       <c r="D277" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E277" s="1" t="s">
-        <v>1345</v>
+        <v>1349</v>
       </c>
       <c r="F277" s="1" t="s">
-        <v>1346</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="278" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B278" s="1" t="s">
-        <v>1112</v>
+        <v>529</v>
       </c>
       <c r="D278" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E278" s="1" t="s">
-        <v>1113</v>
+        <v>496</v>
       </c>
       <c r="F278" s="1" t="s">
-        <v>1114</v>
+        <v>469</v>
       </c>
     </row>
     <row r="279" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B279" s="1" t="s">
-        <v>1330</v>
+        <v>811</v>
       </c>
       <c r="D279" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E279" s="1" t="s">
-        <v>1331</v>
+        <v>812</v>
       </c>
       <c r="F279" s="1" t="s">
-        <v>1332</v>
+        <v>813</v>
       </c>
     </row>
     <row r="280" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B280" s="1" t="s">
-        <v>986</v>
+        <v>1092</v>
       </c>
       <c r="D280" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E280" s="1" t="s">
-        <v>987</v>
+        <v>1093</v>
       </c>
       <c r="F280" s="1" t="s">
-        <v>988</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="281" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B281" s="1" t="s">
-        <v>1194</v>
+        <v>1025</v>
       </c>
       <c r="D281" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E281" s="1" t="s">
-        <v>1195</v>
+        <v>1026</v>
       </c>
       <c r="F281" s="1" t="s">
-        <v>1196</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="282" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B282" s="1" t="s">
-        <v>1261</v>
+        <v>1182</v>
       </c>
       <c r="D282" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E282" s="1" t="s">
-        <v>1262</v>
+        <v>1183</v>
       </c>
       <c r="F282" s="1" t="s">
-        <v>1263</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="283" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B283" s="1" t="s">
-        <v>1016</v>
+        <v>1319</v>
       </c>
       <c r="D283" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E283" s="1" t="s">
-        <v>1017</v>
+        <v>1320</v>
       </c>
       <c r="F283" s="1" t="s">
-        <v>1018</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="284" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B284" s="1" t="s">
-        <v>810</v>
+        <v>1089</v>
       </c>
       <c r="D284" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E284" s="1" t="s">
-        <v>811</v>
+        <v>1090</v>
       </c>
       <c r="F284" s="1" t="s">
-        <v>812</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="285" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B285" s="1" t="s">
-        <v>963</v>
+        <v>1305</v>
       </c>
       <c r="D285" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E285" s="1" t="s">
-        <v>964</v>
+        <v>1306</v>
       </c>
       <c r="F285" s="1" t="s">
-        <v>965</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="286" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B286" s="1" t="s">
-        <v>1126</v>
+        <v>963</v>
       </c>
       <c r="D286" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E286" s="1" t="s">
-        <v>1127</v>
+        <v>964</v>
       </c>
       <c r="F286" s="1" t="s">
-        <v>1128</v>
+        <v>965</v>
       </c>
     </row>
     <row r="287" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B287" s="1" t="s">
-        <v>1130</v>
+        <v>1170</v>
       </c>
       <c r="D287" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E287" s="1" t="s">
-        <v>1131</v>
+        <v>1171</v>
       </c>
       <c r="F287" s="1" t="s">
-        <v>1132</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="288" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B288" s="1" t="s">
-        <v>1091</v>
+        <v>1237</v>
       </c>
       <c r="D288" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E288" s="1" t="s">
-        <v>1092</v>
+        <v>1238</v>
       </c>
       <c r="F288" s="1" t="s">
-        <v>1093</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="289" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B289" s="1" t="s">
-        <v>1070</v>
+        <v>993</v>
       </c>
       <c r="D289" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E289" s="1" t="s">
-        <v>1071</v>
+        <v>994</v>
       </c>
       <c r="F289" s="1" t="s">
-        <v>1072</v>
+        <v>995</v>
       </c>
     </row>
     <row r="290" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B290" s="1" t="s">
-        <v>1038</v>
+        <v>804</v>
       </c>
       <c r="D290" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E290" s="1" t="s">
-        <v>1039</v>
+        <v>805</v>
       </c>
       <c r="F290" s="1" t="s">
-        <v>1040</v>
+        <v>806</v>
       </c>
     </row>
     <row r="291" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B291" s="1" t="s">
-        <v>1197</v>
+        <v>940</v>
       </c>
       <c r="D291" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E291" s="1" t="s">
-        <v>1198</v>
+        <v>941</v>
       </c>
       <c r="F291" s="1" t="s">
-        <v>1199</v>
+        <v>942</v>
       </c>
     </row>
     <row r="292" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B292" s="1" t="s">
-        <v>1200</v>
+        <v>1103</v>
       </c>
       <c r="D292" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E292" s="1" t="s">
-        <v>1201</v>
+        <v>1104</v>
       </c>
       <c r="F292" s="1" t="s">
-        <v>1202</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="293" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B293" s="1" t="s">
-        <v>1094</v>
+        <v>1107</v>
       </c>
       <c r="D293" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E293" s="1" t="s">
-        <v>1095</v>
+        <v>1108</v>
       </c>
       <c r="F293" s="1" t="s">
-        <v>1096</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="294" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B294" s="1" t="s">
-        <v>1054</v>
+        <v>1068</v>
       </c>
       <c r="D294" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E294" s="1" t="s">
-        <v>1055</v>
+        <v>1069</v>
       </c>
       <c r="F294" s="1" t="s">
-        <v>1056</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="295" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B295" s="1" t="s">
-        <v>790</v>
+        <v>1047</v>
       </c>
       <c r="D295" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E295" s="1" t="s">
-        <v>793</v>
+        <v>1048</v>
       </c>
       <c r="F295" s="1" t="s">
-        <v>551</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="296" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B296" s="1" t="s">
-        <v>848</v>
+        <v>1015</v>
       </c>
       <c r="D296" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E296" s="1" t="s">
-        <v>849</v>
+        <v>1016</v>
       </c>
       <c r="F296" s="1" t="s">
-        <v>850</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="297" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B297" s="1" t="s">
-        <v>794</v>
+        <v>1173</v>
       </c>
       <c r="D297" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E297" s="1" t="s">
-        <v>796</v>
+        <v>1174</v>
       </c>
       <c r="F297" s="1" t="s">
-        <v>799</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="298" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B298" s="1" t="s">
-        <v>1216</v>
+        <v>1176</v>
       </c>
       <c r="D298" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E298" s="1" t="s">
-        <v>1217</v>
+        <v>1177</v>
       </c>
       <c r="F298" s="1" t="s">
-        <v>853</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="299" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B299" s="1" t="s">
-        <v>851</v>
+        <v>1071</v>
       </c>
       <c r="D299" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E299" s="1" t="s">
-        <v>852</v>
+        <v>1072</v>
       </c>
       <c r="F299" s="1" t="s">
-        <v>1215</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="300" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B300" s="1" t="s">
-        <v>791</v>
+        <v>1031</v>
       </c>
       <c r="D300" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E300" s="1" t="s">
-        <v>792</v>
+        <v>1032</v>
       </c>
       <c r="F300" s="1" t="s">
-        <v>552</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="301" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B301" s="1" t="s">
-        <v>795</v>
+        <v>784</v>
       </c>
       <c r="D301" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E301" s="1" t="s">
-        <v>797</v>
+        <v>787</v>
       </c>
       <c r="F301" s="1" t="s">
-        <v>798</v>
+        <v>550</v>
       </c>
     </row>
     <row r="302" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B302" s="1" t="s">
-        <v>1309</v>
+        <v>842</v>
       </c>
       <c r="D302" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E302" s="1" t="s">
-        <v>1310</v>
+        <v>843</v>
       </c>
       <c r="F302" s="1" t="s">
-        <v>1311</v>
+        <v>844</v>
       </c>
     </row>
     <row r="303" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B303" s="1" t="s">
-        <v>826</v>
+        <v>788</v>
       </c>
       <c r="D303" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E303" s="1" t="s">
-        <v>827</v>
+        <v>790</v>
       </c>
       <c r="F303" s="1" t="s">
-        <v>828</v>
+        <v>793</v>
       </c>
     </row>
     <row r="304" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B304" s="1" t="s">
-        <v>875</v>
+        <v>1192</v>
       </c>
       <c r="D304" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E304" s="1" t="s">
-        <v>876</v>
+        <v>1193</v>
       </c>
       <c r="F304" s="1" t="s">
-        <v>877</v>
+        <v>847</v>
       </c>
     </row>
     <row r="305" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B305" s="1" t="s">
-        <v>1067</v>
+        <v>845</v>
       </c>
       <c r="D305" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E305" s="1" t="s">
-        <v>1068</v>
+        <v>846</v>
       </c>
       <c r="F305" s="1" t="s">
-        <v>1069</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="306" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B306" s="1" t="s">
-        <v>1060</v>
+        <v>785</v>
       </c>
       <c r="D306" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E306" s="1" t="s">
-        <v>1061</v>
+        <v>786</v>
       </c>
       <c r="F306" s="1" t="s">
-        <v>1062</v>
+        <v>551</v>
       </c>
     </row>
     <row r="307" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B307" s="1" t="s">
-        <v>1035</v>
+        <v>789</v>
       </c>
       <c r="D307" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E307" s="1" t="s">
-        <v>1036</v>
+        <v>791</v>
       </c>
       <c r="F307" s="1" t="s">
-        <v>1037</v>
+        <v>792</v>
       </c>
     </row>
     <row r="308" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B308" s="1" t="s">
-        <v>783</v>
+        <v>1285</v>
       </c>
       <c r="D308" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E308" s="1" t="s">
-        <v>501</v>
+        <v>1286</v>
       </c>
       <c r="F308" s="1" t="s">
-        <v>532</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="309" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B309" s="1" t="s">
-        <v>1029</v>
+        <v>820</v>
       </c>
       <c r="D309" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E309" s="1" t="s">
-        <v>1122</v>
+        <v>821</v>
       </c>
       <c r="F309" s="1" t="s">
-        <v>1031</v>
+        <v>822</v>
       </c>
     </row>
     <row r="310" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B310" s="1" t="s">
-        <v>1121</v>
+        <v>869</v>
       </c>
       <c r="D310" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E310" s="1" t="s">
-        <v>1030</v>
+        <v>870</v>
       </c>
       <c r="F310" s="1" t="s">
-        <v>1123</v>
+        <v>871</v>
       </c>
     </row>
     <row r="311" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B311" s="1" t="s">
-        <v>531</v>
+        <v>1044</v>
       </c>
       <c r="D311" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E311" s="1" t="s">
-        <v>498</v>
+        <v>1045</v>
       </c>
       <c r="F311" s="1" t="s">
-        <v>471</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="312" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B312" s="1" t="s">
-        <v>1044</v>
+        <v>1037</v>
       </c>
       <c r="D312" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E312" s="1" t="s">
-        <v>499</v>
+        <v>1038</v>
       </c>
       <c r="F312" s="1" t="s">
-        <v>472</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="313" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B313" s="1" t="s">
-        <v>549</v>
+        <v>1012</v>
       </c>
       <c r="D313" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E313" s="1" t="s">
-        <v>500</v>
+        <v>1013</v>
       </c>
       <c r="F313" s="1" t="s">
-        <v>473</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="314" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B314" s="1" t="s">
-        <v>782</v>
+        <v>777</v>
       </c>
       <c r="D314" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E314" s="1" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="F314" s="1" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
     </row>
     <row r="315" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B315" s="1" t="s">
-        <v>814</v>
+        <v>1006</v>
       </c>
       <c r="D315" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E315" s="1" t="s">
-        <v>815</v>
+        <v>1099</v>
       </c>
       <c r="F315" s="1" t="s">
-        <v>816</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="316" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B316" s="1" t="s">
-        <v>1264</v>
+        <v>1098</v>
       </c>
       <c r="D316" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E316" s="1" t="s">
-        <v>1265</v>
+        <v>1007</v>
       </c>
       <c r="F316" s="1" t="s">
-        <v>1266</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="317" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B317" s="1" t="s">
-        <v>1258</v>
+        <v>530</v>
       </c>
       <c r="D317" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E317" s="1" t="s">
-        <v>1259</v>
+        <v>497</v>
       </c>
       <c r="F317" s="1" t="s">
-        <v>1260</v>
+        <v>470</v>
       </c>
     </row>
     <row r="318" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B318" s="1" t="s">
-        <v>781</v>
+        <v>1021</v>
       </c>
       <c r="D318" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E318" s="1" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="F318" s="1" t="s">
-        <v>534</v>
+        <v>471</v>
       </c>
     </row>
     <row r="319" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B319" s="1" t="s">
-        <v>1305</v>
+        <v>548</v>
       </c>
       <c r="D319" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E319" s="1" t="s">
-        <v>1306</v>
+        <v>499</v>
       </c>
       <c r="F319" s="1" t="s">
-        <v>1308</v>
+        <v>472</v>
       </c>
     </row>
     <row r="320" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B320" s="1" t="s">
-        <v>1327</v>
+        <v>776</v>
       </c>
       <c r="D320" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E320" s="1" t="s">
-        <v>1328</v>
+        <v>501</v>
       </c>
       <c r="F320" s="1" t="s">
-        <v>1329</v>
+        <v>532</v>
       </c>
     </row>
     <row r="321" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B321" s="1" t="s">
-        <v>1304</v>
+        <v>808</v>
       </c>
       <c r="D321" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E321" s="1" t="s">
-        <v>1333</v>
+        <v>809</v>
       </c>
       <c r="F321" s="1" t="s">
-        <v>1307</v>
+        <v>810</v>
       </c>
     </row>
     <row r="322" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B322" s="1" t="s">
-        <v>784</v>
+        <v>1240</v>
       </c>
       <c r="D322" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E322" s="1" t="s">
-        <v>785</v>
+        <v>1241</v>
       </c>
       <c r="F322" s="1" t="s">
-        <v>786</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="323" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B323" s="1" t="s">
-        <v>780</v>
+        <v>1234</v>
       </c>
       <c r="D323" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E323" s="1" t="s">
-        <v>504</v>
+        <v>1235</v>
       </c>
       <c r="F323" s="1" t="s">
-        <v>535</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="324" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B324" s="1" t="s">
-        <v>787</v>
+        <v>775</v>
       </c>
       <c r="D324" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E324" s="1" t="s">
-        <v>788</v>
+        <v>502</v>
       </c>
       <c r="F324" s="1" t="s">
-        <v>789</v>
+        <v>533</v>
       </c>
     </row>
     <row r="325" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B325" s="1" t="s">
-        <v>800</v>
+        <v>1419</v>
       </c>
       <c r="D325" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E325" s="1" t="s">
-        <v>802</v>
+        <v>1420</v>
       </c>
       <c r="F325" s="1" t="s">
-        <v>801</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="326" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B326" s="1" t="s">
-        <v>803</v>
+        <v>1281</v>
       </c>
       <c r="D326" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E326" s="1" t="s">
-        <v>804</v>
+        <v>1282</v>
       </c>
       <c r="F326" s="1" t="s">
-        <v>813</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="327" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B327" s="1" t="s">
-        <v>887</v>
+        <v>1302</v>
       </c>
       <c r="D327" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E327" s="1" t="s">
-        <v>888</v>
+        <v>1303</v>
       </c>
       <c r="F327" s="1" t="s">
-        <v>889</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="328" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B328" s="1" t="s">
-        <v>1118</v>
+        <v>1280</v>
       </c>
       <c r="D328" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E328" s="1" t="s">
-        <v>1119</v>
+        <v>1308</v>
       </c>
       <c r="F328" s="1" t="s">
-        <v>1120</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="329" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B329" s="1" t="s">
-        <v>1086</v>
+        <v>778</v>
       </c>
       <c r="D329" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E329" s="1" t="s">
-        <v>1087</v>
+        <v>779</v>
       </c>
       <c r="F329" s="1" t="s">
-        <v>1088</v>
+        <v>780</v>
       </c>
     </row>
     <row r="330" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B330" s="1" t="s">
-        <v>1103</v>
+        <v>774</v>
       </c>
       <c r="D330" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E330" s="1" t="s">
-        <v>1104</v>
+        <v>503</v>
       </c>
       <c r="F330" s="1" t="s">
-        <v>1105</v>
+        <v>534</v>
       </c>
     </row>
     <row r="331" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B331" s="1" t="s">
-        <v>1057</v>
+        <v>781</v>
       </c>
       <c r="D331" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E331" s="1" t="s">
-        <v>1058</v>
+        <v>782</v>
       </c>
       <c r="F331" s="1" t="s">
-        <v>1059</v>
+        <v>783</v>
       </c>
     </row>
     <row r="332" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B332" s="1" t="s">
-        <v>1282</v>
+        <v>794</v>
       </c>
       <c r="D332" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E332" s="1" t="s">
-        <v>1284</v>
+        <v>796</v>
       </c>
       <c r="F332" s="1" t="s">
-        <v>1283</v>
+        <v>795</v>
       </c>
     </row>
     <row r="333" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B333" s="1" t="s">
-        <v>1285</v>
+        <v>797</v>
       </c>
       <c r="D333" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E333" s="1" t="s">
-        <v>1286</v>
+        <v>798</v>
       </c>
       <c r="F333" s="1" t="s">
-        <v>1287</v>
+        <v>807</v>
       </c>
     </row>
     <row r="334" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B334" s="1" t="s">
-        <v>777</v>
+        <v>881</v>
       </c>
       <c r="D334" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E334" s="1" t="s">
-        <v>778</v>
+        <v>882</v>
       </c>
       <c r="F334" s="1" t="s">
-        <v>779</v>
+        <v>883</v>
       </c>
     </row>
     <row r="335" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B335" s="1" t="s">
-        <v>854</v>
+        <v>1095</v>
       </c>
       <c r="D335" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E335" s="1" t="s">
-        <v>855</v>
+        <v>1096</v>
       </c>
       <c r="F335" s="1" t="s">
-        <v>856</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="336" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B336" s="1" t="s">
-        <v>1153</v>
+        <v>1063</v>
       </c>
       <c r="D336" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E336" s="1" t="s">
-        <v>1154</v>
+        <v>1064</v>
       </c>
       <c r="F336" s="1" t="s">
-        <v>1155</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="337" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B337" s="1" t="s">
-        <v>820</v>
+        <v>1080</v>
       </c>
       <c r="D337" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E337" s="1" t="s">
-        <v>821</v>
+        <v>1081</v>
       </c>
       <c r="F337" s="1" t="s">
-        <v>822</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="338" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B338" s="1" t="s">
-        <v>1100</v>
+        <v>1034</v>
       </c>
       <c r="D338" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E338" s="1" t="s">
-        <v>1101</v>
+        <v>1035</v>
       </c>
       <c r="F338" s="1" t="s">
-        <v>1102</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="339" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B339" s="1" t="s">
-        <v>1212</v>
+        <v>1258</v>
       </c>
       <c r="D339" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E339" s="1" t="s">
-        <v>1213</v>
+        <v>1260</v>
       </c>
       <c r="F339" s="1" t="s">
-        <v>1214</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="340" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B340" s="1" t="s">
-        <v>992</v>
+        <v>1261</v>
       </c>
       <c r="D340" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E340" s="1" t="s">
-        <v>993</v>
+        <v>1262</v>
       </c>
       <c r="F340" s="1" t="s">
-        <v>994</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="341" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B341" s="1" t="s">
-        <v>894</v>
+        <v>771</v>
       </c>
       <c r="D341" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E341" s="1" t="s">
-        <v>895</v>
+        <v>772</v>
       </c>
       <c r="F341" s="1" t="s">
-        <v>896</v>
+        <v>773</v>
       </c>
     </row>
     <row r="342" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B342" s="1" t="s">
-        <v>1321</v>
+        <v>848</v>
       </c>
       <c r="D342" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E342" s="1" t="s">
-        <v>1322</v>
+        <v>849</v>
       </c>
       <c r="F342" s="1" t="s">
-        <v>1323</v>
+        <v>850</v>
       </c>
     </row>
     <row r="343" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B343" s="1" t="s">
-        <v>983</v>
+        <v>1359</v>
       </c>
       <c r="D343" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E343" s="1" t="s">
-        <v>984</v>
+        <v>1361</v>
       </c>
       <c r="F343" s="1" t="s">
-        <v>985</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="344" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B344" s="1" t="s">
-        <v>839</v>
+        <v>1356</v>
       </c>
       <c r="D344" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E344" s="1" t="s">
-        <v>840</v>
+        <v>1357</v>
       </c>
       <c r="F344" s="1" t="s">
-        <v>841</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="345" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B345" s="1" t="s">
-        <v>1077</v>
+        <v>1129</v>
       </c>
       <c r="D345" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E345" s="1" t="s">
-        <v>1078</v>
+        <v>1130</v>
       </c>
       <c r="F345" s="1" t="s">
-        <v>1079</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="346" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B346" s="1" t="s">
-        <v>1080</v>
+        <v>814</v>
       </c>
       <c r="D346" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E346" s="1" t="s">
-        <v>1081</v>
+        <v>815</v>
       </c>
       <c r="F346" s="1" t="s">
-        <v>1082</v>
+        <v>816</v>
       </c>
     </row>
     <row r="347" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B347" s="1" t="s">
-        <v>1312</v>
+        <v>1077</v>
       </c>
       <c r="D347" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E347" s="1" t="s">
-        <v>1313</v>
+        <v>1078</v>
       </c>
       <c r="F347" s="1" t="s">
-        <v>1317</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="348" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B348" s="1" t="s">
-        <v>1318</v>
+        <v>1188</v>
       </c>
       <c r="D348" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E348" s="1" t="s">
-        <v>1319</v>
+        <v>1189</v>
       </c>
       <c r="F348" s="1" t="s">
-        <v>1320</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="349" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B349" s="1" t="s">
-        <v>1314</v>
+        <v>969</v>
       </c>
       <c r="D349" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E349" s="1" t="s">
-        <v>1315</v>
+        <v>970</v>
       </c>
       <c r="F349" s="1" t="s">
-        <v>1316</v>
+        <v>971</v>
       </c>
     </row>
     <row r="350" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B350" s="1" t="s">
-        <v>1369</v>
+        <v>888</v>
       </c>
       <c r="D350" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E350" s="1" t="s">
-        <v>1370</v>
+        <v>889</v>
       </c>
       <c r="F350" s="1" t="s">
-        <v>1371</v>
+        <v>890</v>
       </c>
     </row>
     <row r="351" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B351" s="1" t="s">
-        <v>1156</v>
+        <v>1297</v>
       </c>
       <c r="D351" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E351" s="1" t="s">
-        <v>1158</v>
+        <v>1298</v>
       </c>
       <c r="F351" s="1" t="s">
-        <v>1157</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="352" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B352" s="1" t="s">
-        <v>1041</v>
+        <v>960</v>
       </c>
       <c r="D352" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E352" s="1" t="s">
-        <v>1042</v>
+        <v>961</v>
       </c>
       <c r="F352" s="1" t="s">
-        <v>1043</v>
+        <v>962</v>
       </c>
     </row>
     <row r="353" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B353" s="1" t="s">
-        <v>1159</v>
+        <v>833</v>
       </c>
       <c r="D353" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E353" s="1" t="s">
-        <v>1160</v>
+        <v>834</v>
       </c>
       <c r="F353" s="1" t="s">
-        <v>1161</v>
+        <v>835</v>
       </c>
     </row>
     <row r="354" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B354" s="1" t="s">
-        <v>1045</v>
+        <v>1054</v>
       </c>
       <c r="D354" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E354" s="1" t="s">
-        <v>1046</v>
+        <v>1055</v>
       </c>
       <c r="F354" s="1" t="s">
-        <v>1047</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="355" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B355" s="1" t="s">
-        <v>1162</v>
+        <v>1057</v>
       </c>
       <c r="D355" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E355" s="1" t="s">
-        <v>1163</v>
+        <v>1058</v>
       </c>
       <c r="F355" s="1" t="s">
-        <v>1164</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="356" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B356" s="1" t="s">
-        <v>1106</v>
+        <v>1288</v>
       </c>
       <c r="D356" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E356" s="1" t="s">
-        <v>1107</v>
+        <v>1289</v>
       </c>
       <c r="F356" s="1" t="s">
-        <v>1108</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="357" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B357" s="1" t="s">
-        <v>1267</v>
+        <v>1362</v>
       </c>
       <c r="D357" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E357" s="1" t="s">
-        <v>1269</v>
+        <v>1363</v>
       </c>
       <c r="F357" s="1" t="s">
-        <v>1271</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="358" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B358" s="1" t="s">
-        <v>1268</v>
+        <v>1294</v>
       </c>
       <c r="D358" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E358" s="1" t="s">
-        <v>1270</v>
+        <v>1295</v>
       </c>
       <c r="F358" s="1" t="s">
-        <v>1272</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="359" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B359" s="1" t="s">
-        <v>614</v>
+        <v>1290</v>
       </c>
       <c r="D359" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E359" s="1" t="s">
-        <v>615</v>
+        <v>1291</v>
       </c>
       <c r="F359" s="1" t="s">
-        <v>616</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="360" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B360" s="1" t="s">
-        <v>448</v>
+        <v>1365</v>
       </c>
       <c r="D360" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E360" s="1" t="s">
-        <v>442</v>
+        <v>1366</v>
       </c>
       <c r="F360" s="1" t="s">
-        <v>444</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="361" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B361" s="1" t="s">
-        <v>512</v>
+        <v>1343</v>
       </c>
       <c r="D361" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E361" s="1" t="s">
-        <v>445</v>
+        <v>1344</v>
       </c>
       <c r="F361" s="1" t="s">
-        <v>447</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="362" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B362" s="1" t="s">
-        <v>513</v>
+        <v>1132</v>
       </c>
       <c r="D362" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E362" s="1" t="s">
-        <v>446</v>
+        <v>1134</v>
       </c>
       <c r="F362" s="1" t="s">
-        <v>537</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="363" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B363" s="1" t="s">
-        <v>611</v>
+        <v>1018</v>
       </c>
       <c r="D363" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E363" s="1" t="s">
-        <v>612</v>
+        <v>1019</v>
       </c>
       <c r="F363" s="1" t="s">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="364" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>1020</v>
+      </c>
+    </row>
+    <row r="364" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B364" s="1" t="s">
-        <v>698</v>
+        <v>1135</v>
       </c>
       <c r="D364" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E364" s="1" t="s">
-        <v>700</v>
+        <v>1136</v>
       </c>
       <c r="F364" s="1" t="s">
-        <v>699</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="365" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B365" s="1" t="s">
-        <v>701</v>
+        <v>1022</v>
       </c>
       <c r="D365" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E365" s="1" t="s">
-        <v>702</v>
+        <v>1023</v>
       </c>
       <c r="F365" s="1" t="s">
-        <v>703</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="366" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B366" s="1" t="s">
-        <v>714</v>
+        <v>1138</v>
       </c>
       <c r="D366" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E366" s="1" t="s">
-        <v>715</v>
+        <v>1139</v>
       </c>
       <c r="F366" s="1" t="s">
-        <v>716</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="367" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B367" s="1" t="s">
-        <v>725</v>
+        <v>1083</v>
       </c>
       <c r="D367" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E367" s="1" t="s">
-        <v>726</v>
+        <v>1084</v>
       </c>
       <c r="F367" s="1" t="s">
-        <v>727</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="368" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B368" s="1" t="s">
-        <v>732</v>
+        <v>1243</v>
       </c>
       <c r="D368" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E368" s="1" t="s">
-        <v>733</v>
+        <v>1245</v>
       </c>
       <c r="F368" s="1" t="s">
-        <v>734</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="369" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B369" s="1" t="s">
-        <v>833</v>
+        <v>1244</v>
       </c>
       <c r="D369" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E369" s="1" t="s">
-        <v>834</v>
+        <v>1246</v>
       </c>
       <c r="F369" s="1" t="s">
-        <v>835</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="370" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B370" s="1" t="s">
-        <v>859</v>
+        <v>613</v>
       </c>
       <c r="D370" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E370" s="1" t="s">
-        <v>860</v>
+        <v>614</v>
       </c>
       <c r="F370" s="1" t="s">
-        <v>861</v>
+        <v>615</v>
       </c>
     </row>
     <row r="371" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B371" s="1" t="s">
-        <v>1235</v>
+        <v>447</v>
       </c>
       <c r="D371" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E371" s="1" t="s">
-        <v>1236</v>
+        <v>441</v>
       </c>
       <c r="F371" s="1" t="s">
-        <v>1237</v>
+        <v>443</v>
       </c>
     </row>
     <row r="372" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B372" s="1" t="s">
-        <v>938</v>
+        <v>511</v>
       </c>
       <c r="D372" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E372" s="1" t="s">
-        <v>939</v>
+        <v>444</v>
       </c>
       <c r="F372" s="1" t="s">
-        <v>773</v>
+        <v>446</v>
       </c>
     </row>
     <row r="373" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B373" s="1" t="s">
-        <v>947</v>
+        <v>512</v>
       </c>
       <c r="D373" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E373" s="1" t="s">
-        <v>948</v>
+        <v>445</v>
       </c>
       <c r="F373" s="1" t="s">
-        <v>943</v>
+        <v>536</v>
       </c>
     </row>
     <row r="374" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B374" s="1" t="s">
-        <v>941</v>
+        <v>610</v>
       </c>
       <c r="D374" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E374" s="1" t="s">
-        <v>942</v>
-      </c>
-      <c r="F374" s="2" t="s">
-        <v>952</v>
-      </c>
-    </row>
-    <row r="375" spans="1:6" x14ac:dyDescent="0.2">
+        <v>611</v>
+      </c>
+      <c r="F374" s="1" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="375" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B375" s="1" t="s">
-        <v>944</v>
+        <v>693</v>
       </c>
       <c r="D375" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E375" s="1" t="s">
-        <v>949</v>
-      </c>
-      <c r="F375" s="2" t="s">
-        <v>953</v>
+        <v>695</v>
+      </c>
+      <c r="F375" s="1" t="s">
+        <v>694</v>
       </c>
     </row>
     <row r="376" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B376" s="1" t="s">
-        <v>945</v>
+        <v>696</v>
       </c>
       <c r="D376" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E376" s="1" t="s">
-        <v>950</v>
-      </c>
-      <c r="F376" s="2" t="s">
-        <v>954</v>
+        <v>697</v>
+      </c>
+      <c r="F376" s="1" t="s">
+        <v>698</v>
       </c>
     </row>
     <row r="377" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B377" s="1" t="s">
-        <v>946</v>
+        <v>709</v>
       </c>
       <c r="D377" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E377" s="1" t="s">
-        <v>951</v>
-      </c>
-      <c r="F377" s="2" t="s">
-        <v>955</v>
+        <v>710</v>
+      </c>
+      <c r="F377" s="1" t="s">
+        <v>711</v>
       </c>
     </row>
     <row r="378" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A378" s="3" t="s">
-        <v>189</v>
+      <c r="B378" s="1" t="s">
+        <v>720</v>
+      </c>
+      <c r="D378" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E378" s="1" t="s">
+        <v>721</v>
+      </c>
+      <c r="F378" s="1" t="s">
+        <v>722</v>
       </c>
     </row>
     <row r="379" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B379" s="1" t="s">
-        <v>1203</v>
+        <v>727</v>
       </c>
       <c r="D379" s="1" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E379" s="1" t="s">
-        <v>1204</v>
+        <v>728</v>
       </c>
       <c r="F379" s="1" t="s">
-        <v>1205</v>
+        <v>729</v>
       </c>
     </row>
     <row r="380" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B380" s="1" t="s">
-        <v>1109</v>
+        <v>827</v>
       </c>
       <c r="D380" s="1" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E380" s="1" t="s">
-        <v>1110</v>
+        <v>828</v>
       </c>
       <c r="F380" s="1" t="s">
-        <v>1111</v>
+        <v>829</v>
       </c>
     </row>
     <row r="381" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B381" s="1" t="s">
-        <v>540</v>
+        <v>853</v>
       </c>
       <c r="D381" s="1" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E381" s="1" t="s">
-        <v>507</v>
+        <v>854</v>
       </c>
       <c r="F381" s="1" t="s">
-        <v>508</v>
+        <v>855</v>
       </c>
     </row>
     <row r="382" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B382" s="1" t="s">
-        <v>539</v>
+        <v>1211</v>
       </c>
       <c r="D382" s="1" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E382" s="1" t="s">
-        <v>510</v>
+        <v>1212</v>
       </c>
       <c r="F382" s="1" t="s">
-        <v>509</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="383" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B383" s="1" t="s">
-        <v>538</v>
-      </c>
-      <c r="D383" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E383" s="1" t="s">
-        <v>511</v>
-      </c>
-      <c r="F383" s="1" t="s">
-        <v>536</v>
+      <c r="A383" s="3" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="384" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B384" s="1" t="s">
-        <v>541</v>
+        <v>1179</v>
       </c>
       <c r="D384" s="1" t="s">
         <v>28</v>
       </c>
       <c r="E384" s="1" t="s">
+        <v>1180</v>
+      </c>
+      <c r="F384" s="1" t="s">
+        <v>1181</v>
+      </c>
+    </row>
+    <row r="385" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B385" s="1" t="s">
+        <v>1086</v>
+      </c>
+      <c r="D385" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E385" s="1" t="s">
+        <v>1087</v>
+      </c>
+      <c r="F385" s="1" t="s">
+        <v>1088</v>
+      </c>
+    </row>
+    <row r="386" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B386" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="D386" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E386" s="1" t="s">
         <v>506</v>
       </c>
-      <c r="F384" s="1" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="386" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A386" s="3" t="s">
-        <v>58</v>
+      <c r="F386" s="1" t="s">
+        <v>507</v>
       </c>
     </row>
     <row r="387" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B387" s="1" t="s">
-        <v>86</v>
+        <v>538</v>
       </c>
       <c r="D387" s="1" t="s">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="E387" s="1" t="s">
-        <v>53</v>
+        <v>509</v>
       </c>
       <c r="F387" s="1" t="s">
-        <v>178</v>
+        <v>508</v>
       </c>
     </row>
     <row r="388" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B388" s="1" t="s">
-        <v>179</v>
+        <v>537</v>
       </c>
       <c r="D388" s="1" t="s">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="E388" s="1" t="s">
-        <v>43</v>
+        <v>510</v>
       </c>
       <c r="F388" s="1" t="s">
-        <v>180</v>
+        <v>535</v>
       </c>
     </row>
     <row r="389" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A389" s="3" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="390" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B390" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="D390" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E390" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F390" s="1" t="s">
-        <v>162</v>
+      <c r="B389" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="D389" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E389" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="F389" s="1" t="s">
+        <v>504</v>
       </c>
     </row>
     <row r="391" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B391" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="D391" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E391" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="F391" s="1" t="s">
-        <v>163</v>
+      <c r="A391" s="3" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="392" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B392" s="1" t="s">
-        <v>1129</v>
+        <v>86</v>
       </c>
       <c r="D392" s="1" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="E392" s="1" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="F392" s="1" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
     </row>
     <row r="393" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B393" s="1" t="s">
-        <v>159</v>
+        <v>178</v>
       </c>
       <c r="D393" s="1" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="E393" s="1" t="s">
-        <v>108</v>
+        <v>43</v>
       </c>
       <c r="F393" s="1" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
     </row>
     <row r="394" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B394" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="D394" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E394" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="F394" s="1" t="s">
-        <v>166</v>
+      <c r="A394" s="3" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="395" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B395" s="1" t="s">
-        <v>196</v>
+        <v>87</v>
       </c>
       <c r="D395" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E395" s="1" t="s">
-        <v>201</v>
+        <v>22</v>
       </c>
       <c r="F395" s="1" t="s">
-        <v>211</v>
+        <v>161</v>
       </c>
     </row>
     <row r="396" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B396" s="1" t="s">
-        <v>197</v>
+        <v>175</v>
       </c>
       <c r="D396" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E396" s="1" t="s">
-        <v>202</v>
+        <v>53</v>
       </c>
       <c r="F396" s="1" t="s">
-        <v>235</v>
+        <v>162</v>
       </c>
     </row>
     <row r="397" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B397" s="1" t="s">
-        <v>198</v>
+        <v>1106</v>
       </c>
       <c r="D397" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E397" s="1" t="s">
-        <v>203</v>
+        <v>30</v>
       </c>
       <c r="F397" s="1" t="s">
-        <v>212</v>
+        <v>163</v>
       </c>
     </row>
     <row r="398" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B398" s="1" t="s">
-        <v>199</v>
+        <v>158</v>
       </c>
       <c r="D398" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E398" s="1" t="s">
-        <v>204</v>
+        <v>108</v>
       </c>
       <c r="F398" s="1" t="s">
-        <v>213</v>
+        <v>164</v>
       </c>
     </row>
     <row r="399" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B399" s="1" t="s">
-        <v>200</v>
+        <v>159</v>
       </c>
       <c r="D399" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E399" s="1" t="s">
-        <v>205</v>
+        <v>160</v>
       </c>
       <c r="F399" s="1" t="s">
-        <v>214</v>
+        <v>165</v>
       </c>
     </row>
     <row r="400" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B400" s="1" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="D400" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E400" s="1" t="s">
-        <v>43</v>
+        <v>200</v>
       </c>
       <c r="F400" s="1" t="s">
-        <v>171</v>
+        <v>210</v>
       </c>
     </row>
     <row r="401" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B401" s="1" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="D401" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E401" s="1" t="s">
-        <v>167</v>
+        <v>201</v>
       </c>
       <c r="F401" s="1" t="s">
-        <v>172</v>
+        <v>234</v>
       </c>
     </row>
     <row r="402" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B402" s="1" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="D402" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E402" s="1" t="s">
-        <v>168</v>
+        <v>202</v>
       </c>
       <c r="F402" s="1" t="s">
-        <v>173</v>
+        <v>211</v>
       </c>
     </row>
     <row r="403" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B403" s="1" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="D403" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E403" s="1" t="s">
-        <v>169</v>
+        <v>203</v>
       </c>
       <c r="F403" s="1" t="s">
-        <v>174</v>
+        <v>212</v>
       </c>
     </row>
     <row r="404" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B404" s="1" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="D404" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E404" s="1" t="s">
-        <v>170</v>
+        <v>204</v>
       </c>
       <c r="F404" s="1" t="s">
-        <v>175</v>
+        <v>213</v>
       </c>
     </row>
     <row r="405" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B405" s="1" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="D405" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E405" s="1" t="s">
-        <v>215</v>
+        <v>43</v>
       </c>
       <c r="F405" s="1" t="s">
-        <v>220</v>
+        <v>170</v>
       </c>
     </row>
     <row r="406" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B406" s="1" t="s">
-        <v>226</v>
+        <v>206</v>
       </c>
       <c r="D406" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E406" s="1" t="s">
-        <v>216</v>
+        <v>166</v>
       </c>
       <c r="F406" s="1" t="s">
-        <v>221</v>
+        <v>171</v>
       </c>
     </row>
     <row r="407" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B407" s="1" t="s">
-        <v>227</v>
+        <v>207</v>
       </c>
       <c r="D407" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E407" s="1" t="s">
-        <v>217</v>
+        <v>167</v>
       </c>
       <c r="F407" s="1" t="s">
-        <v>222</v>
+        <v>172</v>
       </c>
     </row>
     <row r="408" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B408" s="1" t="s">
-        <v>228</v>
+        <v>208</v>
       </c>
       <c r="D408" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E408" s="1" t="s">
-        <v>219</v>
+        <v>168</v>
       </c>
       <c r="F408" s="1" t="s">
-        <v>223</v>
+        <v>173</v>
       </c>
     </row>
     <row r="409" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B409" s="1" t="s">
-        <v>229</v>
+        <v>209</v>
       </c>
       <c r="D409" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E409" s="1" t="s">
-        <v>218</v>
+        <v>169</v>
       </c>
       <c r="F409" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="410" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B410" s="1" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="410" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A410" s="3" t="s">
-        <v>230</v>
+      <c r="D410" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E410" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="F410" s="1" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="411" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B411" s="1" t="s">
-        <v>157</v>
+        <v>225</v>
       </c>
       <c r="D411" s="1" t="s">
-        <v>284</v>
+        <v>23</v>
       </c>
       <c r="E411" s="1" t="s">
-        <v>22</v>
+        <v>215</v>
       </c>
       <c r="F411" s="1" t="s">
-        <v>231</v>
+        <v>220</v>
+      </c>
+    </row>
+    <row r="412" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B412" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="D412" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E412" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="F412" s="1" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="413" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B413" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="D413" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E413" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="F413" s="1" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="414" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B414" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="D414" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E414" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="F414" s="1" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="415" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A415" s="3" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="416" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B416" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="D416" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="E416" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F416" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="418" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B418" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="D413" s="1" t="s">
+      <c r="D418" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E413" s="1" t="s">
+      <c r="E418" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F413" s="1" t="s">
+      <c r="F418" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="415" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B415" s="1" t="s">
+    <row r="420" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B420" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D415" s="1" t="s">
+      <c r="D420" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E415" s="1" t="s">
+      <c r="E420" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F415" s="1" t="s">
+      <c r="F420" s="1" t="s">
         <v>25</v>
-      </c>
-    </row>
-    <row r="417" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B417" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="D417" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E417" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F417" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="419" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B419" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="D419" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E419" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F419" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="420" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A420" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="421" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B421" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="D421" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E421" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F421" s="1" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="422" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B422" s="1" t="s">
-        <v>336</v>
+        <v>90</v>
       </c>
       <c r="D422" s="1" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="E422" s="1" t="s">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="F422" s="1" t="s">
-        <v>338</v>
+        <v>27</v>
       </c>
     </row>
     <row r="424" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B424" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D424" s="1" t="s">
-        <v>63</v>
+        <v>36</v>
       </c>
       <c r="E424" s="1" t="s">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="F424" s="1" t="s">
-        <v>64</v>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="425" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A425" s="3" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="426" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A426" s="3" t="s">
-        <v>286</v>
+      <c r="B426" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D426" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E426" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F426" s="1" t="s">
+        <v>336</v>
       </c>
     </row>
     <row r="427" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B427" s="1" t="s">
-        <v>151</v>
+        <v>335</v>
       </c>
       <c r="D427" s="1" t="s">
-        <v>152</v>
+        <v>40</v>
       </c>
       <c r="E427" s="1" t="s">
-        <v>1338</v>
+        <v>53</v>
       </c>
       <c r="F427" s="1" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="428" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B428" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="D428" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="E428" s="1" t="s">
-        <v>1339</v>
-      </c>
-      <c r="F428" s="1" t="s">
-        <v>156</v>
+        <v>337</v>
       </c>
     </row>
     <row r="429" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B429" s="1" t="s">
-        <v>678</v>
+        <v>93</v>
       </c>
       <c r="D429" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E429" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F429" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="431" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A431" s="3" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="432" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B432" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="D432" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="E432" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="F432" s="1" t="s">
         <v>152</v>
-      </c>
-      <c r="E429" s="1" t="s">
-        <v>1340</v>
-      </c>
-      <c r="F429" s="1" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="430" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B430" s="1" t="s">
-        <v>872</v>
-      </c>
-      <c r="D430" s="1" t="s">
-        <v>873</v>
-      </c>
-      <c r="E430" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F430" s="1" t="s">
-        <v>874</v>
-      </c>
-    </row>
-    <row r="431" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B431" s="1" t="s">
-        <v>1341</v>
-      </c>
-      <c r="D431" s="1" t="s">
-        <v>873</v>
-      </c>
-      <c r="E431" s="1" t="s">
-        <v>1342</v>
-      </c>
-      <c r="F431" s="1" t="s">
-        <v>1343</v>
-      </c>
-    </row>
-    <row r="432" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A432" s="3" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="433" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B433" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D433" s="1" t="s">
-        <v>289</v>
+        <v>154</v>
       </c>
       <c r="E433" s="1" t="s">
-        <v>20</v>
+        <v>1314</v>
       </c>
       <c r="F433" s="1" t="s">
-        <v>290</v>
+        <v>155</v>
       </c>
     </row>
     <row r="434" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B434" s="1" t="s">
-        <v>291</v>
+        <v>673</v>
       </c>
       <c r="D434" s="1" t="s">
-        <v>319</v>
+        <v>151</v>
       </c>
       <c r="E434" s="1" t="s">
-        <v>20</v>
+        <v>1315</v>
       </c>
       <c r="F434" s="1" t="s">
-        <v>292</v>
+        <v>674</v>
       </c>
     </row>
     <row r="435" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A435" s="3" t="s">
-        <v>295</v>
+      <c r="B435" s="1" t="s">
+        <v>866</v>
+      </c>
+      <c r="D435" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="E435" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F435" s="1" t="s">
+        <v>868</v>
       </c>
     </row>
     <row r="436" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B436" s="1" t="s">
-        <v>293</v>
+        <v>1316</v>
       </c>
       <c r="D436" s="1" t="s">
-        <v>294</v>
+        <v>867</v>
       </c>
       <c r="E436" s="1" t="s">
-        <v>709</v>
+        <v>1317</v>
       </c>
       <c r="F436" s="1" t="s">
-        <v>298</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="437" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B437" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="D437" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="E437" s="1" t="s">
-        <v>710</v>
-      </c>
-      <c r="F437" s="1" t="s">
-        <v>296</v>
+      <c r="A437" s="3" t="s">
+        <v>287</v>
       </c>
     </row>
     <row r="438" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A438" s="3" t="s">
-        <v>343</v>
+      <c r="B438" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D438" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="E438" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F438" s="1" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="439" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B439" s="1" t="s">
-        <v>344</v>
+        <v>290</v>
       </c>
       <c r="D439" s="1" t="s">
-        <v>345</v>
+        <v>318</v>
       </c>
       <c r="E439" s="1" t="s">
-        <v>349</v>
+        <v>20</v>
       </c>
       <c r="F439" s="1" t="s">
-        <v>350</v>
+        <v>291</v>
       </c>
     </row>
     <row r="440" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B440" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="D440" s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="E440" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="F440" s="1" t="s">
-        <v>360</v>
+      <c r="A440" s="3" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="441" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B441" s="1" t="s">
-        <v>347</v>
+        <v>292</v>
       </c>
       <c r="D441" s="1" t="s">
-        <v>345</v>
+        <v>293</v>
       </c>
       <c r="E441" s="1" t="s">
-        <v>354</v>
+        <v>704</v>
       </c>
       <c r="F441" s="1" t="s">
-        <v>361</v>
+        <v>297</v>
       </c>
     </row>
     <row r="442" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B442" s="1" t="s">
-        <v>348</v>
+        <v>296</v>
       </c>
       <c r="D442" s="1" t="s">
-        <v>345</v>
+        <v>293</v>
       </c>
       <c r="E442" s="1" t="s">
-        <v>355</v>
+        <v>705</v>
       </c>
       <c r="F442" s="1" t="s">
-        <v>351</v>
+        <v>295</v>
       </c>
     </row>
     <row r="443" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B443" s="1" t="s">
-        <v>366</v>
-      </c>
-      <c r="D443" s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="E443" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="F443" s="1" t="s">
-        <v>362</v>
+      <c r="A443" s="3" t="s">
+        <v>342</v>
       </c>
     </row>
     <row r="444" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B444" s="1" t="s">
-        <v>367</v>
+        <v>343</v>
       </c>
       <c r="D444" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E444" s="1" t="s">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="F444" s="1" t="s">
-        <v>363</v>
+        <v>349</v>
       </c>
     </row>
     <row r="445" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B445" s="1" t="s">
-        <v>1168</v>
+        <v>345</v>
       </c>
       <c r="D445" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E445" s="1" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="F445" s="1" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
     </row>
     <row r="446" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B446" s="1" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="D446" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E446" s="1" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="F446" s="1" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
     </row>
     <row r="447" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A447" s="3" t="s">
-        <v>431</v>
+      <c r="B447" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="D447" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="E447" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="F447" s="1" t="s">
+        <v>350</v>
       </c>
     </row>
     <row r="448" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B448" s="1" t="s">
-        <v>432</v>
+        <v>365</v>
       </c>
       <c r="D448" s="1" t="s">
-        <v>433</v>
+        <v>344</v>
       </c>
       <c r="E448" s="1" t="s">
-        <v>22</v>
+        <v>355</v>
       </c>
       <c r="F448" s="1" t="s">
-        <v>435</v>
+        <v>361</v>
       </c>
     </row>
     <row r="449" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B449" s="1" t="s">
-        <v>434</v>
+        <v>366</v>
       </c>
       <c r="D449" s="1" t="s">
-        <v>433</v>
+        <v>344</v>
       </c>
       <c r="E449" s="1" t="s">
-        <v>53</v>
+        <v>356</v>
       </c>
       <c r="F449" s="1" t="s">
-        <v>436</v>
+        <v>362</v>
       </c>
     </row>
     <row r="450" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A450" s="3" t="s">
-        <v>600</v>
+      <c r="B450" s="1" t="s">
+        <v>1144</v>
+      </c>
+      <c r="D450" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="E450" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="F450" s="1" t="s">
+        <v>363</v>
       </c>
     </row>
     <row r="451" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B451" s="1" t="s">
-        <v>597</v>
+        <v>351</v>
       </c>
       <c r="D451" s="1" t="s">
-        <v>598</v>
+        <v>344</v>
       </c>
       <c r="E451" s="1" t="s">
-        <v>43</v>
+        <v>358</v>
       </c>
       <c r="F451" s="1" t="s">
-        <v>599</v>
+        <v>364</v>
       </c>
     </row>
     <row r="452" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B452" s="1" t="s">
-        <v>662</v>
-      </c>
-      <c r="D452" s="1" t="s">
-        <v>664</v>
-      </c>
-      <c r="F452" s="1" t="s">
-        <v>663</v>
+      <c r="A452" s="3" t="s">
+        <v>430</v>
       </c>
     </row>
     <row r="453" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B453" s="1" t="s">
-        <v>956</v>
+        <v>431</v>
       </c>
       <c r="D453" s="1" t="s">
-        <v>957</v>
+        <v>432</v>
+      </c>
+      <c r="E453" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="F453" s="1" t="s">
-        <v>958</v>
+        <v>434</v>
       </c>
     </row>
     <row r="454" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A454" s="3" t="s">
-        <v>617</v>
+      <c r="B454" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="D454" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="E454" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F454" s="1" t="s">
+        <v>435</v>
       </c>
     </row>
     <row r="455" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B455" s="1" t="s">
-        <v>618</v>
-      </c>
-      <c r="D455" s="1" t="s">
-        <v>623</v>
-      </c>
-      <c r="E455" s="1" t="s">
-        <v>1372</v>
-      </c>
-      <c r="F455" s="6" t="s">
-        <v>628</v>
+      <c r="A455" s="3" t="s">
+        <v>599</v>
       </c>
     </row>
     <row r="456" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B456" s="1" t="s">
-        <v>632</v>
+        <v>596</v>
       </c>
       <c r="D456" s="1" t="s">
-        <v>623</v>
+        <v>597</v>
       </c>
       <c r="E456" s="1" t="s">
-        <v>1373</v>
-      </c>
-      <c r="F456" s="6" t="s">
-        <v>633</v>
+        <v>43</v>
+      </c>
+      <c r="F456" s="1" t="s">
+        <v>598</v>
       </c>
     </row>
     <row r="457" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A457" s="3" t="s">
-        <v>624</v>
+      <c r="B457" s="1" t="s">
+        <v>657</v>
+      </c>
+      <c r="D457" s="1" t="s">
+        <v>659</v>
+      </c>
+      <c r="F457" s="1" t="s">
+        <v>658</v>
       </c>
     </row>
     <row r="458" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B458" s="1" t="s">
-        <v>1133</v>
+        <v>933</v>
       </c>
       <c r="D458" s="1" t="s">
-        <v>626</v>
-      </c>
-      <c r="E458" s="1" t="s">
-        <v>61</v>
+        <v>934</v>
       </c>
       <c r="F458" s="1" t="s">
-        <v>1134</v>
+        <v>935</v>
       </c>
     </row>
     <row r="459" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B459" s="1" t="s">
-        <v>652</v>
-      </c>
-      <c r="D459" s="1" t="s">
-        <v>626</v>
-      </c>
-      <c r="E459" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F459" s="1" t="s">
-        <v>653</v>
+      <c r="A459" s="3" t="s">
+        <v>616</v>
       </c>
     </row>
     <row r="460" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B460" s="1" t="s">
-        <v>625</v>
+        <v>617</v>
       </c>
       <c r="D460" s="1" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="E460" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="F460" s="1" t="s">
-        <v>627</v>
+        <v>1346</v>
+      </c>
+      <c r="F460" s="6" t="s">
+        <v>624</v>
       </c>
     </row>
     <row r="461" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B461" s="1" t="s">
-        <v>1367</v>
+        <v>628</v>
       </c>
       <c r="D461" s="1" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="E461" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="F461" s="1" t="s">
-        <v>1368</v>
+        <v>1347</v>
+      </c>
+      <c r="F461" s="6" t="s">
+        <v>629</v>
       </c>
     </row>
     <row r="462" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B462" s="1" t="s">
-        <v>1324</v>
-      </c>
-      <c r="D462" s="1" t="s">
-        <v>626</v>
-      </c>
-      <c r="E462" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="F462" s="1" t="s">
-        <v>1325</v>
+      <c r="A462" s="3" t="s">
+        <v>1392</v>
       </c>
     </row>
     <row r="463" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A463" s="3" t="s">
-        <v>713</v>
+      <c r="B463" s="1" t="s">
+        <v>1395</v>
+      </c>
+      <c r="D463" s="1" t="s">
+        <v>1391</v>
+      </c>
+      <c r="E463" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="F463" s="1" t="s">
+        <v>1110</v>
       </c>
     </row>
     <row r="464" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B464" s="1" t="s">
-        <v>704</v>
+        <v>1396</v>
       </c>
       <c r="D464" s="1" t="s">
-        <v>708</v>
+        <v>1391</v>
       </c>
       <c r="E464" s="1" t="s">
-        <v>711</v>
-      </c>
-      <c r="F464" s="6" t="s">
-        <v>707</v>
+        <v>353</v>
+      </c>
+      <c r="F464" s="1" t="s">
+        <v>648</v>
       </c>
     </row>
     <row r="465" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B465" s="1" t="s">
-        <v>705</v>
+        <v>1397</v>
       </c>
       <c r="D465" s="1" t="s">
-        <v>708</v>
+        <v>1391</v>
       </c>
       <c r="E465" s="1" t="s">
-        <v>712</v>
-      </c>
-      <c r="F465" s="6" t="s">
-        <v>706</v>
+        <v>1381</v>
+      </c>
+      <c r="F465" s="1" t="s">
+        <v>623</v>
       </c>
     </row>
     <row r="466" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A466" s="3" t="s">
-        <v>718</v>
-      </c>
-      <c r="F466" s="6"/>
-    </row>
-    <row r="467" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B466" s="1" t="s">
+        <v>1398</v>
+      </c>
+      <c r="D466" s="1" t="s">
+        <v>1391</v>
+      </c>
+      <c r="E466" s="1" t="s">
+        <v>1393</v>
+      </c>
+      <c r="F466" s="1" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="467" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B467" s="1" t="s">
-        <v>719</v>
+        <v>1399</v>
       </c>
       <c r="D467" s="1" t="s">
-        <v>720</v>
+        <v>1391</v>
       </c>
       <c r="E467" s="1" t="s">
-        <v>721</v>
-      </c>
-      <c r="F467" s="6" t="s">
-        <v>722</v>
+        <v>1394</v>
+      </c>
+      <c r="F467" s="1" t="s">
+        <v>1300</v>
       </c>
     </row>
     <row r="468" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B468" s="1" t="s">
-        <v>717</v>
+        <v>1400</v>
       </c>
       <c r="D468" s="1" t="s">
-        <v>720</v>
+        <v>1391</v>
       </c>
       <c r="E468" s="1" t="s">
-        <v>723</v>
-      </c>
-      <c r="F468" s="6" t="s">
-        <v>724</v>
+        <v>1401</v>
+      </c>
+      <c r="F468" s="1" t="s">
+        <v>1402</v>
       </c>
     </row>
     <row r="469" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A469" s="3" t="s">
-        <v>728</v>
-      </c>
-      <c r="F469" s="6"/>
+      <c r="B469" s="1" t="s">
+        <v>1412</v>
+      </c>
+      <c r="D469" s="1" t="s">
+        <v>1391</v>
+      </c>
+      <c r="E469" s="1" t="s">
+        <v>1413</v>
+      </c>
+      <c r="F469" s="1" t="s">
+        <v>1414</v>
+      </c>
     </row>
     <row r="470" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B470" s="1" t="s">
-        <v>731</v>
-      </c>
-      <c r="D470" s="1" t="s">
-        <v>900</v>
-      </c>
-      <c r="E470" s="1" t="s">
-        <v>729</v>
-      </c>
-      <c r="F470" s="6" t="s">
-        <v>730</v>
+      <c r="A470" s="3" t="s">
+        <v>708</v>
       </c>
     </row>
     <row r="471" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B471" s="1" t="s">
-        <v>735</v>
+        <v>699</v>
       </c>
       <c r="D471" s="1" t="s">
-        <v>900</v>
+        <v>703</v>
       </c>
       <c r="E471" s="1" t="s">
-        <v>899</v>
+        <v>706</v>
       </c>
       <c r="F471" s="6" t="s">
-        <v>901</v>
+        <v>702</v>
       </c>
     </row>
     <row r="472" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A472" s="3" t="s">
-        <v>756</v>
-      </c>
-      <c r="F472" s="6"/>
+      <c r="B472" s="1" t="s">
+        <v>700</v>
+      </c>
+      <c r="D472" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="E472" s="1" t="s">
+        <v>707</v>
+      </c>
+      <c r="F472" s="6" t="s">
+        <v>701</v>
+      </c>
     </row>
     <row r="473" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B473" s="1" t="s">
-        <v>758</v>
-      </c>
-      <c r="D473" s="1" t="s">
-        <v>760</v>
-      </c>
-      <c r="E473" s="1" t="s">
-        <v>763</v>
-      </c>
-      <c r="F473" s="6" t="s">
-        <v>767</v>
-      </c>
+      <c r="A473" s="3" t="s">
+        <v>713</v>
+      </c>
+      <c r="F473" s="6"/>
     </row>
     <row r="474" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B474" s="1" t="s">
-        <v>759</v>
+        <v>714</v>
       </c>
       <c r="D474" s="1" t="s">
-        <v>760</v>
+        <v>715</v>
       </c>
       <c r="E474" s="1" t="s">
-        <v>765</v>
+        <v>716</v>
       </c>
       <c r="F474" s="6" t="s">
-        <v>768</v>
+        <v>717</v>
       </c>
     </row>
     <row r="475" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B475" s="1" t="s">
-        <v>764</v>
+        <v>712</v>
       </c>
       <c r="D475" s="1" t="s">
-        <v>760</v>
+        <v>715</v>
       </c>
       <c r="E475" s="1" t="s">
-        <v>766</v>
+        <v>718</v>
       </c>
       <c r="F475" s="6" t="s">
-        <v>769</v>
+        <v>719</v>
       </c>
     </row>
     <row r="476" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B476" s="1" t="s">
-        <v>980</v>
-      </c>
-      <c r="D476" s="1" t="s">
-        <v>760</v>
-      </c>
-      <c r="E476" s="1" t="s">
-        <v>981</v>
-      </c>
-      <c r="F476" s="6" t="s">
-        <v>982</v>
-      </c>
+      <c r="A476" s="3" t="s">
+        <v>723</v>
+      </c>
+      <c r="F476" s="6"/>
     </row>
     <row r="477" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A477" s="3" t="s">
-        <v>757</v>
-      </c>
-      <c r="F477" s="6"/>
+      <c r="B477" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="D477" s="1" t="s">
+        <v>894</v>
+      </c>
+      <c r="E477" s="1" t="s">
+        <v>724</v>
+      </c>
+      <c r="F477" s="6" t="s">
+        <v>725</v>
+      </c>
     </row>
     <row r="478" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B478" s="1" t="s">
-        <v>761</v>
+        <v>730</v>
       </c>
       <c r="D478" s="1" t="s">
-        <v>762</v>
+        <v>894</v>
       </c>
       <c r="E478" s="1" t="s">
-        <v>763</v>
+        <v>893</v>
       </c>
       <c r="F478" s="6" t="s">
-        <v>809</v>
+        <v>895</v>
       </c>
     </row>
     <row r="479" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B479" s="1" t="s">
-        <v>1012</v>
-      </c>
-      <c r="D479" s="1" t="s">
-        <v>762</v>
-      </c>
-      <c r="E479" s="1" t="s">
-        <v>765</v>
-      </c>
-      <c r="F479" s="6" t="s">
-        <v>1010</v>
-      </c>
+      <c r="A479" s="3" t="s">
+        <v>751</v>
+      </c>
+      <c r="F479" s="6"/>
     </row>
     <row r="480" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B480" s="1" t="s">
-        <v>1009</v>
+        <v>753</v>
       </c>
       <c r="D480" s="1" t="s">
+        <v>755</v>
+      </c>
+      <c r="E480" s="1" t="s">
+        <v>758</v>
+      </c>
+      <c r="F480" s="6" t="s">
         <v>762</v>
-      </c>
-      <c r="E480" s="1" t="s">
-        <v>766</v>
-      </c>
-      <c r="F480" s="6" t="s">
-        <v>1011</v>
       </c>
     </row>
     <row r="481" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B481" s="1" t="s">
-        <v>1013</v>
+        <v>754</v>
       </c>
       <c r="D481" s="1" t="s">
-        <v>762</v>
+        <v>755</v>
       </c>
       <c r="E481" s="1" t="s">
-        <v>1025</v>
+        <v>760</v>
       </c>
       <c r="F481" s="6" t="s">
-        <v>1026</v>
+        <v>763</v>
       </c>
     </row>
     <row r="482" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A482" s="3" t="s">
-        <v>805</v>
-      </c>
-      <c r="F482" s="6"/>
+      <c r="B482" s="1" t="s">
+        <v>759</v>
+      </c>
+      <c r="D482" s="1" t="s">
+        <v>755</v>
+      </c>
+      <c r="E482" s="1" t="s">
+        <v>761</v>
+      </c>
+      <c r="F482" s="6" t="s">
+        <v>764</v>
+      </c>
     </row>
     <row r="483" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B483" s="1" t="s">
-        <v>1124</v>
+        <v>957</v>
       </c>
       <c r="D483" s="1" t="s">
-        <v>808</v>
+        <v>755</v>
       </c>
       <c r="E483" s="1" t="s">
-        <v>22</v>
+        <v>958</v>
       </c>
       <c r="F483" s="6" t="s">
-        <v>1125</v>
+        <v>959</v>
       </c>
     </row>
     <row r="484" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B484" s="1" t="s">
-        <v>806</v>
-      </c>
-      <c r="D484" s="1" t="s">
-        <v>808</v>
-      </c>
-      <c r="E484" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F484" s="6" t="s">
-        <v>807</v>
-      </c>
+      <c r="A484" s="3" t="s">
+        <v>752</v>
+      </c>
+      <c r="F484" s="6"/>
     </row>
     <row r="485" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B485" s="1" t="s">
-        <v>1027</v>
+        <v>756</v>
       </c>
       <c r="D485" s="1" t="s">
-        <v>808</v>
+        <v>757</v>
       </c>
       <c r="E485" s="1" t="s">
-        <v>109</v>
+        <v>758</v>
       </c>
       <c r="F485" s="6" t="s">
-        <v>1028</v>
+        <v>803</v>
       </c>
     </row>
     <row r="486" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B486" s="1" t="s">
-        <v>1231</v>
+        <v>989</v>
       </c>
       <c r="D486" s="1" t="s">
-        <v>808</v>
+        <v>757</v>
       </c>
       <c r="E486" s="1" t="s">
-        <v>1182</v>
+        <v>760</v>
       </c>
       <c r="F486" s="6" t="s">
-        <v>1232</v>
+        <v>987</v>
       </c>
     </row>
     <row r="487" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B487" s="1" t="s">
-        <v>1230</v>
+        <v>986</v>
       </c>
       <c r="D487" s="1" t="s">
-        <v>808</v>
+        <v>757</v>
       </c>
       <c r="E487" s="1" t="s">
-        <v>1183</v>
+        <v>761</v>
       </c>
       <c r="F487" s="6" t="s">
-        <v>1326</v>
+        <v>988</v>
       </c>
     </row>
     <row r="488" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A488" s="3" t="s">
-        <v>880</v>
-      </c>
-      <c r="F488" s="6"/>
+      <c r="B488" s="1" t="s">
+        <v>990</v>
+      </c>
+      <c r="D488" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="E488" s="1" t="s">
+        <v>1002</v>
+      </c>
+      <c r="F488" s="6" t="s">
+        <v>1003</v>
+      </c>
     </row>
     <row r="489" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B489" s="1" t="s">
-        <v>881</v>
-      </c>
-      <c r="D489" s="1" t="s">
-        <v>882</v>
-      </c>
-      <c r="E489" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F489" s="6" t="s">
-        <v>883</v>
-      </c>
+      <c r="A489" s="3" t="s">
+        <v>799</v>
+      </c>
+      <c r="F489" s="6"/>
     </row>
     <row r="490" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A490" s="3" t="s">
-        <v>891</v>
-      </c>
-      <c r="F490" s="6"/>
+      <c r="B490" s="1" t="s">
+        <v>1101</v>
+      </c>
+      <c r="D490" s="1" t="s">
+        <v>802</v>
+      </c>
+      <c r="E490" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F490" s="6" t="s">
+        <v>1102</v>
+      </c>
     </row>
     <row r="491" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B491" s="1" t="s">
-        <v>892</v>
+        <v>800</v>
       </c>
       <c r="D491" s="1" t="s">
-        <v>893</v>
+        <v>802</v>
       </c>
       <c r="E491" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F491" s="6" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="492" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B492" s="1" t="s">
+        <v>1004</v>
+      </c>
+      <c r="D492" s="1" t="s">
+        <v>802</v>
+      </c>
+      <c r="E492" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="F491" s="6" t="s">
-        <v>890</v>
-      </c>
-    </row>
-    <row r="492" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A492" s="3" t="s">
-        <v>970</v>
-      </c>
-      <c r="F492" s="6"/>
+      <c r="F492" s="6" t="s">
+        <v>1005</v>
+      </c>
     </row>
     <row r="493" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B493" s="1" t="s">
-        <v>966</v>
+        <v>1207</v>
       </c>
       <c r="D493" s="1" t="s">
-        <v>967</v>
+        <v>802</v>
       </c>
       <c r="E493" s="1" t="s">
-        <v>969</v>
+        <v>1158</v>
       </c>
       <c r="F493" s="6" t="s">
-        <v>968</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="494" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A494" s="3" t="s">
+      <c r="B494" s="1" t="s">
+        <v>1206</v>
+      </c>
+      <c r="D494" s="1" t="s">
+        <v>802</v>
+      </c>
+      <c r="E494" s="1" t="s">
+        <v>1159</v>
+      </c>
+      <c r="F494" s="6" t="s">
+        <v>1301</v>
+      </c>
+    </row>
+    <row r="495" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A495" s="3" t="s">
+        <v>874</v>
+      </c>
+      <c r="F495" s="6"/>
+    </row>
+    <row r="496" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B496" s="1" t="s">
+        <v>875</v>
+      </c>
+      <c r="D496" s="1" t="s">
+        <v>876</v>
+      </c>
+      <c r="E496" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F496" s="6" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="497" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A497" s="3" t="s">
+        <v>885</v>
+      </c>
+      <c r="F497" s="6"/>
+    </row>
+    <row r="498" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B498" s="1" t="s">
+        <v>886</v>
+      </c>
+      <c r="D498" s="1" t="s">
+        <v>887</v>
+      </c>
+      <c r="E498" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="F498" s="6" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="499" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A499" s="3" t="s">
+        <v>947</v>
+      </c>
+      <c r="F499" s="6"/>
+    </row>
+    <row r="500" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B500" s="1" t="s">
+        <v>943</v>
+      </c>
+      <c r="D500" s="1" t="s">
+        <v>944</v>
+      </c>
+      <c r="E500" s="1" t="s">
+        <v>946</v>
+      </c>
+      <c r="F500" s="6" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="501" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A501" s="3" t="s">
+        <v>1353</v>
+      </c>
+      <c r="F501" s="6"/>
+    </row>
+    <row r="502" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B502" s="1" t="s">
+        <v>1351</v>
+      </c>
+      <c r="D502" s="1" t="s">
+        <v>1352</v>
+      </c>
+      <c r="E502" s="1" t="s">
+        <v>1355</v>
+      </c>
+      <c r="F502" s="6" t="s">
+        <v>1354</v>
+      </c>
+    </row>
+    <row r="503" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A503" s="7" t="s">
+        <v>1380</v>
+      </c>
+      <c r="F503" s="6"/>
+    </row>
+    <row r="504" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B504" s="1" t="s">
+        <v>1388</v>
+      </c>
+      <c r="D504" s="1" t="s">
+        <v>1379</v>
+      </c>
+      <c r="E504" s="1" t="s">
+        <v>1389</v>
+      </c>
+      <c r="F504" s="6" t="s">
+        <v>1390</v>
+      </c>
+    </row>
+    <row r="505" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B505" s="1" t="s">
+        <v>1383</v>
+      </c>
+      <c r="D505" s="1" t="s">
+        <v>1379</v>
+      </c>
+      <c r="E505" s="1" t="s">
+        <v>1382</v>
+      </c>
+      <c r="F505" s="6" t="s">
+        <v>1385</v>
+      </c>
+    </row>
+    <row r="506" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B506" s="1" t="s">
+        <v>1384</v>
+      </c>
+      <c r="D506" s="1" t="s">
+        <v>1379</v>
+      </c>
+      <c r="E506" s="1" t="s">
+        <v>1387</v>
+      </c>
+      <c r="F506" s="6" t="s">
+        <v>1386</v>
+      </c>
+    </row>
+    <row r="507" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A507" s="7" t="s">
+        <v>1403</v>
+      </c>
+      <c r="F507" s="6"/>
+    </row>
+    <row r="508" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B508" s="1" t="s">
+        <v>1404</v>
+      </c>
+      <c r="D508" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E508" s="1" t="s">
+        <v>1406</v>
+      </c>
+      <c r="F508" s="6" t="s">
+        <v>1407</v>
+      </c>
+    </row>
+    <row r="509" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A509" s="7" t="s">
+        <v>1418</v>
+      </c>
+      <c r="F509" s="6"/>
+    </row>
+    <row r="510" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B510" s="1" t="s">
+        <v>1415</v>
+      </c>
+      <c r="D510" s="1" t="s">
+        <v>1417</v>
+      </c>
+      <c r="E510" s="1" t="s">
+        <v>1382</v>
+      </c>
+      <c r="F510" s="6" t="s">
+        <v>1416</v>
+      </c>
+    </row>
+    <row r="511" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A511" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="512" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B512" s="1" t="s">
         <v>587</v>
       </c>
-    </row>
-    <row r="495" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B495" s="1" t="s">
+      <c r="D512" s="5" t="s">
         <v>588</v>
       </c>
-      <c r="D495" s="5" t="s">
+      <c r="E512" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F512" s="1" t="s">
         <v>589</v>
       </c>
-      <c r="E495" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F495" s="1" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="496" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A496" s="3" t="s">
+    </row>
+    <row r="513" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A513" s="3" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="514" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B514" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="D514" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="F514" s="1" t="s">
         <v>341</v>
-      </c>
-    </row>
-    <row r="497" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B497" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="D497" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="F497" s="1" t="s">
-        <v>342</v>
       </c>
     </row>
   </sheetData>

--- a/Luban/Config/Datas/#BattleMomentEffectConfig.xlsx
+++ b/Luban/Config/Datas/#BattleMomentEffectConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98149279-BC5B-4E13-8F22-3E4F696FC19E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{709ACDA5-4D97-44E2-BA46-53F22CC6C12D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2125" uniqueCount="1601">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2145" uniqueCount="1618">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -6300,6 +6300,74 @@
   </si>
   <si>
     <t>127206501</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6900001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ReturnSkillResourceCost</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自身返还刚气消耗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>返还技能消耗(目标，刚气，玄气，键)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>窃取一种消耗品</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7000001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>StealBattleProp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>窃取目标一个消耗品</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4041</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4041002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Effect4041002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(目标)下一次术杀式的基础威力不会低于140%技（巧来方计状态）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4046</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4046001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Effect4046001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>下一次行动中恢复刚炁时获得等量玄炁，恢复玄炁时获得等量刚炁（玉摄念状态）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -6724,7 +6792,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4CF470-E9E0-44FF-BA6C-71B5C42FB7B2}">
-  <dimension ref="A1:I582"/>
+  <dimension ref="A1:I590"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="29.75" style="1" customWidth="1"/>
@@ -14112,209 +14180,287 @@
       </c>
     </row>
     <row r="560" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A560" s="3" t="s">
-        <v>584</v>
-      </c>
+      <c r="A560" s="7" t="s">
+        <v>1605</v>
+      </c>
+      <c r="F560" s="6"/>
     </row>
     <row r="561" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B561" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="D561" s="5" t="s">
-        <v>586</v>
+        <v>1601</v>
+      </c>
+      <c r="D561" s="1" t="s">
+        <v>1603</v>
       </c>
       <c r="E561" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F561" s="1" t="s">
-        <v>587</v>
+        <v>1602</v>
+      </c>
+      <c r="F561" s="6" t="s">
+        <v>1604</v>
       </c>
     </row>
     <row r="562" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A562" s="3" t="s">
-        <v>340</v>
-      </c>
+      <c r="A562" s="7" t="s">
+        <v>1606</v>
+      </c>
+      <c r="F562" s="6"/>
     </row>
     <row r="563" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B563" s="1" t="s">
+        <v>1607</v>
+      </c>
+      <c r="D563" s="1" t="s">
+        <v>1608</v>
+      </c>
+      <c r="E563" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F563" s="6" t="s">
+        <v>1609</v>
+      </c>
+    </row>
+    <row r="564" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A564" s="3" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="565" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B565" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="D565" s="5" t="s">
+        <v>586</v>
+      </c>
+      <c r="E565" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F565" s="1" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="566" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A566" s="3" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="567" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B567" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="D563" s="1" t="s">
+      <c r="D567" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="F563" s="1" t="s">
+      <c r="F567" s="1" t="s">
         <v>341</v>
-      </c>
-    </row>
-    <row r="565" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A565" s="3" t="s">
-        <v>1489</v>
-      </c>
-    </row>
-    <row r="566" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B566" s="1" t="s">
-        <v>1490</v>
-      </c>
-      <c r="D566" s="1" t="s">
-        <v>1491</v>
-      </c>
-      <c r="E566" s="1" t="s">
-        <v>1493</v>
-      </c>
-      <c r="F566" s="6" t="s">
-        <v>1492</v>
-      </c>
-    </row>
-    <row r="567" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A567" s="3" t="s">
-        <v>1582</v>
-      </c>
-      <c r="F567" s="6"/>
-    </row>
-    <row r="568" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B568" s="1" t="s">
-        <v>1581</v>
-      </c>
-      <c r="D568" s="1" t="s">
-        <v>1583</v>
-      </c>
-      <c r="E568" s="1" t="s">
-        <v>1585</v>
-      </c>
-      <c r="F568" s="6" t="s">
-        <v>1584</v>
       </c>
     </row>
     <row r="569" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A569" s="3" t="s">
-        <v>1410</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="570" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B570" s="1" t="s">
-        <v>1408</v>
+        <v>1490</v>
       </c>
       <c r="D570" s="1" t="s">
-        <v>1409</v>
+        <v>1491</v>
       </c>
       <c r="E570" s="1" t="s">
-        <v>767</v>
-      </c>
-      <c r="F570" s="1" t="s">
-        <v>1407</v>
+        <v>1493</v>
+      </c>
+      <c r="F570" s="6" t="s">
+        <v>1492</v>
       </c>
     </row>
     <row r="571" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A571" s="3" t="s">
-        <v>1498</v>
-      </c>
+        <v>1582</v>
+      </c>
+      <c r="F571" s="6"/>
     </row>
     <row r="572" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B572" s="1" t="s">
-        <v>1497</v>
+        <v>1581</v>
       </c>
       <c r="D572" s="1" t="s">
-        <v>1499</v>
+        <v>1583</v>
       </c>
       <c r="E572" s="1" t="s">
-        <v>1481</v>
+        <v>1585</v>
       </c>
       <c r="F572" s="6" t="s">
-        <v>1500</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="573" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A573" s="3" t="s">
-        <v>1424</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="574" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B574" s="1" t="s">
-        <v>1426</v>
+        <v>1408</v>
       </c>
       <c r="D574" s="1" t="s">
-        <v>1427</v>
+        <v>1409</v>
       </c>
       <c r="E574" s="1" t="s">
-        <v>1428</v>
-      </c>
-      <c r="F574" s="6" t="s">
-        <v>1425</v>
+        <v>767</v>
+      </c>
+      <c r="F574" s="1" t="s">
+        <v>1407</v>
       </c>
     </row>
     <row r="575" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A575" s="3" t="s">
-        <v>1431</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="576" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B576" s="1" t="s">
-        <v>1432</v>
+        <v>1497</v>
       </c>
       <c r="D576" s="1" t="s">
-        <v>1433</v>
+        <v>1499</v>
       </c>
       <c r="E576" s="1" t="s">
-        <v>1502</v>
+        <v>1481</v>
       </c>
       <c r="F576" s="6" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="577" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A577" s="3" t="s">
-        <v>1464</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="578" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B578" s="1" t="s">
-        <v>1465</v>
+        <v>1426</v>
       </c>
       <c r="D578" s="1" t="s">
-        <v>1466</v>
+        <v>1427</v>
       </c>
       <c r="E578" s="1" t="s">
-        <v>1468</v>
+        <v>1428</v>
       </c>
       <c r="F578" s="6" t="s">
-        <v>1467</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="579" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A579" s="3" t="s">
-        <v>1458</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="580" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B580" s="1" t="s">
-        <v>1459</v>
+        <v>1432</v>
       </c>
       <c r="D580" s="1" t="s">
-        <v>1460</v>
+        <v>1433</v>
       </c>
       <c r="E580" s="1" t="s">
-        <v>1462</v>
+        <v>1502</v>
       </c>
       <c r="F580" s="6" t="s">
-        <v>1461</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="581" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A581" s="3" t="s">
-        <v>1567</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="582" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B582" s="1" t="s">
+        <v>1465</v>
+      </c>
+      <c r="D582" s="1" t="s">
+        <v>1466</v>
+      </c>
+      <c r="E582" s="1" t="s">
+        <v>1468</v>
+      </c>
+      <c r="F582" s="6" t="s">
+        <v>1467</v>
+      </c>
+    </row>
+    <row r="583" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A583" s="3" t="s">
+        <v>1610</v>
+      </c>
+    </row>
+    <row r="584" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B584" s="1" t="s">
+        <v>1611</v>
+      </c>
+      <c r="D584" s="1" t="s">
+        <v>1612</v>
+      </c>
+      <c r="E584" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F584" s="6" t="s">
+        <v>1613</v>
+      </c>
+    </row>
+    <row r="585" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A585" s="3" t="s">
+        <v>1614</v>
+      </c>
+    </row>
+    <row r="586" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B586" s="1" t="s">
+        <v>1615</v>
+      </c>
+      <c r="D586" s="1" t="s">
+        <v>1616</v>
+      </c>
+      <c r="E586" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F586" s="6" t="s">
+        <v>1617</v>
+      </c>
+    </row>
+    <row r="587" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A587" s="3" t="s">
+        <v>1458</v>
+      </c>
+    </row>
+    <row r="588" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B588" s="1" t="s">
+        <v>1459</v>
+      </c>
+      <c r="D588" s="1" t="s">
+        <v>1460</v>
+      </c>
+      <c r="E588" s="1" t="s">
+        <v>1462</v>
+      </c>
+      <c r="F588" s="6" t="s">
+        <v>1461</v>
+      </c>
+    </row>
+    <row r="589" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A589" s="3" t="s">
+        <v>1567</v>
+      </c>
+    </row>
+    <row r="590" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B590" s="1" t="s">
         <v>1568</v>
       </c>
-      <c r="D582" s="1" t="s">
+      <c r="D590" s="1" t="s">
         <v>1571</v>
       </c>
-      <c r="E582" s="1" t="s">
+      <c r="E590" s="1" t="s">
         <v>1570</v>
       </c>
-      <c r="F582" s="6" t="s">
+      <c r="F590" s="6" t="s">
         <v>1569</v>
       </c>
     </row>

--- a/Luban/Config/Datas/#BattleMomentEffectConfig.xlsx
+++ b/Luban/Config/Datas/#BattleMomentEffectConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F402AAB-E400-4E15-B4E2-8F2E7B169AEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E509DBB-2766-4F79-9443-EDD8EDF6B76F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>

--- a/Luban/Config/Datas/#BattleMomentEffectConfig.xlsx
+++ b/Luban/Config/Datas/#BattleMomentEffectConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF30A20C-DAD7-4A65-AA5E-1A8F89CC52A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F1A2F74-568B-4A2E-8CDF-D5F0ADDA69F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1885" uniqueCount="1426">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1874" uniqueCount="1417">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2320,42 +2320,6 @@
   </si>
   <si>
     <t>自己获取50%力的护体</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>伤害减免</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>109001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1,22001,0.5,3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>自己，伤害减免百分比，0.5，招式</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1,22001,-0.5,3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>自己，伤害减免百分比，-0.5，招式</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>109002</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>免伤增加50%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>免伤增加-50%</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -6034,7 +5998,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4CF470-E9E0-44FF-BA6C-71B5C42FB7B2}">
-  <dimension ref="A1:I513"/>
+  <dimension ref="A1:I510"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="29.75" style="1" customWidth="1"/>
@@ -6236,177 +6200,177 @@
     </row>
     <row r="13" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B13" s="1" t="s">
-        <v>644</v>
+        <v>635</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>635</v>
+        <v>626</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>638</v>
+        <v>629</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>643</v>
+        <v>634</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
-        <v>634</v>
+        <v>625</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>636</v>
+        <v>627</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>639</v>
+        <v>630</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>642</v>
+        <v>633</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B15" s="1" t="s">
-        <v>737</v>
+        <v>728</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>637</v>
+        <v>628</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>640</v>
+        <v>631</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>641</v>
+        <v>632</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
-        <v>738</v>
+        <v>729</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>739</v>
+        <v>730</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>740</v>
+        <v>731</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>741</v>
+        <v>732</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B17" s="1" t="s">
-        <v>758</v>
+        <v>749</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>759</v>
+        <v>750</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>760</v>
+        <v>751</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>761</v>
+        <v>752</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B18" s="1" t="s">
-        <v>799</v>
+        <v>790</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>800</v>
+        <v>791</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>801</v>
+        <v>792</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>802</v>
+        <v>793</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
-        <v>980</v>
+        <v>971</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>981</v>
+        <v>972</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>982</v>
+        <v>973</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>983</v>
+        <v>974</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B20" s="1" t="s">
-        <v>1052</v>
+        <v>1043</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>762</v>
+        <v>753</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>763</v>
+        <v>754</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>764</v>
+        <v>755</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B21" s="1" t="s">
-        <v>1053</v>
+        <v>1044</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>1003</v>
+        <v>994</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>1004</v>
+        <v>995</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>1005</v>
+        <v>996</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B22" s="1" t="s">
-        <v>1054</v>
+        <v>1045</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>1049</v>
+        <v>1040</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>1050</v>
+        <v>1041</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>1051</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B23" s="1" t="s">
-        <v>1055</v>
+        <v>1046</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>506</v>
@@ -6423,36 +6387,36 @@
     </row>
     <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B24" s="1" t="s">
-        <v>1171</v>
+        <v>1162</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>1172</v>
+        <v>1163</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>1167</v>
+        <v>1158</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>1173</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B25" s="1" t="s">
-        <v>1175</v>
+        <v>1166</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>1176</v>
+        <v>1167</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>1177</v>
+        <v>1168</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>1178</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.2">
@@ -6616,155 +6580,155 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B36" s="1" t="s">
-        <v>841</v>
+        <v>832</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>835</v>
+        <v>826</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>837</v>
+        <v>828</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>839</v>
+        <v>830</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
-        <v>842</v>
+        <v>833</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>836</v>
+        <v>827</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>838</v>
+        <v>829</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>840</v>
+        <v>831</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B38" s="1" t="s">
-        <v>903</v>
+        <v>894</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>904</v>
+        <v>895</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>905</v>
+        <v>896</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>906</v>
+        <v>897</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B39" s="1" t="s">
-        <v>913</v>
+        <v>904</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>914</v>
+        <v>905</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>915</v>
+        <v>906</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>916</v>
+        <v>907</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B40" s="1" t="s">
-        <v>987</v>
+        <v>978</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>988</v>
+        <v>979</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>989</v>
+        <v>980</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>990</v>
+        <v>981</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B41" s="1" t="s">
-        <v>1006</v>
+        <v>997</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>1007</v>
+        <v>998</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>1008</v>
+        <v>999</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>1009</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B42" s="1" t="s">
-        <v>1056</v>
+        <v>1047</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>795</v>
+        <v>786</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>789</v>
+        <v>780</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>790</v>
+        <v>781</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B43" s="1" t="s">
-        <v>1057</v>
+        <v>1048</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>1058</v>
+        <v>1049</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>1060</v>
+        <v>1051</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>1059</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B44" s="1" t="s">
-        <v>1179</v>
+        <v>1170</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>1180</v>
+        <v>1171</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>1181</v>
+        <v>1172</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>1182</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.2">
@@ -6898,10 +6862,10 @@
         <v>368</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>1167</v>
+        <v>1158</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>1168</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.2">
@@ -6924,41 +6888,41 @@
         <v>202</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>1168</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B57" s="1" t="s">
-        <v>1170</v>
+        <v>1161</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>1166</v>
+        <v>1157</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>368</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>915</v>
+        <v>906</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>1169</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B58" s="1" t="s">
-        <v>1354</v>
+        <v>1345</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>1355</v>
+        <v>1346</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>368</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>1356</v>
+        <v>1347</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>1357</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.2">
@@ -6986,36 +6950,36 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B61" s="1" t="s">
-        <v>1120</v>
+        <v>1111</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>1121</v>
+        <v>1112</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>1122</v>
+        <v>1113</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>1123</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B62" s="1" t="s">
-        <v>1248</v>
+        <v>1239</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>1249</v>
+        <v>1240</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>1423</v>
+        <v>1414</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>1250</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.2">
@@ -7043,662 +7007,673 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A65" s="4" t="s">
-        <v>600</v>
+        <v>762</v>
       </c>
       <c r="E65" s="2"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B66" s="1" t="s">
-        <v>601</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>607</v>
+        <v>1341</v>
+      </c>
+      <c r="C66" s="6" t="s">
+        <v>717</v>
       </c>
       <c r="D66" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>602</v>
+        <v>782</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>603</v>
+        <v>785</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B67" s="1" t="s">
-        <v>606</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>608</v>
+        <v>1342</v>
+      </c>
+      <c r="C67" s="6" t="s">
+        <v>718</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>604</v>
+        <v>783</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>605</v>
+        <v>784</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A68" s="4" t="s">
-        <v>771</v>
+        <v>1061</v>
       </c>
       <c r="E68" s="2"/>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B69" s="1" t="s">
-        <v>1350</v>
-      </c>
-      <c r="C69" s="6" t="s">
-        <v>726</v>
+        <v>1343</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>1062</v>
       </c>
       <c r="D69" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>791</v>
+        <v>1063</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>794</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B70" s="1" t="s">
-        <v>1351</v>
-      </c>
-      <c r="C70" s="6" t="s">
-        <v>727</v>
-      </c>
-      <c r="D70" s="1" t="s">
+      <c r="A70" s="4" t="s">
+        <v>1065</v>
+      </c>
+      <c r="E70" s="2"/>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B71" s="1" t="s">
+        <v>1344</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>1066</v>
+      </c>
+      <c r="D71" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E70" s="2" t="s">
-        <v>792</v>
-      </c>
-      <c r="F70" s="1" t="s">
-        <v>793</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A71" s="4" t="s">
-        <v>1070</v>
-      </c>
-      <c r="E71" s="2"/>
+      <c r="E71" s="2" t="s">
+        <v>1068</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>1067</v>
+      </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B72" s="1" t="s">
-        <v>1352</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>1071</v>
-      </c>
-      <c r="D72" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E72" s="2" t="s">
-        <v>1072</v>
-      </c>
-      <c r="F72" s="1" t="s">
-        <v>1073</v>
-      </c>
+      <c r="A72" s="3" t="s">
+        <v>1205</v>
+      </c>
+      <c r="E72" s="2"/>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A73" s="4" t="s">
-        <v>1074</v>
-      </c>
-      <c r="E73" s="2"/>
+      <c r="B73" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>1203</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>1206</v>
+      </c>
+      <c r="F73" s="6" t="s">
+        <v>1207</v>
+      </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B74" s="1" t="s">
-        <v>1353</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>1075</v>
+        <v>1204</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>10</v>
+        <v>1203</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>1077</v>
-      </c>
-      <c r="F74" s="1" t="s">
-        <v>1076</v>
+        <v>1208</v>
+      </c>
+      <c r="F74" s="6" t="s">
+        <v>1209</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A75" s="3" t="s">
-        <v>1214</v>
-      </c>
-      <c r="E75" s="2"/>
+      <c r="B75" s="1" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>1203</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>1253</v>
+      </c>
+      <c r="F75" s="6" t="s">
+        <v>1254</v>
+      </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B76" s="1" t="s">
-        <v>65</v>
+        <v>1260</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>1212</v>
+        <v>1203</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>1215</v>
+        <v>1261</v>
       </c>
       <c r="F76" s="6" t="s">
-        <v>1216</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B77" s="1" t="s">
-        <v>1213</v>
+        <v>1263</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>1212</v>
+        <v>1203</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>1217</v>
+        <v>1264</v>
       </c>
       <c r="F77" s="6" t="s">
-        <v>1218</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B78" s="1" t="s">
-        <v>1261</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>1212</v>
-      </c>
-      <c r="E78" s="2" t="s">
-        <v>1262</v>
-      </c>
-      <c r="F78" s="6" t="s">
-        <v>1263</v>
-      </c>
+      <c r="A78" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E78" s="2"/>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
-        <v>1269</v>
+        <v>66</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>1212</v>
-      </c>
-      <c r="E79" s="2" t="s">
-        <v>1270</v>
-      </c>
-      <c r="F79" s="6" t="s">
-        <v>1271</v>
+        <v>56</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>1144</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B80" s="1" t="s">
-        <v>1272</v>
-      </c>
-      <c r="D80" s="1" t="s">
-        <v>1212</v>
-      </c>
-      <c r="E80" s="2" t="s">
-        <v>1273</v>
-      </c>
-      <c r="F80" s="6" t="s">
-        <v>1274</v>
-      </c>
-    </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A81" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="E81" s="2"/>
-    </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A80" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="E80" s="2"/>
+    </row>
+    <row r="81" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B81" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>1386</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="I81" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="82" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B82" s="1" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>28</v>
+        <v>1387</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>1153</v>
-      </c>
-    </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A83" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="E83" s="2"/>
-    </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.2">
+        <v>103</v>
+      </c>
+      <c r="I82" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="83" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B83" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>1388</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="84" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B84" s="1" t="s">
-        <v>67</v>
+        <v>1165</v>
       </c>
       <c r="D84" s="1" t="s">
         <v>27</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>1395</v>
+        <v>1389</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="I84" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.2">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="85" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B85" s="1" t="s">
-        <v>86</v>
+        <v>358</v>
       </c>
       <c r="D85" s="1" t="s">
         <v>27</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>1396</v>
+        <v>1390</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="I85" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.2">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="86" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B86" s="1" t="s">
-        <v>112</v>
+        <v>276</v>
       </c>
       <c r="D86" s="1" t="s">
         <v>27</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>1397</v>
+        <v>1391</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.2">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="87" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B87" s="1" t="s">
-        <v>1174</v>
+        <v>1032</v>
       </c>
       <c r="D87" s="1" t="s">
         <v>27</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>1398</v>
+        <v>1392</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.2">
+        <v>1033</v>
+      </c>
+    </row>
+    <row r="88" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B88" s="1" t="s">
-        <v>358</v>
+        <v>95</v>
       </c>
       <c r="D88" s="1" t="s">
         <v>27</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>1399</v>
+        <v>1393</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.2">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="89" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B89" s="1" t="s">
-        <v>276</v>
+        <v>87</v>
       </c>
       <c r="D89" s="1" t="s">
         <v>27</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>1400</v>
+        <v>1394</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.2">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="90" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B90" s="1" t="s">
-        <v>1041</v>
+        <v>96</v>
       </c>
       <c r="D90" s="1" t="s">
         <v>27</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>1401</v>
+        <v>1395</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>1042</v>
-      </c>
-    </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.2">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="91" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B91" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D91" s="1" t="s">
         <v>27</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>1402</v>
+        <v>1396</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.2">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="92" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B92" s="1" t="s">
-        <v>87</v>
+        <v>268</v>
       </c>
       <c r="D92" s="1" t="s">
         <v>27</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>1403</v>
+        <v>1397</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.2">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="93" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B93" s="1" t="s">
-        <v>96</v>
+        <v>269</v>
       </c>
       <c r="D93" s="1" t="s">
         <v>27</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>1404</v>
+        <v>1398</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.2">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="94" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B94" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D94" s="1" t="s">
         <v>27</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>1405</v>
+        <v>1399</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+      <c r="I94" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="95" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B95" s="1" t="s">
-        <v>268</v>
+        <v>99</v>
       </c>
       <c r="D95" s="1" t="s">
         <v>27</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>1406</v>
+        <v>1400</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.2">
+        <v>109</v>
+      </c>
+      <c r="I95" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="96" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B96" s="1" t="s">
-        <v>269</v>
+        <v>100</v>
       </c>
       <c r="D96" s="1" t="s">
         <v>27</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>1407</v>
+        <v>1401</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="97" spans="2:9" x14ac:dyDescent="0.2">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B97" s="1" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D97" s="1" t="s">
         <v>27</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>1408</v>
+        <v>1402</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="I97" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="98" spans="2:9" x14ac:dyDescent="0.2">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B98" s="1" t="s">
-        <v>99</v>
+        <v>270</v>
       </c>
       <c r="D98" s="1" t="s">
         <v>27</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>1409</v>
+        <v>1403</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="I98" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="99" spans="2:9" x14ac:dyDescent="0.2">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B99" s="1" t="s">
-        <v>100</v>
+        <v>271</v>
       </c>
       <c r="D99" s="1" t="s">
         <v>27</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>1410</v>
+        <v>1404</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="100" spans="2:9" x14ac:dyDescent="0.2">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B100" s="1" t="s">
-        <v>101</v>
+        <v>1004</v>
       </c>
       <c r="D100" s="1" t="s">
         <v>27</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>1411</v>
+        <v>1405</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="101" spans="2:9" x14ac:dyDescent="0.2">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B101" s="1" t="s">
-        <v>270</v>
+        <v>1005</v>
       </c>
       <c r="D101" s="1" t="s">
         <v>27</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>1412</v>
+        <v>1406</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="102" spans="2:9" x14ac:dyDescent="0.2">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B102" s="1" t="s">
-        <v>271</v>
+        <v>1006</v>
       </c>
       <c r="D102" s="1" t="s">
         <v>27</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>1413</v>
+        <v>1407</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="103" spans="2:9" x14ac:dyDescent="0.2">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B103" s="1" t="s">
-        <v>1013</v>
+        <v>1007</v>
       </c>
       <c r="D103" s="1" t="s">
         <v>27</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>1414</v>
+        <v>1408</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>1021</v>
-      </c>
-    </row>
-    <row r="104" spans="2:9" x14ac:dyDescent="0.2">
+        <v>1015</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B104" s="1" t="s">
-        <v>1014</v>
+        <v>1008</v>
       </c>
       <c r="D104" s="1" t="s">
         <v>27</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>1415</v>
+        <v>1409</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>1022</v>
-      </c>
-    </row>
-    <row r="105" spans="2:9" x14ac:dyDescent="0.2">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B105" s="1" t="s">
-        <v>1015</v>
+        <v>1009</v>
       </c>
       <c r="D105" s="1" t="s">
         <v>27</v>
       </c>
       <c r="E105" s="1" t="s">
+        <v>1410</v>
+      </c>
+      <c r="F105" s="1" t="s">
+        <v>1017</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B107" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E107" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F107" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="I107" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B108" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E108" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F108" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="I108" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B109" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E109" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="F109" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="I109" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A110" s="3" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B111" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E111" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F111" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="I111" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B112" s="1" t="s">
         <v>1416</v>
       </c>
-      <c r="F105" s="1" t="s">
-        <v>1023</v>
-      </c>
-    </row>
-    <row r="106" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B106" s="1" t="s">
-        <v>1016</v>
-      </c>
-      <c r="D106" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E106" s="1" t="s">
-        <v>1417</v>
-      </c>
-      <c r="F106" s="1" t="s">
-        <v>1024</v>
-      </c>
-    </row>
-    <row r="107" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B107" s="1" t="s">
-        <v>1017</v>
-      </c>
-      <c r="D107" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E107" s="1" t="s">
-        <v>1418</v>
-      </c>
-      <c r="F107" s="1" t="s">
-        <v>1025</v>
-      </c>
-    </row>
-    <row r="108" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B108" s="1" t="s">
-        <v>1018</v>
-      </c>
-      <c r="D108" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E108" s="1" t="s">
-        <v>1419</v>
-      </c>
-      <c r="F108" s="1" t="s">
-        <v>1026</v>
-      </c>
-    </row>
-    <row r="110" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B110" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="D110" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E110" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F110" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="I110" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="111" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B111" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="D111" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E111" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="F111" s="1" t="s">
-        <v>479</v>
-      </c>
-      <c r="I111" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="112" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B112" s="1" t="s">
-        <v>117</v>
-      </c>
       <c r="D112" s="1" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>119</v>
+        <v>20</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>120</v>
+        <v>290</v>
       </c>
       <c r="I112" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A113" s="3" t="s">
-        <v>283</v>
+      <c r="B113" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E113" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="F113" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="I113" s="1" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B114" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D114" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>57</v>
+        <v>288</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="I114" s="1" t="s">
         <v>37</v>
@@ -7706,1700 +7681,1691 @@
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B115" s="1" t="s">
-        <v>1425</v>
+        <v>295</v>
       </c>
       <c r="D115" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>20</v>
+        <v>289</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="I115" s="1" t="s">
-        <v>37</v>
+        <v>293</v>
       </c>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B116" s="1" t="s">
-        <v>284</v>
+        <v>1055</v>
       </c>
       <c r="D116" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>287</v>
+        <v>84</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="I116" s="1" t="s">
-        <v>37</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B117" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="D117" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E117" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="F117" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="I117" s="1" t="s">
-        <v>37</v>
+      <c r="A117" s="3" t="s">
+        <v>321</v>
       </c>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B118" s="1" t="s">
-        <v>295</v>
+        <v>69</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>289</v>
+        <v>18</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>293</v>
+        <v>46</v>
+      </c>
+      <c r="I118" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B119" s="1" t="s">
-        <v>1064</v>
+        <v>323</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>84</v>
+        <v>118</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>1065</v>
+        <v>324</v>
+      </c>
+      <c r="I119" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A120" s="3" t="s">
-        <v>321</v>
+      <c r="B120" s="1" t="s">
+        <v>662</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E120" s="1" t="s">
+        <v>663</v>
+      </c>
+      <c r="F120" s="1" t="s">
+        <v>664</v>
       </c>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B121" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="D121" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E121" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F121" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="I121" s="1" t="s">
-        <v>47</v>
+      <c r="A121" s="3" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B122" s="1" t="s">
-        <v>323</v>
+        <v>70</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>118</v>
+        <v>20</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="I122" s="1" t="s">
-        <v>47</v>
+        <v>322</v>
       </c>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B123" s="1" t="s">
-        <v>671</v>
+        <v>325</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>672</v>
+        <v>287</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>673</v>
+        <v>331</v>
       </c>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A124" s="3" t="s">
-        <v>52</v>
+      <c r="B124" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E124" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="F124" s="1" t="s">
+        <v>332</v>
       </c>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B125" s="1" t="s">
-        <v>70</v>
+        <v>327</v>
       </c>
       <c r="D125" s="1" t="s">
         <v>51</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>20</v>
+        <v>289</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>322</v>
+        <v>333</v>
       </c>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B126" s="1" t="s">
-        <v>325</v>
+        <v>1415</v>
       </c>
       <c r="D126" s="1" t="s">
         <v>51</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>287</v>
+        <v>330</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B127" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="D127" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="E127" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="F127" s="1" t="s">
-        <v>332</v>
+      <c r="A127" s="3" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B128" s="1" t="s">
-        <v>327</v>
+        <v>352</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>289</v>
+        <v>57</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B129" s="1" t="s">
-        <v>1424</v>
+        <v>353</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>330</v>
+        <v>20</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A130" s="3" t="s">
-        <v>114</v>
+      <c r="B130" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E130" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F130" s="1" t="s">
+        <v>338</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B131" s="1" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="D131" s="1" t="s">
         <v>53</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>57</v>
+        <v>288</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>329</v>
+        <v>340</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B132" s="1" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="D132" s="1" t="s">
         <v>53</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>20</v>
+        <v>289</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>335</v>
+        <v>344</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B133" s="1" t="s">
-        <v>354</v>
+        <v>1288</v>
       </c>
       <c r="D133" s="1" t="s">
         <v>53</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>50</v>
+        <v>330</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>338</v>
+        <v>349</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B134" s="1" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="D134" s="1" t="s">
         <v>53</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>288</v>
+        <v>341</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>340</v>
+        <v>351</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B135" s="1" t="s">
-        <v>337</v>
+        <v>1060</v>
       </c>
       <c r="D135" s="1" t="s">
         <v>53</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>289</v>
+        <v>343</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>344</v>
+        <v>328</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B136" s="1" t="s">
-        <v>1297</v>
+        <v>342</v>
       </c>
       <c r="D136" s="1" t="s">
         <v>53</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>330</v>
+        <v>346</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B137" s="1" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="D137" s="1" t="s">
         <v>53</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B138" s="1" t="s">
-        <v>1069</v>
+        <v>347</v>
       </c>
       <c r="D138" s="1" t="s">
         <v>53</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B139" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="D139" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="E139" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="F139" s="1" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B140" s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="D140" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="E140" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="F140" s="1" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B141" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="D141" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="E141" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="F141" s="1" t="s">
         <v>357</v>
       </c>
     </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A142" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B143" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D143" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E143" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F143" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A144" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="C144" s="2"/>
+      <c r="D144" s="2"/>
+      <c r="E144" s="2"/>
+    </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A145" s="3" t="s">
-        <v>63</v>
+      <c r="B145" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C145" s="2"/>
+      <c r="D145" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E145" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F145" s="2" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B146" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="D146" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="E146" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="F146" s="1" t="s">
-        <v>63</v>
+        <v>480</v>
+      </c>
+      <c r="D146" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E146" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F146" s="2" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A147" s="3" t="s">
-        <v>208</v>
+      <c r="B147" s="1" t="s">
+        <v>204</v>
       </c>
       <c r="C147" s="2"/>
-      <c r="D147" s="2"/>
-      <c r="E147" s="2"/>
+      <c r="D147" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E147" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F147" s="2" t="s">
+        <v>217</v>
+      </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B148" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" s="2" t="s">
         <v>40</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>20</v>
+        <v>84</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B149" s="1" t="s">
-        <v>480</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="C149" s="2"/>
       <c r="D149" s="2" t="s">
         <v>40</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B150" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="C150" s="2"/>
+        <v>207</v>
+      </c>
       <c r="D150" s="2" t="s">
         <v>40</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>41</v>
+        <v>85</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B151" s="1" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B152" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="C152" s="2"/>
+        <v>210</v>
+      </c>
       <c r="D152" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B153" s="1" t="s">
-        <v>207</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="C153" s="2"/>
       <c r="D153" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>85</v>
+        <v>41</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B154" s="1" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" s="2" t="s">
         <v>43</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>20</v>
+        <v>84</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B155" s="1" t="s">
-        <v>210</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="C155" s="2"/>
       <c r="D155" s="2" t="s">
         <v>43</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B156" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="C156" s="2"/>
+        <v>214</v>
+      </c>
       <c r="D156" s="2" t="s">
         <v>43</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>41</v>
+        <v>85</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B157" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="C157" s="2"/>
-      <c r="D157" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E157" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="F157" s="2" t="s">
-        <v>224</v>
-      </c>
+      <c r="A157" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D157" s="2"/>
+      <c r="E157" s="2"/>
+      <c r="F157" s="2"/>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B158" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="C158" s="2"/>
-      <c r="D158" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E158" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F158" s="2" t="s">
-        <v>225</v>
+        <v>72</v>
+      </c>
+      <c r="D158" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E158" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F158" s="1" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B159" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="D159" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E159" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="F159" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
+      </c>
+      <c r="D159" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E159" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F159" s="1" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A160" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D160" s="2"/>
-      <c r="E160" s="2"/>
-      <c r="F160" s="2"/>
+      <c r="B160" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="D160" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E160" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F160" s="1" t="s">
+        <v>232</v>
+      </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B161" s="1" t="s">
-        <v>72</v>
+        <v>230</v>
       </c>
       <c r="D161" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B162" s="1" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="D162" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B163" s="1" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="D163" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>232</v>
+        <v>243</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B164" s="1" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="D164" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B165" s="1" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="D165" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>41</v>
+        <v>91</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B166" s="1" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="D166" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>89</v>
+        <v>42</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B167" s="1" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="D167" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B168" s="1" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="D168" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B169" s="1" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="D169" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>42</v>
+        <v>94</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B170" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="D170" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E170" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="F170" s="1" t="s">
-        <v>247</v>
+      <c r="A170" s="3" t="s">
+        <v>639</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B171" s="1" t="s">
-        <v>240</v>
+        <v>73</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>93</v>
+        <v>747</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>248</v>
+        <v>637</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B172" s="1" t="s">
-        <v>241</v>
+        <v>837</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>94</v>
+        <v>640</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>249</v>
+        <v>834</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A173" s="3" t="s">
-        <v>648</v>
+      <c r="B173" s="1" t="s">
+        <v>838</v>
+      </c>
+      <c r="D173" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E173" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="F173" s="1" t="s">
+        <v>835</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B174" s="1" t="s">
-        <v>73</v>
+        <v>839</v>
       </c>
       <c r="D174" s="1" t="s">
         <v>48</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>756</v>
+        <v>642</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>646</v>
+        <v>836</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B175" s="1" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="D175" s="1" t="s">
         <v>48</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>649</v>
+        <v>723</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B176" s="1" t="s">
-        <v>847</v>
+        <v>863</v>
       </c>
       <c r="D176" s="1" t="s">
         <v>48</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>650</v>
+        <v>864</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>844</v>
+        <v>865</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B177" s="1" t="s">
-        <v>848</v>
-      </c>
-      <c r="D177" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E177" s="1" t="s">
-        <v>651</v>
-      </c>
-      <c r="F177" s="1" t="s">
-        <v>845</v>
+      <c r="A177" s="3" t="s">
+        <v>638</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B178" s="1" t="s">
-        <v>854</v>
+        <v>74</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>732</v>
+        <v>640</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>855</v>
+        <v>636</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B179" s="1" t="s">
-        <v>872</v>
+        <v>964</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>873</v>
+        <v>641</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>874</v>
+        <v>643</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A180" s="3" t="s">
-        <v>647</v>
+      <c r="B180" s="1" t="s">
+        <v>733</v>
+      </c>
+      <c r="D180" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E180" s="1" t="s">
+        <v>642</v>
+      </c>
+      <c r="F180" s="1" t="s">
+        <v>644</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B181" s="1" t="s">
-        <v>74</v>
+        <v>713</v>
       </c>
       <c r="D181" s="1" t="s">
         <v>49</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>649</v>
+        <v>711</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>645</v>
+        <v>712</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B182" s="1" t="s">
-        <v>973</v>
+        <v>722</v>
       </c>
       <c r="D182" s="1" t="s">
         <v>49</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>650</v>
+        <v>723</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>652</v>
+        <v>724</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B183" s="1" t="s">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="D183" s="1" t="s">
         <v>49</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>651</v>
+        <v>747</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>653</v>
+        <v>748</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B184" s="1" t="s">
-        <v>722</v>
+        <v>767</v>
       </c>
       <c r="D184" s="1" t="s">
         <v>49</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>720</v>
+        <v>768</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>721</v>
+        <v>769</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B185" s="1" t="s">
-        <v>731</v>
+        <v>807</v>
       </c>
       <c r="D185" s="1" t="s">
         <v>49</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>732</v>
+        <v>805</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>733</v>
+        <v>806</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B186" s="1" t="s">
-        <v>755</v>
+        <v>920</v>
       </c>
       <c r="D186" s="1" t="s">
         <v>49</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>756</v>
+        <v>864</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>757</v>
-      </c>
-    </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B187" s="1" t="s">
-        <v>776</v>
-      </c>
-      <c r="D187" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E187" s="1" t="s">
-        <v>777</v>
-      </c>
-      <c r="F187" s="1" t="s">
-        <v>778</v>
+        <v>921</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B188" s="1" t="s">
-        <v>816</v>
+        <v>75</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>814</v>
+        <v>18</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>815</v>
+        <v>17</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B189" s="1" t="s">
-        <v>929</v>
-      </c>
-      <c r="D189" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E189" s="1" t="s">
-        <v>873</v>
-      </c>
-      <c r="F189" s="1" t="s">
-        <v>930</v>
+      <c r="A189" s="3" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B190" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="D190" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E190" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="F190" s="1" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B191" s="1" t="s">
-        <v>75</v>
+        <v>467</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>18</v>
+        <v>401</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>17</v>
+        <v>376</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A192" s="3" t="s">
-        <v>148</v>
+      <c r="B192" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="D192" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E192" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="F192" s="1" t="s">
+        <v>377</v>
       </c>
     </row>
     <row r="193" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B193" s="1" t="s">
-        <v>373</v>
+        <v>1087</v>
       </c>
       <c r="D193" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>400</v>
+        <v>1089</v>
       </c>
       <c r="F193" s="1" t="s">
-        <v>375</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="194" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B194" s="1" t="s">
-        <v>467</v>
+        <v>515</v>
       </c>
       <c r="D194" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>401</v>
+        <v>516</v>
       </c>
       <c r="F194" s="1" t="s">
-        <v>376</v>
+        <v>517</v>
       </c>
     </row>
     <row r="195" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B195" s="1" t="s">
-        <v>472</v>
+        <v>1099</v>
       </c>
       <c r="D195" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>402</v>
+        <v>1100</v>
       </c>
       <c r="F195" s="1" t="s">
-        <v>377</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="196" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B196" s="1" t="s">
-        <v>1096</v>
+        <v>439</v>
       </c>
       <c r="D196" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>1098</v>
+        <v>438</v>
       </c>
       <c r="F196" s="1" t="s">
-        <v>1097</v>
+        <v>403</v>
       </c>
     </row>
     <row r="197" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B197" s="1" t="s">
-        <v>515</v>
+        <v>820</v>
       </c>
       <c r="D197" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>516</v>
+        <v>822</v>
       </c>
       <c r="F197" s="1" t="s">
-        <v>517</v>
+        <v>821</v>
       </c>
     </row>
     <row r="198" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B198" s="1" t="s">
-        <v>1108</v>
+        <v>928</v>
       </c>
       <c r="D198" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>1109</v>
+        <v>929</v>
       </c>
       <c r="F198" s="1" t="s">
-        <v>1110</v>
+        <v>930</v>
       </c>
     </row>
     <row r="199" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B199" s="1" t="s">
-        <v>439</v>
+        <v>576</v>
       </c>
       <c r="D199" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>438</v>
+        <v>574</v>
       </c>
       <c r="F199" s="1" t="s">
-        <v>403</v>
+        <v>575</v>
       </c>
     </row>
     <row r="200" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B200" s="1" t="s">
-        <v>829</v>
+        <v>440</v>
       </c>
       <c r="D200" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>831</v>
+        <v>404</v>
       </c>
       <c r="F200" s="1" t="s">
-        <v>830</v>
+        <v>378</v>
       </c>
     </row>
     <row r="201" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B201" s="1" t="s">
-        <v>937</v>
+        <v>441</v>
       </c>
       <c r="D201" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>938</v>
+        <v>405</v>
       </c>
       <c r="F201" s="1" t="s">
-        <v>939</v>
+        <v>466</v>
       </c>
     </row>
     <row r="202" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B202" s="1" t="s">
-        <v>576</v>
+        <v>442</v>
       </c>
       <c r="D202" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>574</v>
+        <v>410</v>
       </c>
       <c r="F202" s="1" t="s">
-        <v>575</v>
+        <v>379</v>
       </c>
     </row>
     <row r="203" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B203" s="1" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="D203" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="F203" s="1" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="204" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B204" s="1" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="D204" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="F204" s="1" t="s">
-        <v>466</v>
+        <v>381</v>
       </c>
     </row>
     <row r="205" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B205" s="1" t="s">
-        <v>442</v>
+        <v>471</v>
       </c>
       <c r="D205" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="F205" s="1" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="206" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B206" s="1" t="s">
-        <v>443</v>
+        <v>474</v>
       </c>
       <c r="D206" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="F206" s="1" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="207" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B207" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D207" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="F207" s="1" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="208" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B208" s="1" t="s">
-        <v>471</v>
+        <v>446</v>
       </c>
       <c r="D208" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="F208" s="1" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="209" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B209" s="1" t="s">
-        <v>474</v>
+        <v>447</v>
       </c>
       <c r="D209" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="F209" s="1" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="210" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B210" s="1" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="D210" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="F210" s="1" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="211" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B211" s="1" t="s">
-        <v>446</v>
+        <v>468</v>
       </c>
       <c r="D211" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="F211" s="1" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="212" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B212" s="1" t="s">
-        <v>447</v>
+        <v>470</v>
       </c>
       <c r="D212" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="F212" s="1" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="213" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B213" s="1" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D213" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F213" s="1" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="214" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B214" s="1" t="s">
-        <v>468</v>
+        <v>1001</v>
       </c>
       <c r="D214" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>415</v>
+        <v>1002</v>
       </c>
       <c r="F214" s="1" t="s">
-        <v>388</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="215" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B215" s="1" t="s">
-        <v>470</v>
+        <v>450</v>
       </c>
       <c r="D215" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="F215" s="1" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="216" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B216" s="1" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="D216" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="F216" s="1" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="217" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B217" s="1" t="s">
-        <v>1010</v>
+        <v>469</v>
       </c>
       <c r="D217" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>1011</v>
+        <v>420</v>
       </c>
       <c r="F217" s="1" t="s">
-        <v>1012</v>
+        <v>393</v>
       </c>
     </row>
     <row r="218" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B218" s="1" t="s">
-        <v>450</v>
+        <v>594</v>
       </c>
       <c r="D218" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>418</v>
+        <v>595</v>
       </c>
       <c r="F218" s="1" t="s">
-        <v>391</v>
+        <v>596</v>
       </c>
     </row>
     <row r="219" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B219" s="1" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D219" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="F219" s="1" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="220" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B220" s="1" t="s">
-        <v>469</v>
+        <v>1102</v>
       </c>
       <c r="D220" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>420</v>
+        <v>1103</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>393</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="221" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B221" s="1" t="s">
-        <v>594</v>
+        <v>1084</v>
       </c>
       <c r="D221" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>595</v>
+        <v>1085</v>
       </c>
       <c r="F221" s="1" t="s">
-        <v>596</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="222" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B222" s="1" t="s">
-        <v>452</v>
+        <v>882</v>
       </c>
       <c r="D222" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E222" s="1" t="s">
-        <v>421</v>
+        <v>883</v>
       </c>
       <c r="F222" s="1" t="s">
-        <v>394</v>
+        <v>884</v>
       </c>
     </row>
     <row r="223" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B223" s="1" t="s">
-        <v>1111</v>
+        <v>453</v>
       </c>
       <c r="D223" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E223" s="1" t="s">
-        <v>1112</v>
+        <v>422</v>
       </c>
       <c r="F223" s="1" t="s">
-        <v>1113</v>
+        <v>395</v>
       </c>
     </row>
     <row r="224" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B224" s="1" t="s">
-        <v>1093</v>
+        <v>525</v>
       </c>
       <c r="D224" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>1094</v>
+        <v>527</v>
       </c>
       <c r="F224" s="1" t="s">
-        <v>1095</v>
+        <v>529</v>
       </c>
     </row>
     <row r="225" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B225" s="1" t="s">
-        <v>891</v>
+        <v>526</v>
       </c>
       <c r="D225" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>892</v>
+        <v>528</v>
       </c>
       <c r="F225" s="1" t="s">
-        <v>893</v>
+        <v>530</v>
       </c>
     </row>
     <row r="226" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B226" s="1" t="s">
-        <v>453</v>
+        <v>804</v>
       </c>
       <c r="D226" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>422</v>
+        <v>802</v>
       </c>
       <c r="F226" s="1" t="s">
-        <v>395</v>
+        <v>803</v>
       </c>
     </row>
     <row r="227" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B227" s="1" t="s">
-        <v>525</v>
+        <v>808</v>
       </c>
       <c r="D227" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E227" s="1" t="s">
-        <v>527</v>
+        <v>809</v>
       </c>
       <c r="F227" s="1" t="s">
-        <v>529</v>
+        <v>810</v>
       </c>
     </row>
     <row r="228" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B228" s="1" t="s">
-        <v>526</v>
+        <v>1090</v>
       </c>
       <c r="D228" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E228" s="1" t="s">
-        <v>528</v>
+        <v>1091</v>
       </c>
       <c r="F228" s="1" t="s">
-        <v>530</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="229" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B229" s="1" t="s">
-        <v>813</v>
+        <v>965</v>
       </c>
       <c r="D229" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E229" s="1" t="s">
-        <v>811</v>
+        <v>966</v>
       </c>
       <c r="F229" s="1" t="s">
-        <v>812</v>
+        <v>967</v>
       </c>
     </row>
     <row r="230" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B230" s="1" t="s">
-        <v>817</v>
+        <v>968</v>
       </c>
       <c r="D230" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>818</v>
+        <v>969</v>
       </c>
       <c r="F230" s="1" t="s">
-        <v>819</v>
+        <v>970</v>
       </c>
     </row>
     <row r="231" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B231" s="1" t="s">
-        <v>1099</v>
+        <v>1105</v>
       </c>
       <c r="D231" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E231" s="1" t="s">
-        <v>1100</v>
+        <v>1106</v>
       </c>
       <c r="F231" s="1" t="s">
-        <v>1101</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="232" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B232" s="1" t="s">
-        <v>974</v>
+        <v>853</v>
       </c>
       <c r="D232" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>975</v>
+        <v>854</v>
       </c>
       <c r="F232" s="1" t="s">
-        <v>976</v>
+        <v>855</v>
       </c>
     </row>
     <row r="233" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B233" s="1" t="s">
-        <v>977</v>
+        <v>1108</v>
       </c>
       <c r="D233" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>978</v>
+        <v>1109</v>
       </c>
       <c r="F233" s="1" t="s">
-        <v>979</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="234" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B234" s="1" t="s">
-        <v>1114</v>
+        <v>518</v>
       </c>
       <c r="D234" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>1115</v>
+        <v>519</v>
       </c>
       <c r="F234" s="1" t="s">
-        <v>1116</v>
+        <v>520</v>
       </c>
     </row>
     <row r="235" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B235" s="1" t="s">
-        <v>862</v>
+        <v>567</v>
       </c>
       <c r="D235" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E235" s="1" t="s">
-        <v>863</v>
+        <v>568</v>
       </c>
       <c r="F235" s="1" t="s">
-        <v>864</v>
+        <v>569</v>
       </c>
     </row>
     <row r="236" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B236" s="1" t="s">
-        <v>1117</v>
+        <v>914</v>
       </c>
       <c r="D236" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E236" s="1" t="s">
-        <v>1118</v>
+        <v>915</v>
       </c>
       <c r="F236" s="1" t="s">
-        <v>1119</v>
+        <v>916</v>
       </c>
     </row>
     <row r="237" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B237" s="1" t="s">
-        <v>518</v>
+        <v>550</v>
       </c>
       <c r="D237" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E237" s="1" t="s">
-        <v>519</v>
+        <v>551</v>
       </c>
       <c r="F237" s="1" t="s">
-        <v>520</v>
+        <v>552</v>
       </c>
     </row>
     <row r="238" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B238" s="1" t="s">
-        <v>567</v>
+        <v>1145</v>
       </c>
       <c r="D238" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E238" s="1" t="s">
-        <v>568</v>
+        <v>1146</v>
       </c>
       <c r="F238" s="1" t="s">
-        <v>569</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="239" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B239" s="1" t="s">
-        <v>923</v>
+        <v>975</v>
       </c>
       <c r="D239" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E239" s="1" t="s">
-        <v>924</v>
+        <v>976</v>
       </c>
       <c r="F239" s="1" t="s">
-        <v>925</v>
+        <v>977</v>
       </c>
     </row>
     <row r="240" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B240" s="1" t="s">
-        <v>550</v>
+        <v>570</v>
       </c>
       <c r="D240" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E240" s="1" t="s">
-        <v>551</v>
+        <v>571</v>
       </c>
       <c r="F240" s="1" t="s">
-        <v>552</v>
+        <v>572</v>
       </c>
     </row>
     <row r="241" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B241" s="1" t="s">
-        <v>1154</v>
+        <v>1174</v>
       </c>
       <c r="D241" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E241" s="1" t="s">
-        <v>1155</v>
+        <v>1175</v>
       </c>
       <c r="F241" s="1" t="s">
-        <v>1156</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="242" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B242" s="1" t="s">
-        <v>984</v>
+        <v>850</v>
       </c>
       <c r="D242" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E242" s="1" t="s">
-        <v>985</v>
+        <v>851</v>
       </c>
       <c r="F242" s="1" t="s">
-        <v>986</v>
+        <v>852</v>
       </c>
     </row>
     <row r="243" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B243" s="1" t="s">
-        <v>570</v>
+        <v>659</v>
       </c>
       <c r="D243" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E243" s="1" t="s">
-        <v>571</v>
+        <v>660</v>
       </c>
       <c r="F243" s="1" t="s">
-        <v>572</v>
+        <v>661</v>
       </c>
     </row>
     <row r="244" spans="2:6" x14ac:dyDescent="0.2">
@@ -9418,3337 +9384,3295 @@
     </row>
     <row r="245" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B245" s="1" t="s">
-        <v>859</v>
+        <v>454</v>
       </c>
       <c r="D245" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E245" s="1" t="s">
-        <v>860</v>
+        <v>423</v>
       </c>
       <c r="F245" s="1" t="s">
-        <v>861</v>
+        <v>396</v>
       </c>
     </row>
     <row r="246" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B246" s="1" t="s">
-        <v>668</v>
+        <v>705</v>
       </c>
       <c r="D246" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E246" s="1" t="s">
-        <v>669</v>
+        <v>706</v>
       </c>
       <c r="F246" s="1" t="s">
-        <v>670</v>
+        <v>707</v>
       </c>
     </row>
     <row r="247" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B247" s="1" t="s">
-        <v>1192</v>
+        <v>945</v>
       </c>
       <c r="D247" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>1193</v>
+        <v>946</v>
       </c>
       <c r="F247" s="1" t="s">
-        <v>1194</v>
+        <v>947</v>
       </c>
     </row>
     <row r="248" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B248" s="1" t="s">
-        <v>454</v>
+        <v>879</v>
       </c>
       <c r="D248" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E248" s="1" t="s">
-        <v>423</v>
+        <v>880</v>
       </c>
       <c r="F248" s="1" t="s">
-        <v>396</v>
+        <v>881</v>
       </c>
     </row>
     <row r="249" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B249" s="1" t="s">
-        <v>714</v>
+        <v>1029</v>
       </c>
       <c r="D249" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E249" s="1" t="s">
-        <v>715</v>
+        <v>1030</v>
       </c>
       <c r="F249" s="1" t="s">
-        <v>716</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="250" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B250" s="1" t="s">
-        <v>954</v>
+        <v>1154</v>
       </c>
       <c r="D250" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E250" s="1" t="s">
-        <v>955</v>
+        <v>1155</v>
       </c>
       <c r="F250" s="1" t="s">
-        <v>956</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="251" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B251" s="1" t="s">
-        <v>888</v>
+        <v>942</v>
       </c>
       <c r="D251" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E251" s="1" t="s">
-        <v>889</v>
+        <v>943</v>
       </c>
       <c r="F251" s="1" t="s">
-        <v>890</v>
+        <v>944</v>
       </c>
     </row>
     <row r="252" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B252" s="1" t="s">
-        <v>1038</v>
+        <v>1140</v>
       </c>
       <c r="D252" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E252" s="1" t="s">
-        <v>1039</v>
+        <v>1141</v>
       </c>
       <c r="F252" s="1" t="s">
-        <v>1040</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="253" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B253" s="1" t="s">
-        <v>1163</v>
+        <v>817</v>
       </c>
       <c r="D253" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E253" s="1" t="s">
-        <v>1164</v>
+        <v>818</v>
       </c>
       <c r="F253" s="1" t="s">
-        <v>1165</v>
+        <v>819</v>
       </c>
     </row>
     <row r="254" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B254" s="1" t="s">
-        <v>951</v>
+        <v>1018</v>
       </c>
       <c r="D254" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E254" s="1" t="s">
-        <v>952</v>
+        <v>1019</v>
       </c>
       <c r="F254" s="1" t="s">
-        <v>953</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="255" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B255" s="1" t="s">
-        <v>1149</v>
+        <v>1072</v>
       </c>
       <c r="D255" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E255" s="1" t="s">
-        <v>1150</v>
+        <v>1073</v>
       </c>
       <c r="F255" s="1" t="s">
-        <v>1151</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="256" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B256" s="1" t="s">
-        <v>826</v>
+        <v>847</v>
       </c>
       <c r="D256" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E256" s="1" t="s">
-        <v>827</v>
+        <v>848</v>
       </c>
       <c r="F256" s="1" t="s">
-        <v>828</v>
+        <v>849</v>
       </c>
     </row>
     <row r="257" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B257" s="1" t="s">
-        <v>1027</v>
+        <v>698</v>
       </c>
       <c r="D257" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E257" s="1" t="s">
-        <v>1028</v>
+        <v>699</v>
       </c>
       <c r="F257" s="1" t="s">
-        <v>1029</v>
+        <v>700</v>
       </c>
     </row>
     <row r="258" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B258" s="1" t="s">
-        <v>1081</v>
+        <v>794</v>
       </c>
       <c r="D258" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E258" s="1" t="s">
-        <v>1082</v>
+        <v>795</v>
       </c>
       <c r="F258" s="1" t="s">
-        <v>1083</v>
+        <v>796</v>
       </c>
     </row>
     <row r="259" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B259" s="1" t="s">
-        <v>856</v>
+        <v>956</v>
       </c>
       <c r="D259" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>857</v>
+        <v>957</v>
       </c>
       <c r="F259" s="1" t="s">
-        <v>858</v>
+        <v>958</v>
       </c>
     </row>
     <row r="260" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B260" s="1" t="s">
-        <v>707</v>
+        <v>960</v>
       </c>
       <c r="D260" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E260" s="1" t="s">
-        <v>708</v>
+        <v>961</v>
       </c>
       <c r="F260" s="1" t="s">
-        <v>709</v>
+        <v>962</v>
       </c>
     </row>
     <row r="261" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B261" s="1" t="s">
-        <v>803</v>
+        <v>922</v>
       </c>
       <c r="D261" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E261" s="1" t="s">
-        <v>804</v>
+        <v>923</v>
       </c>
       <c r="F261" s="1" t="s">
-        <v>805</v>
+        <v>924</v>
       </c>
     </row>
     <row r="262" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B262" s="1" t="s">
-        <v>965</v>
+        <v>901</v>
       </c>
       <c r="D262" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E262" s="1" t="s">
-        <v>966</v>
+        <v>902</v>
       </c>
       <c r="F262" s="1" t="s">
-        <v>967</v>
+        <v>903</v>
       </c>
     </row>
     <row r="263" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B263" s="1" t="s">
-        <v>969</v>
+        <v>869</v>
       </c>
       <c r="D263" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E263" s="1" t="s">
-        <v>970</v>
+        <v>870</v>
       </c>
       <c r="F263" s="1" t="s">
-        <v>971</v>
+        <v>871</v>
       </c>
     </row>
     <row r="264" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B264" s="1" t="s">
-        <v>931</v>
+        <v>1021</v>
       </c>
       <c r="D264" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E264" s="1" t="s">
-        <v>932</v>
+        <v>1022</v>
       </c>
       <c r="F264" s="1" t="s">
-        <v>933</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="265" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B265" s="1" t="s">
-        <v>910</v>
+        <v>1024</v>
       </c>
       <c r="D265" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E265" s="1" t="s">
-        <v>911</v>
+        <v>1025</v>
       </c>
       <c r="F265" s="1" t="s">
-        <v>912</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="266" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B266" s="1" t="s">
-        <v>878</v>
+        <v>925</v>
       </c>
       <c r="D266" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E266" s="1" t="s">
-        <v>879</v>
+        <v>926</v>
       </c>
       <c r="F266" s="1" t="s">
-        <v>880</v>
+        <v>927</v>
       </c>
     </row>
     <row r="267" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B267" s="1" t="s">
-        <v>1030</v>
+        <v>1297</v>
       </c>
       <c r="D267" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E267" s="1" t="s">
-        <v>1031</v>
+        <v>1298</v>
       </c>
       <c r="F267" s="1" t="s">
-        <v>1032</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="268" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B268" s="1" t="s">
-        <v>1033</v>
+        <v>885</v>
       </c>
       <c r="D268" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E268" s="1" t="s">
-        <v>1034</v>
+        <v>886</v>
       </c>
       <c r="F268" s="1" t="s">
-        <v>1035</v>
+        <v>887</v>
       </c>
     </row>
     <row r="269" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B269" s="1" t="s">
-        <v>934</v>
+        <v>678</v>
       </c>
       <c r="D269" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E269" s="1" t="s">
-        <v>935</v>
+        <v>681</v>
       </c>
       <c r="F269" s="1" t="s">
-        <v>936</v>
+        <v>475</v>
       </c>
     </row>
     <row r="270" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B270" s="1" t="s">
-        <v>1306</v>
+        <v>734</v>
       </c>
       <c r="D270" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E270" s="1" t="s">
-        <v>1307</v>
+        <v>735</v>
       </c>
       <c r="F270" s="1" t="s">
-        <v>1308</v>
+        <v>736</v>
       </c>
     </row>
     <row r="271" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B271" s="1" t="s">
-        <v>894</v>
+        <v>682</v>
       </c>
       <c r="D271" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E271" s="1" t="s">
-        <v>895</v>
+        <v>684</v>
       </c>
       <c r="F271" s="1" t="s">
-        <v>896</v>
+        <v>687</v>
       </c>
     </row>
     <row r="272" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B272" s="1" t="s">
-        <v>687</v>
+        <v>1038</v>
       </c>
       <c r="D272" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E272" s="1" t="s">
-        <v>690</v>
+        <v>1039</v>
       </c>
       <c r="F272" s="1" t="s">
-        <v>475</v>
+        <v>739</v>
       </c>
     </row>
     <row r="273" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B273" s="1" t="s">
-        <v>743</v>
+        <v>737</v>
       </c>
       <c r="D273" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E273" s="1" t="s">
-        <v>744</v>
+        <v>738</v>
       </c>
       <c r="F273" s="1" t="s">
-        <v>745</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="274" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B274" s="1" t="s">
-        <v>691</v>
+        <v>679</v>
       </c>
       <c r="D274" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E274" s="1" t="s">
-        <v>693</v>
+        <v>680</v>
       </c>
       <c r="F274" s="1" t="s">
-        <v>696</v>
+        <v>476</v>
       </c>
     </row>
     <row r="275" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B275" s="1" t="s">
-        <v>1047</v>
+        <v>683</v>
       </c>
       <c r="D275" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E275" s="1" t="s">
-        <v>1048</v>
+        <v>685</v>
       </c>
       <c r="F275" s="1" t="s">
-        <v>748</v>
+        <v>686</v>
       </c>
     </row>
     <row r="276" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B276" s="1" t="s">
-        <v>746</v>
+        <v>1120</v>
       </c>
       <c r="D276" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E276" s="1" t="s">
-        <v>747</v>
+        <v>1121</v>
       </c>
       <c r="F276" s="1" t="s">
-        <v>1046</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="277" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B277" s="1" t="s">
-        <v>688</v>
+        <v>714</v>
       </c>
       <c r="D277" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E277" s="1" t="s">
-        <v>689</v>
+        <v>715</v>
       </c>
       <c r="F277" s="1" t="s">
-        <v>476</v>
+        <v>716</v>
       </c>
     </row>
     <row r="278" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B278" s="1" t="s">
-        <v>692</v>
+        <v>759</v>
       </c>
       <c r="D278" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E278" s="1" t="s">
-        <v>694</v>
+        <v>760</v>
       </c>
       <c r="F278" s="1" t="s">
-        <v>695</v>
+        <v>761</v>
       </c>
     </row>
     <row r="279" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B279" s="1" t="s">
-        <v>1129</v>
+        <v>898</v>
       </c>
       <c r="D279" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E279" s="1" t="s">
-        <v>1130</v>
+        <v>899</v>
       </c>
       <c r="F279" s="1" t="s">
-        <v>1131</v>
+        <v>900</v>
       </c>
     </row>
     <row r="280" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B280" s="1" t="s">
-        <v>723</v>
+        <v>891</v>
       </c>
       <c r="D280" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E280" s="1" t="s">
-        <v>724</v>
+        <v>892</v>
       </c>
       <c r="F280" s="1" t="s">
-        <v>725</v>
+        <v>893</v>
       </c>
     </row>
     <row r="281" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B281" s="1" t="s">
-        <v>768</v>
+        <v>866</v>
       </c>
       <c r="D281" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E281" s="1" t="s">
-        <v>769</v>
+        <v>867</v>
       </c>
       <c r="F281" s="1" t="s">
-        <v>770</v>
+        <v>868</v>
       </c>
     </row>
     <row r="282" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B282" s="1" t="s">
-        <v>907</v>
+        <v>671</v>
       </c>
       <c r="D282" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E282" s="1" t="s">
-        <v>908</v>
+        <v>427</v>
       </c>
       <c r="F282" s="1" t="s">
-        <v>909</v>
+        <v>456</v>
       </c>
     </row>
     <row r="283" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B283" s="1" t="s">
-        <v>900</v>
+        <v>860</v>
       </c>
       <c r="D283" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E283" s="1" t="s">
-        <v>901</v>
+        <v>952</v>
       </c>
       <c r="F283" s="1" t="s">
-        <v>902</v>
+        <v>862</v>
       </c>
     </row>
     <row r="284" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B284" s="1" t="s">
-        <v>875</v>
+        <v>951</v>
       </c>
       <c r="D284" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E284" s="1" t="s">
-        <v>876</v>
+        <v>861</v>
       </c>
       <c r="F284" s="1" t="s">
-        <v>877</v>
+        <v>953</v>
       </c>
     </row>
     <row r="285" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B285" s="1" t="s">
-        <v>680</v>
+        <v>455</v>
       </c>
       <c r="D285" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E285" s="1" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="F285" s="1" t="s">
-        <v>456</v>
+        <v>397</v>
       </c>
     </row>
     <row r="286" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B286" s="1" t="s">
-        <v>869</v>
+        <v>875</v>
       </c>
       <c r="D286" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E286" s="1" t="s">
-        <v>961</v>
+        <v>425</v>
       </c>
       <c r="F286" s="1" t="s">
-        <v>871</v>
+        <v>398</v>
       </c>
     </row>
     <row r="287" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B287" s="1" t="s">
-        <v>960</v>
+        <v>473</v>
       </c>
       <c r="D287" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E287" s="1" t="s">
-        <v>870</v>
+        <v>426</v>
       </c>
       <c r="F287" s="1" t="s">
-        <v>962</v>
+        <v>399</v>
       </c>
     </row>
     <row r="288" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B288" s="1" t="s">
-        <v>455</v>
+        <v>670</v>
       </c>
       <c r="D288" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E288" s="1" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="F288" s="1" t="s">
-        <v>397</v>
+        <v>457</v>
       </c>
     </row>
     <row r="289" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B289" s="1" t="s">
-        <v>884</v>
+        <v>702</v>
       </c>
       <c r="D289" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E289" s="1" t="s">
-        <v>425</v>
+        <v>703</v>
       </c>
       <c r="F289" s="1" t="s">
-        <v>398</v>
+        <v>704</v>
       </c>
     </row>
     <row r="290" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B290" s="1" t="s">
-        <v>473</v>
+        <v>1075</v>
       </c>
       <c r="D290" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E290" s="1" t="s">
-        <v>426</v>
+        <v>1076</v>
       </c>
       <c r="F290" s="1" t="s">
-        <v>399</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="291" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B291" s="1" t="s">
-        <v>679</v>
+        <v>1069</v>
       </c>
       <c r="D291" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E291" s="1" t="s">
-        <v>428</v>
+        <v>1070</v>
       </c>
       <c r="F291" s="1" t="s">
-        <v>457</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="292" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B292" s="1" t="s">
-        <v>711</v>
+        <v>669</v>
       </c>
       <c r="D292" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E292" s="1" t="s">
-        <v>712</v>
+        <v>429</v>
       </c>
       <c r="F292" s="1" t="s">
-        <v>713</v>
+        <v>458</v>
       </c>
     </row>
     <row r="293" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B293" s="1" t="s">
-        <v>1084</v>
+        <v>1249</v>
       </c>
       <c r="D293" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E293" s="1" t="s">
-        <v>1085</v>
+        <v>1250</v>
       </c>
       <c r="F293" s="1" t="s">
-        <v>1086</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="294" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B294" s="1" t="s">
-        <v>1078</v>
+        <v>1116</v>
       </c>
       <c r="D294" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E294" s="1" t="s">
-        <v>1079</v>
+        <v>1117</v>
       </c>
       <c r="F294" s="1" t="s">
-        <v>1080</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="295" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B295" s="1" t="s">
-        <v>678</v>
+        <v>1137</v>
       </c>
       <c r="D295" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E295" s="1" t="s">
-        <v>429</v>
+        <v>1138</v>
       </c>
       <c r="F295" s="1" t="s">
-        <v>458</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="296" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B296" s="1" t="s">
-        <v>1258</v>
+        <v>1115</v>
       </c>
       <c r="D296" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E296" s="1" t="s">
-        <v>1259</v>
+        <v>1143</v>
       </c>
       <c r="F296" s="1" t="s">
-        <v>1260</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="297" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B297" s="1" t="s">
-        <v>1125</v>
+        <v>672</v>
       </c>
       <c r="D297" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E297" s="1" t="s">
-        <v>1126</v>
+        <v>673</v>
       </c>
       <c r="F297" s="1" t="s">
-        <v>1128</v>
+        <v>674</v>
       </c>
     </row>
     <row r="298" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B298" s="1" t="s">
-        <v>1146</v>
+        <v>668</v>
       </c>
       <c r="D298" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E298" s="1" t="s">
-        <v>1147</v>
+        <v>430</v>
       </c>
       <c r="F298" s="1" t="s">
-        <v>1148</v>
+        <v>459</v>
       </c>
     </row>
     <row r="299" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B299" s="1" t="s">
-        <v>1124</v>
+        <v>675</v>
       </c>
       <c r="D299" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E299" s="1" t="s">
-        <v>1152</v>
+        <v>676</v>
       </c>
       <c r="F299" s="1" t="s">
-        <v>1127</v>
+        <v>677</v>
       </c>
     </row>
     <row r="300" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B300" s="1" t="s">
-        <v>681</v>
+        <v>688</v>
       </c>
       <c r="D300" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E300" s="1" t="s">
-        <v>682</v>
+        <v>690</v>
       </c>
       <c r="F300" s="1" t="s">
-        <v>683</v>
+        <v>689</v>
       </c>
     </row>
     <row r="301" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B301" s="1" t="s">
-        <v>677</v>
+        <v>691</v>
       </c>
       <c r="D301" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E301" s="1" t="s">
-        <v>430</v>
+        <v>692</v>
       </c>
       <c r="F301" s="1" t="s">
-        <v>459</v>
+        <v>701</v>
       </c>
     </row>
     <row r="302" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B302" s="1" t="s">
-        <v>684</v>
+        <v>770</v>
       </c>
       <c r="D302" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E302" s="1" t="s">
-        <v>685</v>
+        <v>771</v>
       </c>
       <c r="F302" s="1" t="s">
-        <v>686</v>
+        <v>772</v>
       </c>
     </row>
     <row r="303" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B303" s="1" t="s">
-        <v>697</v>
+        <v>948</v>
       </c>
       <c r="D303" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E303" s="1" t="s">
-        <v>699</v>
+        <v>949</v>
       </c>
       <c r="F303" s="1" t="s">
-        <v>698</v>
+        <v>950</v>
       </c>
     </row>
     <row r="304" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B304" s="1" t="s">
-        <v>700</v>
+        <v>917</v>
       </c>
       <c r="D304" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E304" s="1" t="s">
-        <v>701</v>
+        <v>918</v>
       </c>
       <c r="F304" s="1" t="s">
-        <v>710</v>
+        <v>919</v>
       </c>
     </row>
     <row r="305" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B305" s="1" t="s">
-        <v>779</v>
+        <v>934</v>
       </c>
       <c r="D305" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E305" s="1" t="s">
-        <v>780</v>
+        <v>935</v>
       </c>
       <c r="F305" s="1" t="s">
-        <v>781</v>
+        <v>936</v>
       </c>
     </row>
     <row r="306" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B306" s="1" t="s">
-        <v>957</v>
+        <v>888</v>
       </c>
       <c r="D306" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E306" s="1" t="s">
-        <v>958</v>
+        <v>889</v>
       </c>
       <c r="F306" s="1" t="s">
-        <v>959</v>
+        <v>890</v>
       </c>
     </row>
     <row r="307" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B307" s="1" t="s">
-        <v>926</v>
+        <v>1093</v>
       </c>
       <c r="D307" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E307" s="1" t="s">
-        <v>927</v>
+        <v>1095</v>
       </c>
       <c r="F307" s="1" t="s">
-        <v>928</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="308" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B308" s="1" t="s">
-        <v>943</v>
+        <v>1096</v>
       </c>
       <c r="D308" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E308" s="1" t="s">
-        <v>944</v>
+        <v>1097</v>
       </c>
       <c r="F308" s="1" t="s">
-        <v>945</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="309" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B309" s="1" t="s">
-        <v>897</v>
+        <v>665</v>
       </c>
       <c r="D309" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E309" s="1" t="s">
-        <v>898</v>
+        <v>666</v>
       </c>
       <c r="F309" s="1" t="s">
-        <v>899</v>
+        <v>667</v>
       </c>
     </row>
     <row r="310" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B310" s="1" t="s">
-        <v>1102</v>
+        <v>740</v>
       </c>
       <c r="D310" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E310" s="1" t="s">
-        <v>1104</v>
+        <v>741</v>
       </c>
       <c r="F310" s="1" t="s">
-        <v>1103</v>
+        <v>742</v>
       </c>
     </row>
     <row r="311" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B311" s="1" t="s">
-        <v>1105</v>
+        <v>1194</v>
       </c>
       <c r="D311" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E311" s="1" t="s">
-        <v>1106</v>
+        <v>1196</v>
       </c>
       <c r="F311" s="1" t="s">
-        <v>1107</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="312" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B312" s="1" t="s">
-        <v>674</v>
+        <v>1191</v>
       </c>
       <c r="D312" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E312" s="1" t="s">
-        <v>675</v>
+        <v>1192</v>
       </c>
       <c r="F312" s="1" t="s">
-        <v>676</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="313" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B313" s="1" t="s">
-        <v>749</v>
+        <v>982</v>
       </c>
       <c r="D313" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E313" s="1" t="s">
-        <v>750</v>
+        <v>983</v>
       </c>
       <c r="F313" s="1" t="s">
-        <v>751</v>
+        <v>984</v>
       </c>
     </row>
     <row r="314" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B314" s="1" t="s">
-        <v>1203</v>
+        <v>708</v>
       </c>
       <c r="D314" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E314" s="1" t="s">
-        <v>1205</v>
+        <v>709</v>
       </c>
       <c r="F314" s="1" t="s">
-        <v>1204</v>
+        <v>710</v>
       </c>
     </row>
     <row r="315" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B315" s="1" t="s">
-        <v>1200</v>
+        <v>931</v>
       </c>
       <c r="D315" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E315" s="1" t="s">
-        <v>1201</v>
+        <v>932</v>
       </c>
       <c r="F315" s="1" t="s">
-        <v>1202</v>
+        <v>933</v>
       </c>
     </row>
     <row r="316" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B316" s="1" t="s">
-        <v>991</v>
+        <v>1034</v>
       </c>
       <c r="D316" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E316" s="1" t="s">
-        <v>992</v>
+        <v>1035</v>
       </c>
       <c r="F316" s="1" t="s">
-        <v>993</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="317" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B317" s="1" t="s">
-        <v>717</v>
+        <v>823</v>
       </c>
       <c r="D317" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E317" s="1" t="s">
-        <v>718</v>
+        <v>824</v>
       </c>
       <c r="F317" s="1" t="s">
-        <v>719</v>
+        <v>825</v>
       </c>
     </row>
     <row r="318" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B318" s="1" t="s">
-        <v>940</v>
+        <v>777</v>
       </c>
       <c r="D318" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E318" s="1" t="s">
-        <v>941</v>
+        <v>778</v>
       </c>
       <c r="F318" s="1" t="s">
-        <v>942</v>
+        <v>779</v>
       </c>
     </row>
     <row r="319" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B319" s="1" t="s">
-        <v>1043</v>
+        <v>1132</v>
       </c>
       <c r="D319" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E319" s="1" t="s">
-        <v>1044</v>
+        <v>1133</v>
       </c>
       <c r="F319" s="1" t="s">
-        <v>1045</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="320" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B320" s="1" t="s">
-        <v>832</v>
+        <v>814</v>
       </c>
       <c r="D320" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E320" s="1" t="s">
-        <v>833</v>
+        <v>815</v>
       </c>
       <c r="F320" s="1" t="s">
-        <v>834</v>
+        <v>816</v>
       </c>
     </row>
     <row r="321" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B321" s="1" t="s">
-        <v>786</v>
+        <v>725</v>
       </c>
       <c r="D321" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E321" s="1" t="s">
-        <v>787</v>
+        <v>726</v>
       </c>
       <c r="F321" s="1" t="s">
-        <v>788</v>
+        <v>727</v>
       </c>
     </row>
     <row r="322" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B322" s="1" t="s">
-        <v>1141</v>
+        <v>908</v>
       </c>
       <c r="D322" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E322" s="1" t="s">
-        <v>1142</v>
+        <v>909</v>
       </c>
       <c r="F322" s="1" t="s">
-        <v>1143</v>
+        <v>910</v>
       </c>
     </row>
     <row r="323" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B323" s="1" t="s">
-        <v>823</v>
+        <v>911</v>
       </c>
       <c r="D323" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E323" s="1" t="s">
-        <v>824</v>
+        <v>912</v>
       </c>
       <c r="F323" s="1" t="s">
-        <v>825</v>
+        <v>913</v>
       </c>
     </row>
     <row r="324" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B324" s="1" t="s">
-        <v>734</v>
+        <v>1123</v>
       </c>
       <c r="D324" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E324" s="1" t="s">
-        <v>735</v>
+        <v>1124</v>
       </c>
       <c r="F324" s="1" t="s">
-        <v>736</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="325" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B325" s="1" t="s">
-        <v>917</v>
+        <v>1197</v>
       </c>
       <c r="D325" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E325" s="1" t="s">
-        <v>918</v>
+        <v>1198</v>
       </c>
       <c r="F325" s="1" t="s">
-        <v>919</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="326" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B326" s="1" t="s">
-        <v>920</v>
+        <v>1129</v>
       </c>
       <c r="D326" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E326" s="1" t="s">
-        <v>921</v>
+        <v>1130</v>
       </c>
       <c r="F326" s="1" t="s">
-        <v>922</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="327" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B327" s="1" t="s">
-        <v>1132</v>
+        <v>1125</v>
       </c>
       <c r="D327" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E327" s="1" t="s">
-        <v>1133</v>
+        <v>1126</v>
       </c>
       <c r="F327" s="1" t="s">
-        <v>1137</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="328" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B328" s="1" t="s">
-        <v>1206</v>
+        <v>1200</v>
       </c>
       <c r="D328" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E328" s="1" t="s">
-        <v>1207</v>
+        <v>1201</v>
       </c>
       <c r="F328" s="1" t="s">
-        <v>1208</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="329" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B329" s="1" t="s">
-        <v>1138</v>
+        <v>1294</v>
       </c>
       <c r="D329" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E329" s="1" t="s">
-        <v>1139</v>
+        <v>1295</v>
       </c>
       <c r="F329" s="1" t="s">
-        <v>1140</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="330" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B330" s="1" t="s">
-        <v>1134</v>
+        <v>1305</v>
       </c>
       <c r="D330" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E330" s="1" t="s">
-        <v>1135</v>
+        <v>1306</v>
       </c>
       <c r="F330" s="1" t="s">
-        <v>1136</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="331" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B331" s="1" t="s">
-        <v>1209</v>
+        <v>1178</v>
       </c>
       <c r="D331" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E331" s="1" t="s">
-        <v>1210</v>
+        <v>1179</v>
       </c>
       <c r="F331" s="1" t="s">
-        <v>1211</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="332" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B332" s="1" t="s">
-        <v>1303</v>
+        <v>985</v>
       </c>
       <c r="D332" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E332" s="1" t="s">
-        <v>1304</v>
+        <v>987</v>
       </c>
       <c r="F332" s="1" t="s">
-        <v>1305</v>
+        <v>986</v>
       </c>
     </row>
     <row r="333" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B333" s="1" t="s">
-        <v>1314</v>
+        <v>872</v>
       </c>
       <c r="D333" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E333" s="1" t="s">
-        <v>1315</v>
+        <v>873</v>
       </c>
       <c r="F333" s="1" t="s">
-        <v>1316</v>
+        <v>874</v>
       </c>
     </row>
     <row r="334" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B334" s="1" t="s">
-        <v>1187</v>
+        <v>988</v>
       </c>
       <c r="D334" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E334" s="1" t="s">
-        <v>1188</v>
+        <v>989</v>
       </c>
       <c r="F334" s="1" t="s">
-        <v>1189</v>
+        <v>990</v>
       </c>
     </row>
     <row r="335" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B335" s="1" t="s">
-        <v>994</v>
+        <v>876</v>
       </c>
       <c r="D335" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E335" s="1" t="s">
-        <v>996</v>
+        <v>877</v>
       </c>
       <c r="F335" s="1" t="s">
-        <v>995</v>
+        <v>878</v>
       </c>
     </row>
     <row r="336" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B336" s="1" t="s">
-        <v>881</v>
+        <v>991</v>
       </c>
       <c r="D336" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E336" s="1" t="s">
-        <v>882</v>
+        <v>992</v>
       </c>
       <c r="F336" s="1" t="s">
-        <v>883</v>
+        <v>993</v>
       </c>
     </row>
     <row r="337" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B337" s="1" t="s">
-        <v>997</v>
+        <v>937</v>
       </c>
       <c r="D337" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E337" s="1" t="s">
-        <v>998</v>
+        <v>938</v>
       </c>
       <c r="F337" s="1" t="s">
-        <v>999</v>
+        <v>939</v>
       </c>
     </row>
     <row r="338" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B338" s="1" t="s">
-        <v>885</v>
+        <v>1078</v>
       </c>
       <c r="D338" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E338" s="1" t="s">
-        <v>886</v>
+        <v>1080</v>
       </c>
       <c r="F338" s="1" t="s">
-        <v>887</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="339" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B339" s="1" t="s">
-        <v>1000</v>
+        <v>1079</v>
       </c>
       <c r="D339" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E339" s="1" t="s">
-        <v>1001</v>
+        <v>1081</v>
       </c>
       <c r="F339" s="1" t="s">
-        <v>1002</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="340" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B340" s="1" t="s">
-        <v>946</v>
+        <v>538</v>
       </c>
       <c r="D340" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E340" s="1" t="s">
-        <v>947</v>
+        <v>539</v>
       </c>
       <c r="F340" s="1" t="s">
-        <v>948</v>
+        <v>540</v>
       </c>
     </row>
     <row r="341" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B341" s="1" t="s">
-        <v>1087</v>
+        <v>1308</v>
       </c>
       <c r="D341" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E341" s="1" t="s">
-        <v>1089</v>
-      </c>
-      <c r="F341" s="1" t="s">
-        <v>1091</v>
+        <v>1309</v>
+      </c>
+      <c r="F341" s="6" t="s">
+        <v>1310</v>
       </c>
     </row>
     <row r="342" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B342" s="1" t="s">
-        <v>1088</v>
+        <v>1411</v>
       </c>
       <c r="D342" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E342" s="1" t="s">
-        <v>1090</v>
-      </c>
-      <c r="F342" s="1" t="s">
-        <v>1092</v>
+        <v>1412</v>
+      </c>
+      <c r="F342" s="6" t="s">
+        <v>1413</v>
       </c>
     </row>
     <row r="343" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B343" s="1" t="s">
-        <v>538</v>
+        <v>1372</v>
       </c>
       <c r="D343" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E343" s="1" t="s">
-        <v>539</v>
+        <v>1370</v>
       </c>
       <c r="F343" s="1" t="s">
-        <v>540</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="344" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B344" s="1" t="s">
-        <v>1317</v>
+        <v>437</v>
       </c>
       <c r="D344" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E344" s="1" t="s">
-        <v>1318</v>
-      </c>
-      <c r="F344" s="6" t="s">
-        <v>1319</v>
+        <v>374</v>
+      </c>
+      <c r="F344" s="1" t="s">
+        <v>461</v>
       </c>
     </row>
     <row r="345" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B345" s="1" t="s">
-        <v>1420</v>
+        <v>535</v>
       </c>
       <c r="D345" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E345" s="1" t="s">
-        <v>1421</v>
-      </c>
-      <c r="F345" s="6" t="s">
-        <v>1422</v>
-      </c>
-    </row>
-    <row r="346" spans="2:6" x14ac:dyDescent="0.2">
+        <v>536</v>
+      </c>
+      <c r="F345" s="1" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="346" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B346" s="1" t="s">
-        <v>1381</v>
+        <v>600</v>
       </c>
       <c r="D346" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E346" s="1" t="s">
-        <v>1379</v>
+        <v>602</v>
       </c>
       <c r="F346" s="1" t="s">
-        <v>1380</v>
+        <v>601</v>
       </c>
     </row>
     <row r="347" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B347" s="1" t="s">
-        <v>437</v>
+        <v>603</v>
       </c>
       <c r="D347" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E347" s="1" t="s">
-        <v>374</v>
+        <v>604</v>
       </c>
       <c r="F347" s="1" t="s">
-        <v>461</v>
+        <v>605</v>
       </c>
     </row>
     <row r="348" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B348" s="1" t="s">
-        <v>535</v>
+        <v>616</v>
       </c>
       <c r="D348" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E348" s="1" t="s">
-        <v>536</v>
+        <v>617</v>
       </c>
       <c r="F348" s="1" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="349" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="349" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B349" s="1" t="s">
-        <v>609</v>
+        <v>619</v>
       </c>
       <c r="D349" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E349" s="1" t="s">
-        <v>611</v>
+        <v>620</v>
       </c>
       <c r="F349" s="1" t="s">
-        <v>610</v>
+        <v>621</v>
       </c>
     </row>
     <row r="350" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B350" s="1" t="s">
-        <v>612</v>
+        <v>622</v>
       </c>
       <c r="D350" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E350" s="1" t="s">
-        <v>613</v>
+        <v>623</v>
       </c>
       <c r="F350" s="1" t="s">
-        <v>614</v>
+        <v>624</v>
       </c>
     </row>
     <row r="351" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B351" s="1" t="s">
-        <v>625</v>
+        <v>719</v>
       </c>
       <c r="D351" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E351" s="1" t="s">
-        <v>626</v>
+        <v>720</v>
       </c>
       <c r="F351" s="1" t="s">
-        <v>627</v>
+        <v>721</v>
       </c>
     </row>
     <row r="352" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B352" s="1" t="s">
-        <v>628</v>
+        <v>743</v>
       </c>
       <c r="D352" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E352" s="1" t="s">
-        <v>629</v>
+        <v>744</v>
       </c>
       <c r="F352" s="1" t="s">
-        <v>630</v>
+        <v>745</v>
       </c>
     </row>
     <row r="353" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B353" s="1" t="s">
-        <v>631</v>
+        <v>1057</v>
       </c>
       <c r="D353" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E353" s="1" t="s">
-        <v>632</v>
+        <v>1058</v>
       </c>
       <c r="F353" s="1" t="s">
-        <v>633</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="354" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B354" s="1" t="s">
-        <v>728</v>
+        <v>1326</v>
       </c>
       <c r="D354" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E354" s="1" t="s">
-        <v>729</v>
+        <v>1327</v>
       </c>
       <c r="F354" s="1" t="s">
-        <v>730</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="355" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B355" s="1" t="s">
-        <v>752</v>
+        <v>1329</v>
       </c>
       <c r="D355" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E355" s="1" t="s">
-        <v>753</v>
+        <v>1330</v>
       </c>
       <c r="F355" s="1" t="s">
-        <v>754</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="356" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B356" s="1" t="s">
-        <v>1066</v>
+        <v>1331</v>
       </c>
       <c r="D356" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E356" s="1" t="s">
-        <v>1067</v>
+        <v>1332</v>
       </c>
       <c r="F356" s="1" t="s">
-        <v>1068</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="357" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B357" s="1" t="s">
-        <v>1335</v>
+        <v>1360</v>
       </c>
       <c r="D357" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E357" s="1" t="s">
-        <v>1336</v>
+        <v>1362</v>
       </c>
       <c r="F357" s="1" t="s">
-        <v>1337</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="358" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B358" s="1" t="s">
-        <v>1338</v>
+        <v>1363</v>
       </c>
       <c r="D358" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E358" s="1" t="s">
-        <v>1339</v>
+        <v>1364</v>
       </c>
       <c r="F358" s="1" t="s">
-        <v>1342</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="359" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B359" s="1" t="s">
-        <v>1340</v>
+        <v>1385</v>
       </c>
       <c r="D359" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E359" s="1" t="s">
-        <v>1341</v>
+        <v>1384</v>
       </c>
       <c r="F359" s="1" t="s">
-        <v>1343</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="360" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B360" s="1" t="s">
-        <v>1369</v>
-      </c>
-      <c r="D360" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E360" s="1" t="s">
-        <v>1371</v>
-      </c>
-      <c r="F360" s="1" t="s">
-        <v>1370</v>
+      <c r="A360" s="3" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="361" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B361" s="1" t="s">
-        <v>1372</v>
+        <v>1027</v>
       </c>
       <c r="D361" s="1" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E361" s="1" t="s">
-        <v>1373</v>
+        <v>1273</v>
       </c>
       <c r="F361" s="1" t="s">
-        <v>1374</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="362" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B362" s="1" t="s">
-        <v>1394</v>
+        <v>940</v>
       </c>
       <c r="D362" s="1" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E362" s="1" t="s">
-        <v>1393</v>
+        <v>1274</v>
       </c>
       <c r="F362" s="1" t="s">
-        <v>1378</v>
+        <v>941</v>
       </c>
     </row>
     <row r="363" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A363" s="3" t="s">
-        <v>156</v>
+      <c r="B363" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="D363" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E363" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="F363" s="1" t="s">
+        <v>433</v>
       </c>
     </row>
     <row r="364" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B364" s="1" t="s">
-        <v>1036</v>
+        <v>463</v>
       </c>
       <c r="D364" s="1" t="s">
         <v>26</v>
       </c>
       <c r="E364" s="1" t="s">
-        <v>1282</v>
+        <v>435</v>
       </c>
       <c r="F364" s="1" t="s">
-        <v>1037</v>
+        <v>434</v>
       </c>
     </row>
     <row r="365" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B365" s="1" t="s">
-        <v>949</v>
+        <v>462</v>
       </c>
       <c r="D365" s="1" t="s">
         <v>26</v>
       </c>
       <c r="E365" s="1" t="s">
-        <v>1283</v>
+        <v>436</v>
       </c>
       <c r="F365" s="1" t="s">
-        <v>950</v>
+        <v>460</v>
       </c>
     </row>
     <row r="366" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B366" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D366" s="1" t="s">
         <v>26</v>
       </c>
       <c r="E366" s="1" t="s">
-        <v>432</v>
+        <v>1275</v>
       </c>
       <c r="F366" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="367" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B367" s="1" t="s">
-        <v>463</v>
+        <v>1291</v>
       </c>
       <c r="D367" s="1" t="s">
         <v>26</v>
       </c>
       <c r="E367" s="1" t="s">
-        <v>435</v>
+        <v>1292</v>
       </c>
       <c r="F367" s="1" t="s">
-        <v>434</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="368" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B368" s="1" t="s">
-        <v>462</v>
+        <v>1266</v>
       </c>
       <c r="D368" s="1" t="s">
         <v>26</v>
       </c>
       <c r="E368" s="1" t="s">
-        <v>436</v>
+        <v>1276</v>
       </c>
       <c r="F368" s="1" t="s">
-        <v>460</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="369" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B369" s="1" t="s">
-        <v>465</v>
+        <v>1268</v>
       </c>
       <c r="D369" s="1" t="s">
         <v>26</v>
       </c>
       <c r="E369" s="1" t="s">
-        <v>1284</v>
+        <v>1277</v>
       </c>
       <c r="F369" s="1" t="s">
-        <v>431</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="370" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B370" s="1" t="s">
-        <v>1300</v>
-      </c>
-      <c r="D370" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E370" s="1" t="s">
-        <v>1301</v>
-      </c>
-      <c r="F370" s="1" t="s">
-        <v>1302</v>
+      <c r="A370" s="3" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="371" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B371" s="1" t="s">
-        <v>1275</v>
+        <v>76</v>
       </c>
       <c r="D371" s="1" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="E371" s="1" t="s">
-        <v>1285</v>
+        <v>50</v>
       </c>
       <c r="F371" s="1" t="s">
-        <v>1276</v>
+        <v>149</v>
       </c>
     </row>
     <row r="372" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B372" s="1" t="s">
-        <v>1277</v>
+        <v>150</v>
       </c>
       <c r="D372" s="1" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="E372" s="1" t="s">
-        <v>1286</v>
+        <v>41</v>
       </c>
       <c r="F372" s="1" t="s">
-        <v>1278</v>
+        <v>151</v>
       </c>
     </row>
     <row r="373" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A373" s="3" t="s">
-        <v>55</v>
+        <v>129</v>
       </c>
     </row>
     <row r="374" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B374" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D374" s="1" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="E374" s="1" t="s">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="F374" s="1" t="s">
-        <v>149</v>
+        <v>133</v>
       </c>
     </row>
     <row r="375" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B375" s="1" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="D375" s="1" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="E375" s="1" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="F375" s="1" t="s">
-        <v>151</v>
+        <v>134</v>
       </c>
     </row>
     <row r="376" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A376" s="3" t="s">
-        <v>129</v>
+      <c r="B376" s="1" t="s">
+        <v>959</v>
+      </c>
+      <c r="D376" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E376" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F376" s="1" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="377" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B377" s="1" t="s">
-        <v>77</v>
+        <v>130</v>
       </c>
       <c r="D377" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E377" s="1" t="s">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="F377" s="1" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="378" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B378" s="1" t="s">
-        <v>147</v>
+        <v>131</v>
       </c>
       <c r="D378" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E378" s="1" t="s">
-        <v>50</v>
+        <v>132</v>
       </c>
       <c r="F378" s="1" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="379" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B379" s="1" t="s">
-        <v>968</v>
+        <v>162</v>
       </c>
       <c r="D379" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E379" s="1" t="s">
-        <v>28</v>
+        <v>167</v>
       </c>
       <c r="F379" s="1" t="s">
-        <v>135</v>
+        <v>177</v>
       </c>
     </row>
     <row r="380" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B380" s="1" t="s">
-        <v>130</v>
+        <v>163</v>
       </c>
       <c r="D380" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E380" s="1" t="s">
-        <v>88</v>
+        <v>168</v>
       </c>
       <c r="F380" s="1" t="s">
-        <v>136</v>
+        <v>201</v>
       </c>
     </row>
     <row r="381" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B381" s="1" t="s">
-        <v>131</v>
+        <v>164</v>
       </c>
       <c r="D381" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E381" s="1" t="s">
-        <v>132</v>
+        <v>169</v>
       </c>
       <c r="F381" s="1" t="s">
-        <v>137</v>
+        <v>178</v>
       </c>
     </row>
     <row r="382" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B382" s="1" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="D382" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E382" s="1" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="F382" s="1" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="383" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B383" s="1" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="D383" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E383" s="1" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="F383" s="1" t="s">
-        <v>201</v>
+        <v>180</v>
       </c>
     </row>
     <row r="384" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B384" s="1" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="D384" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E384" s="1" t="s">
-        <v>169</v>
+        <v>41</v>
       </c>
       <c r="F384" s="1" t="s">
-        <v>178</v>
+        <v>142</v>
       </c>
     </row>
     <row r="385" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B385" s="1" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="D385" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E385" s="1" t="s">
-        <v>170</v>
+        <v>138</v>
       </c>
       <c r="F385" s="1" t="s">
-        <v>179</v>
+        <v>143</v>
       </c>
     </row>
     <row r="386" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B386" s="1" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="D386" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E386" s="1" t="s">
-        <v>171</v>
+        <v>139</v>
       </c>
       <c r="F386" s="1" t="s">
-        <v>180</v>
+        <v>144</v>
       </c>
     </row>
     <row r="387" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B387" s="1" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="D387" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E387" s="1" t="s">
-        <v>41</v>
+        <v>140</v>
       </c>
       <c r="F387" s="1" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="388" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B388" s="1" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D388" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E388" s="1" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="F388" s="1" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="389" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B389" s="1" t="s">
-        <v>174</v>
+        <v>191</v>
       </c>
       <c r="D389" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E389" s="1" t="s">
-        <v>139</v>
+        <v>181</v>
       </c>
       <c r="F389" s="1" t="s">
-        <v>144</v>
+        <v>186</v>
       </c>
     </row>
     <row r="390" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B390" s="1" t="s">
-        <v>175</v>
+        <v>192</v>
       </c>
       <c r="D390" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E390" s="1" t="s">
-        <v>140</v>
+        <v>182</v>
       </c>
       <c r="F390" s="1" t="s">
-        <v>145</v>
+        <v>187</v>
       </c>
     </row>
     <row r="391" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B391" s="1" t="s">
-        <v>176</v>
+        <v>193</v>
       </c>
       <c r="D391" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E391" s="1" t="s">
-        <v>141</v>
+        <v>183</v>
       </c>
       <c r="F391" s="1" t="s">
-        <v>146</v>
+        <v>188</v>
       </c>
     </row>
     <row r="392" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B392" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="D392" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E392" s="1" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="F392" s="1" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="393" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B393" s="1" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="D393" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E393" s="1" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F393" s="1" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="394" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B394" s="1" t="s">
-        <v>193</v>
+        <v>1366</v>
       </c>
       <c r="D394" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E394" s="1" t="s">
-        <v>183</v>
+        <v>1367</v>
       </c>
       <c r="F394" s="1" t="s">
-        <v>188</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="395" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B395" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="D395" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E395" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="F395" s="1" t="s">
-        <v>189</v>
+      <c r="A395" s="3" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="396" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B396" s="1" t="s">
-        <v>195</v>
+        <v>128</v>
       </c>
       <c r="D396" s="1" t="s">
-        <v>21</v>
+        <v>250</v>
       </c>
       <c r="E396" s="1" t="s">
-        <v>184</v>
+        <v>20</v>
       </c>
       <c r="F396" s="1" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
     </row>
     <row r="397" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B397" s="1" t="s">
-        <v>1375</v>
+        <v>1382</v>
       </c>
       <c r="D397" s="1" t="s">
-        <v>21</v>
+        <v>250</v>
       </c>
       <c r="E397" s="1" t="s">
-        <v>1376</v>
+        <v>167</v>
       </c>
       <c r="F397" s="1" t="s">
-        <v>1377</v>
-      </c>
-    </row>
-    <row r="398" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A398" s="3" t="s">
-        <v>196</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="399" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B399" s="1" t="s">
-        <v>128</v>
+        <v>78</v>
       </c>
       <c r="D399" s="1" t="s">
-        <v>250</v>
+        <v>29</v>
       </c>
       <c r="E399" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F399" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="401" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B401" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D401" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E401" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F401" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="403" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B403" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D403" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E403" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F403" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="405" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B405" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D405" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E405" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F405" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="406" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A406" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="407" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B407" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D407" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E407" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F399" s="1" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="400" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B400" s="1" t="s">
-        <v>1391</v>
-      </c>
-      <c r="D400" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="E400" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="F400" s="1" t="s">
-        <v>1392</v>
-      </c>
-    </row>
-    <row r="402" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B402" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="D402" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E402" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F402" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="404" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B404" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="D404" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E404" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F404" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="406" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B406" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D406" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E406" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F406" s="1" t="s">
-        <v>25</v>
+      <c r="F407" s="1" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="408" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B408" s="1" t="s">
-        <v>81</v>
+        <v>296</v>
       </c>
       <c r="D408" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E408" s="1" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="F408" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="409" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A409" s="3" t="s">
-        <v>39</v>
+        <v>298</v>
       </c>
     </row>
     <row r="410" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B410" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D410" s="1" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="E410" s="1" t="s">
-        <v>20</v>
+        <v>61</v>
       </c>
       <c r="F410" s="1" t="s">
-        <v>297</v>
+        <v>60</v>
       </c>
     </row>
     <row r="411" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B411" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="D411" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E411" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="F411" s="1" t="s">
-        <v>298</v>
+      <c r="A411" s="7" t="s">
+        <v>1257</v>
+      </c>
+    </row>
+    <row r="412" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B412" s="1" t="s">
+        <v>1255</v>
+      </c>
+      <c r="D412" s="1" t="s">
+        <v>1256</v>
+      </c>
+      <c r="E412" s="1" t="s">
+        <v>1258</v>
+      </c>
+      <c r="F412" s="1" t="s">
+        <v>1259</v>
       </c>
     </row>
     <row r="413" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B413" s="1" t="s">
-        <v>83</v>
+        <v>1283</v>
       </c>
       <c r="D413" s="1" t="s">
-        <v>59</v>
+        <v>1256</v>
       </c>
       <c r="E413" s="1" t="s">
-        <v>61</v>
+        <v>1285</v>
       </c>
       <c r="F413" s="1" t="s">
-        <v>60</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="414" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A414" s="7" t="s">
-        <v>1266</v>
+      <c r="B414" s="1" t="s">
+        <v>1286</v>
+      </c>
+      <c r="D414" s="1" t="s">
+        <v>1256</v>
+      </c>
+      <c r="E414" s="1" t="s">
+        <v>1287</v>
+      </c>
+      <c r="F414" s="1" t="s">
+        <v>1284</v>
       </c>
     </row>
     <row r="415" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B415" s="1" t="s">
-        <v>1264</v>
-      </c>
-      <c r="D415" s="1" t="s">
-        <v>1265</v>
-      </c>
-      <c r="E415" s="1" t="s">
-        <v>1267</v>
-      </c>
-      <c r="F415" s="1" t="s">
-        <v>1268</v>
+      <c r="A415" s="3" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="416" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B416" s="1" t="s">
-        <v>1292</v>
+        <v>122</v>
       </c>
       <c r="D416" s="1" t="s">
-        <v>1265</v>
+        <v>123</v>
       </c>
       <c r="E416" s="1" t="s">
-        <v>1294</v>
+        <v>1148</v>
       </c>
       <c r="F416" s="1" t="s">
-        <v>1293</v>
+        <v>124</v>
       </c>
     </row>
     <row r="417" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B417" s="1" t="s">
-        <v>1295</v>
+        <v>253</v>
       </c>
       <c r="D417" s="1" t="s">
-        <v>1265</v>
+        <v>126</v>
       </c>
       <c r="E417" s="1" t="s">
-        <v>1296</v>
+        <v>1149</v>
       </c>
       <c r="F417" s="1" t="s">
-        <v>1293</v>
+        <v>127</v>
       </c>
     </row>
     <row r="418" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A418" s="3" t="s">
-        <v>252</v>
+      <c r="B418" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="D418" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E418" s="1" t="s">
+        <v>1150</v>
+      </c>
+      <c r="F418" s="1" t="s">
+        <v>599</v>
       </c>
     </row>
     <row r="419" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B419" s="1" t="s">
-        <v>122</v>
+        <v>756</v>
       </c>
       <c r="D419" s="1" t="s">
-        <v>123</v>
+        <v>757</v>
       </c>
       <c r="E419" s="1" t="s">
-        <v>1157</v>
+        <v>32</v>
       </c>
       <c r="F419" s="1" t="s">
-        <v>124</v>
+        <v>758</v>
       </c>
     </row>
     <row r="420" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B420" s="1" t="s">
-        <v>253</v>
+        <v>1151</v>
       </c>
       <c r="D420" s="1" t="s">
-        <v>126</v>
+        <v>757</v>
       </c>
       <c r="E420" s="1" t="s">
-        <v>1158</v>
+        <v>1152</v>
       </c>
       <c r="F420" s="1" t="s">
-        <v>127</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="421" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B421" s="1" t="s">
-        <v>598</v>
-      </c>
-      <c r="D421" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="E421" s="1" t="s">
-        <v>1159</v>
-      </c>
-      <c r="F421" s="1" t="s">
-        <v>599</v>
+      <c r="A421" s="3" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="422" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B422" s="1" t="s">
-        <v>765</v>
+        <v>251</v>
       </c>
       <c r="D422" s="1" t="s">
-        <v>766</v>
+        <v>255</v>
       </c>
       <c r="E422" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F422" s="1" t="s">
-        <v>767</v>
+        <v>256</v>
       </c>
     </row>
     <row r="423" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B423" s="1" t="s">
-        <v>1160</v>
+        <v>257</v>
       </c>
       <c r="D423" s="1" t="s">
-        <v>766</v>
+        <v>280</v>
       </c>
       <c r="E423" s="1" t="s">
-        <v>1161</v>
+        <v>18</v>
       </c>
       <c r="F423" s="1" t="s">
-        <v>1162</v>
+        <v>258</v>
       </c>
     </row>
     <row r="424" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A424" s="3" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
     </row>
     <row r="425" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B425" s="1" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="D425" s="1" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="E425" s="1" t="s">
-        <v>18</v>
+        <v>611</v>
       </c>
       <c r="F425" s="1" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
     </row>
     <row r="426" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B426" s="1" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="D426" s="1" t="s">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="E426" s="1" t="s">
-        <v>18</v>
+        <v>612</v>
       </c>
       <c r="F426" s="1" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
     </row>
     <row r="427" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A427" s="3" t="s">
-        <v>261</v>
+        <v>362</v>
       </c>
     </row>
     <row r="428" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B428" s="1" t="s">
-        <v>259</v>
+        <v>363</v>
       </c>
       <c r="D428" s="1" t="s">
-        <v>260</v>
+        <v>364</v>
       </c>
       <c r="E428" s="1" t="s">
-        <v>620</v>
+        <v>20</v>
       </c>
       <c r="F428" s="1" t="s">
-        <v>264</v>
+        <v>366</v>
       </c>
     </row>
     <row r="429" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B429" s="1" t="s">
-        <v>263</v>
+        <v>365</v>
       </c>
       <c r="D429" s="1" t="s">
-        <v>260</v>
+        <v>364</v>
       </c>
       <c r="E429" s="1" t="s">
-        <v>621</v>
+        <v>50</v>
       </c>
       <c r="F429" s="1" t="s">
-        <v>262</v>
+        <v>367</v>
       </c>
     </row>
     <row r="430" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A430" s="3" t="s">
-        <v>362</v>
+        <v>524</v>
       </c>
     </row>
     <row r="431" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B431" s="1" t="s">
-        <v>363</v>
+        <v>521</v>
       </c>
       <c r="D431" s="1" t="s">
-        <v>364</v>
+        <v>522</v>
       </c>
       <c r="E431" s="1" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="F431" s="1" t="s">
-        <v>366</v>
+        <v>523</v>
       </c>
     </row>
     <row r="432" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B432" s="1" t="s">
-        <v>365</v>
+        <v>582</v>
       </c>
       <c r="D432" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="E432" s="1" t="s">
-        <v>50</v>
+        <v>584</v>
       </c>
       <c r="F432" s="1" t="s">
-        <v>367</v>
+        <v>583</v>
       </c>
     </row>
     <row r="433" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A433" s="3" t="s">
-        <v>524</v>
+      <c r="B433" s="1" t="s">
+        <v>787</v>
+      </c>
+      <c r="D433" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="F433" s="1" t="s">
+        <v>789</v>
       </c>
     </row>
     <row r="434" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B434" s="1" t="s">
-        <v>521</v>
-      </c>
-      <c r="D434" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="E434" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F434" s="1" t="s">
-        <v>523</v>
+      <c r="A434" s="3" t="s">
+        <v>541</v>
       </c>
     </row>
     <row r="435" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B435" s="1" t="s">
-        <v>582</v>
+        <v>542</v>
       </c>
       <c r="D435" s="1" t="s">
-        <v>584</v>
-      </c>
-      <c r="F435" s="1" t="s">
-        <v>583</v>
+        <v>547</v>
+      </c>
+      <c r="E435" s="1" t="s">
+        <v>1181</v>
+      </c>
+      <c r="F435" s="6" t="s">
+        <v>549</v>
       </c>
     </row>
     <row r="436" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B436" s="1" t="s">
-        <v>796</v>
+        <v>553</v>
       </c>
       <c r="D436" s="1" t="s">
-        <v>797</v>
-      </c>
-      <c r="F436" s="1" t="s">
-        <v>798</v>
+        <v>547</v>
+      </c>
+      <c r="E436" s="1" t="s">
+        <v>1182</v>
+      </c>
+      <c r="F436" s="6" t="s">
+        <v>554</v>
       </c>
     </row>
     <row r="437" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A437" s="3" t="s">
-        <v>541</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="438" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B438" s="1" t="s">
-        <v>542</v>
+        <v>1226</v>
       </c>
       <c r="D438" s="1" t="s">
-        <v>547</v>
+        <v>1222</v>
       </c>
       <c r="E438" s="1" t="s">
-        <v>1190</v>
-      </c>
-      <c r="F438" s="6" t="s">
-        <v>549</v>
+        <v>300</v>
+      </c>
+      <c r="F438" s="1" t="s">
+        <v>963</v>
       </c>
     </row>
     <row r="439" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B439" s="1" t="s">
-        <v>553</v>
+        <v>1227</v>
       </c>
       <c r="D439" s="1" t="s">
-        <v>547</v>
+        <v>1222</v>
       </c>
       <c r="E439" s="1" t="s">
-        <v>1191</v>
-      </c>
-      <c r="F439" s="6" t="s">
-        <v>554</v>
+        <v>299</v>
+      </c>
+      <c r="F439" s="1" t="s">
+        <v>573</v>
       </c>
     </row>
     <row r="440" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A440" s="3" t="s">
-        <v>1232</v>
+      <c r="B440" s="1" t="s">
+        <v>1228</v>
+      </c>
+      <c r="D440" s="1" t="s">
+        <v>1222</v>
+      </c>
+      <c r="E440" s="1" t="s">
+        <v>1212</v>
+      </c>
+      <c r="F440" s="1" t="s">
+        <v>548</v>
       </c>
     </row>
     <row r="441" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B441" s="1" t="s">
-        <v>1235</v>
+        <v>1229</v>
       </c>
       <c r="D441" s="1" t="s">
-        <v>1231</v>
+        <v>1222</v>
       </c>
       <c r="E441" s="1" t="s">
-        <v>300</v>
+        <v>1224</v>
       </c>
       <c r="F441" s="1" t="s">
-        <v>972</v>
-      </c>
-    </row>
-    <row r="442" spans="1:6" x14ac:dyDescent="0.2">
+        <v>1177</v>
+      </c>
+    </row>
+    <row r="442" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B442" s="1" t="s">
-        <v>1236</v>
+        <v>1230</v>
       </c>
       <c r="D442" s="1" t="s">
-        <v>1231</v>
+        <v>1222</v>
       </c>
       <c r="E442" s="1" t="s">
-        <v>299</v>
+        <v>1225</v>
       </c>
       <c r="F442" s="1" t="s">
-        <v>573</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="443" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B443" s="1" t="s">
-        <v>1237</v>
+        <v>1271</v>
       </c>
       <c r="D443" s="1" t="s">
-        <v>1231</v>
+        <v>1222</v>
       </c>
       <c r="E443" s="1" t="s">
-        <v>1221</v>
+        <v>1270</v>
       </c>
       <c r="F443" s="1" t="s">
-        <v>548</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="444" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B444" s="1" t="s">
-        <v>1238</v>
+        <v>1231</v>
       </c>
       <c r="D444" s="1" t="s">
-        <v>1231</v>
+        <v>1222</v>
       </c>
       <c r="E444" s="1" t="s">
+        <v>1232</v>
+      </c>
+      <c r="F444" s="1" t="s">
         <v>1233</v>
       </c>
-      <c r="F444" s="1" t="s">
-        <v>1186</v>
-      </c>
-    </row>
-    <row r="445" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="445" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B445" s="1" t="s">
-        <v>1239</v>
+        <v>1242</v>
       </c>
       <c r="D445" s="1" t="s">
-        <v>1231</v>
+        <v>1222</v>
       </c>
       <c r="E445" s="1" t="s">
-        <v>1234</v>
+        <v>1243</v>
       </c>
       <c r="F445" s="1" t="s">
-        <v>1144</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="446" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B446" s="1" t="s">
-        <v>1280</v>
-      </c>
-      <c r="D446" s="1" t="s">
-        <v>1231</v>
-      </c>
-      <c r="E446" s="1" t="s">
-        <v>1279</v>
-      </c>
-      <c r="F446" s="1" t="s">
-        <v>1281</v>
+      <c r="A446" s="3" t="s">
+        <v>615</v>
       </c>
     </row>
     <row r="447" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B447" s="1" t="s">
-        <v>1240</v>
+        <v>606</v>
       </c>
       <c r="D447" s="1" t="s">
-        <v>1231</v>
+        <v>610</v>
       </c>
       <c r="E447" s="1" t="s">
-        <v>1241</v>
-      </c>
-      <c r="F447" s="1" t="s">
-        <v>1242</v>
+        <v>613</v>
+      </c>
+      <c r="F447" s="6" t="s">
+        <v>609</v>
       </c>
     </row>
     <row r="448" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B448" s="1" t="s">
-        <v>1251</v>
+        <v>607</v>
       </c>
       <c r="D448" s="1" t="s">
-        <v>1231</v>
+        <v>610</v>
       </c>
       <c r="E448" s="1" t="s">
-        <v>1252</v>
-      </c>
-      <c r="F448" s="1" t="s">
-        <v>1253</v>
+        <v>614</v>
+      </c>
+      <c r="F448" s="6" t="s">
+        <v>608</v>
       </c>
     </row>
     <row r="449" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A449" s="3" t="s">
-        <v>624</v>
-      </c>
+        <v>645</v>
+      </c>
+      <c r="F449" s="6"/>
     </row>
     <row r="450" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B450" s="1" t="s">
-        <v>615</v>
+        <v>647</v>
       </c>
       <c r="D450" s="1" t="s">
-        <v>619</v>
+        <v>649</v>
       </c>
       <c r="E450" s="1" t="s">
-        <v>622</v>
+        <v>652</v>
       </c>
       <c r="F450" s="6" t="s">
-        <v>618</v>
+        <v>656</v>
       </c>
     </row>
     <row r="451" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B451" s="1" t="s">
-        <v>616</v>
+        <v>648</v>
       </c>
       <c r="D451" s="1" t="s">
-        <v>619</v>
+        <v>649</v>
       </c>
       <c r="E451" s="1" t="s">
-        <v>623</v>
+        <v>654</v>
       </c>
       <c r="F451" s="6" t="s">
-        <v>617</v>
+        <v>657</v>
       </c>
     </row>
     <row r="452" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A452" s="3" t="s">
-        <v>654</v>
-      </c>
-      <c r="F452" s="6"/>
+      <c r="B452" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D452" s="1" t="s">
+        <v>649</v>
+      </c>
+      <c r="E452" s="1" t="s">
+        <v>655</v>
+      </c>
+      <c r="F452" s="6" t="s">
+        <v>658</v>
+      </c>
     </row>
     <row r="453" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B453" s="1" t="s">
-        <v>656</v>
+        <v>811</v>
       </c>
       <c r="D453" s="1" t="s">
-        <v>658</v>
+        <v>649</v>
       </c>
       <c r="E453" s="1" t="s">
-        <v>661</v>
+        <v>812</v>
       </c>
       <c r="F453" s="6" t="s">
-        <v>665</v>
+        <v>813</v>
       </c>
     </row>
     <row r="454" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B454" s="1" t="s">
-        <v>657</v>
-      </c>
-      <c r="D454" s="1" t="s">
-        <v>658</v>
-      </c>
-      <c r="E454" s="1" t="s">
-        <v>663</v>
-      </c>
-      <c r="F454" s="6" t="s">
-        <v>666</v>
-      </c>
+      <c r="A454" s="3" t="s">
+        <v>646</v>
+      </c>
+      <c r="F454" s="6"/>
     </row>
     <row r="455" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B455" s="1" t="s">
-        <v>662</v>
+        <v>650</v>
       </c>
       <c r="D455" s="1" t="s">
-        <v>658</v>
+        <v>651</v>
       </c>
       <c r="E455" s="1" t="s">
-        <v>664</v>
+        <v>652</v>
       </c>
       <c r="F455" s="6" t="s">
-        <v>667</v>
+        <v>697</v>
       </c>
     </row>
     <row r="456" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B456" s="1" t="s">
-        <v>820</v>
+        <v>843</v>
       </c>
       <c r="D456" s="1" t="s">
-        <v>658</v>
+        <v>651</v>
       </c>
       <c r="E456" s="1" t="s">
-        <v>821</v>
+        <v>654</v>
       </c>
       <c r="F456" s="6" t="s">
-        <v>822</v>
+        <v>841</v>
       </c>
     </row>
     <row r="457" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A457" s="3" t="s">
+      <c r="B457" s="1" t="s">
+        <v>840</v>
+      </c>
+      <c r="D457" s="1" t="s">
+        <v>651</v>
+      </c>
+      <c r="E457" s="1" t="s">
         <v>655</v>
       </c>
-      <c r="F457" s="6"/>
+      <c r="F457" s="6" t="s">
+        <v>842</v>
+      </c>
     </row>
     <row r="458" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B458" s="1" t="s">
-        <v>659</v>
+        <v>844</v>
       </c>
       <c r="D458" s="1" t="s">
-        <v>660</v>
+        <v>651</v>
       </c>
       <c r="E458" s="1" t="s">
-        <v>661</v>
+        <v>856</v>
       </c>
       <c r="F458" s="6" t="s">
-        <v>706</v>
+        <v>857</v>
       </c>
     </row>
     <row r="459" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B459" s="1" t="s">
-        <v>852</v>
-      </c>
-      <c r="D459" s="1" t="s">
-        <v>660</v>
-      </c>
-      <c r="E459" s="1" t="s">
-        <v>663</v>
-      </c>
-      <c r="F459" s="6" t="s">
-        <v>850</v>
-      </c>
+      <c r="A459" s="3" t="s">
+        <v>693</v>
+      </c>
+      <c r="F459" s="6"/>
     </row>
     <row r="460" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B460" s="1" t="s">
-        <v>849</v>
+        <v>954</v>
       </c>
       <c r="D460" s="1" t="s">
-        <v>660</v>
+        <v>696</v>
       </c>
       <c r="E460" s="1" t="s">
-        <v>664</v>
+        <v>20</v>
       </c>
       <c r="F460" s="6" t="s">
-        <v>851</v>
+        <v>955</v>
       </c>
     </row>
     <row r="461" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B461" s="1" t="s">
-        <v>853</v>
+        <v>694</v>
       </c>
       <c r="D461" s="1" t="s">
-        <v>660</v>
+        <v>696</v>
       </c>
       <c r="E461" s="1" t="s">
-        <v>865</v>
+        <v>41</v>
       </c>
       <c r="F461" s="6" t="s">
-        <v>866</v>
+        <v>695</v>
       </c>
     </row>
     <row r="462" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A462" s="3" t="s">
-        <v>702</v>
-      </c>
-      <c r="F462" s="6"/>
+      <c r="B462" s="1" t="s">
+        <v>858</v>
+      </c>
+      <c r="D462" s="1" t="s">
+        <v>696</v>
+      </c>
+      <c r="E462" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="F462" s="6" t="s">
+        <v>859</v>
+      </c>
     </row>
     <row r="463" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B463" s="1" t="s">
-        <v>963</v>
+        <v>1053</v>
       </c>
       <c r="D463" s="1" t="s">
-        <v>705</v>
+        <v>696</v>
       </c>
       <c r="E463" s="1" t="s">
-        <v>20</v>
+        <v>1010</v>
       </c>
       <c r="F463" s="6" t="s">
-        <v>964</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="464" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B464" s="1" t="s">
-        <v>703</v>
+        <v>1052</v>
       </c>
       <c r="D464" s="1" t="s">
-        <v>705</v>
+        <v>696</v>
       </c>
       <c r="E464" s="1" t="s">
-        <v>41</v>
+        <v>1011</v>
       </c>
       <c r="F464" s="6" t="s">
-        <v>704</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="465" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B465" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="D465" s="1" t="s">
-        <v>705</v>
-      </c>
-      <c r="E465" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="F465" s="6" t="s">
-        <v>868</v>
-      </c>
+      <c r="A465" s="3" t="s">
+        <v>763</v>
+      </c>
+      <c r="F465" s="6"/>
     </row>
     <row r="466" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B466" s="1" t="s">
-        <v>1062</v>
+        <v>764</v>
       </c>
       <c r="D466" s="1" t="s">
-        <v>705</v>
+        <v>765</v>
       </c>
       <c r="E466" s="1" t="s">
-        <v>1019</v>
+        <v>18</v>
       </c>
       <c r="F466" s="6" t="s">
-        <v>1063</v>
+        <v>766</v>
       </c>
     </row>
     <row r="467" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B467" s="1" t="s">
-        <v>1061</v>
-      </c>
-      <c r="D467" s="1" t="s">
-        <v>705</v>
-      </c>
-      <c r="E467" s="1" t="s">
-        <v>1020</v>
-      </c>
-      <c r="F467" s="6" t="s">
-        <v>1145</v>
-      </c>
+      <c r="A467" s="3" t="s">
+        <v>774</v>
+      </c>
+      <c r="F467" s="6"/>
     </row>
     <row r="468" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A468" s="3" t="s">
-        <v>772</v>
-      </c>
-      <c r="F468" s="6"/>
+      <c r="B468" s="1" t="s">
+        <v>775</v>
+      </c>
+      <c r="D468" s="1" t="s">
+        <v>776</v>
+      </c>
+      <c r="E468" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="F468" s="6" t="s">
+        <v>773</v>
+      </c>
     </row>
     <row r="469" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B469" s="1" t="s">
-        <v>773</v>
-      </c>
-      <c r="D469" s="1" t="s">
-        <v>774</v>
-      </c>
-      <c r="E469" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F469" s="6" t="s">
-        <v>775</v>
-      </c>
+      <c r="A469" s="3" t="s">
+        <v>801</v>
+      </c>
+      <c r="F469" s="6"/>
     </row>
     <row r="470" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A470" s="3" t="s">
-        <v>783</v>
-      </c>
-      <c r="F470" s="6"/>
+      <c r="B470" s="1" t="s">
+        <v>797</v>
+      </c>
+      <c r="D470" s="1" t="s">
+        <v>798</v>
+      </c>
+      <c r="E470" s="1" t="s">
+        <v>800</v>
+      </c>
+      <c r="F470" s="6" t="s">
+        <v>799</v>
+      </c>
     </row>
     <row r="471" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B471" s="1" t="s">
-        <v>784</v>
+        <v>1289</v>
       </c>
       <c r="D471" s="1" t="s">
-        <v>785</v>
+        <v>798</v>
       </c>
       <c r="E471" s="1" t="s">
-        <v>89</v>
+        <v>1290</v>
       </c>
       <c r="F471" s="6" t="s">
-        <v>782</v>
+        <v>799</v>
       </c>
     </row>
     <row r="472" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A472" s="3" t="s">
-        <v>810</v>
-      </c>
-      <c r="F472" s="6"/>
+      <c r="B472" s="1" t="s">
+        <v>1339</v>
+      </c>
+      <c r="D472" s="1" t="s">
+        <v>798</v>
+      </c>
+      <c r="E472" s="1" t="s">
+        <v>1340</v>
+      </c>
+      <c r="F472" s="6" t="s">
+        <v>799</v>
+      </c>
     </row>
     <row r="473" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B473" s="1" t="s">
-        <v>806</v>
-      </c>
-      <c r="D473" s="1" t="s">
-        <v>807</v>
-      </c>
-      <c r="E473" s="1" t="s">
-        <v>809</v>
-      </c>
-      <c r="F473" s="6" t="s">
-        <v>808</v>
-      </c>
+      <c r="A473" s="3" t="s">
+        <v>1188</v>
+      </c>
+      <c r="F473" s="6"/>
     </row>
     <row r="474" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B474" s="1" t="s">
-        <v>1298</v>
+        <v>1186</v>
       </c>
       <c r="D474" s="1" t="s">
-        <v>807</v>
+        <v>1187</v>
       </c>
       <c r="E474" s="1" t="s">
-        <v>1299</v>
+        <v>1190</v>
       </c>
       <c r="F474" s="6" t="s">
-        <v>808</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="475" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B475" s="1" t="s">
-        <v>1348</v>
-      </c>
-      <c r="D475" s="1" t="s">
-        <v>807</v>
-      </c>
-      <c r="E475" s="1" t="s">
-        <v>1349</v>
-      </c>
-      <c r="F475" s="6" t="s">
-        <v>808</v>
-      </c>
+      <c r="A475" s="7" t="s">
+        <v>1211</v>
+      </c>
+      <c r="F475" s="6"/>
     </row>
     <row r="476" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A476" s="3" t="s">
-        <v>1197</v>
-      </c>
-      <c r="F476" s="6"/>
+      <c r="B476" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="D476" s="1" t="s">
+        <v>1210</v>
+      </c>
+      <c r="E476" s="1" t="s">
+        <v>1220</v>
+      </c>
+      <c r="F476" s="6" t="s">
+        <v>1221</v>
+      </c>
     </row>
     <row r="477" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B477" s="1" t="s">
-        <v>1195</v>
+        <v>1214</v>
       </c>
       <c r="D477" s="1" t="s">
-        <v>1196</v>
+        <v>1210</v>
       </c>
       <c r="E477" s="1" t="s">
-        <v>1199</v>
+        <v>1213</v>
       </c>
       <c r="F477" s="6" t="s">
-        <v>1198</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="478" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A478" s="7" t="s">
-        <v>1220</v>
-      </c>
-      <c r="F478" s="6"/>
+      <c r="B478" s="1" t="s">
+        <v>1215</v>
+      </c>
+      <c r="D478" s="1" t="s">
+        <v>1210</v>
+      </c>
+      <c r="E478" s="1" t="s">
+        <v>1218</v>
+      </c>
+      <c r="F478" s="6" t="s">
+        <v>1217</v>
+      </c>
     </row>
     <row r="479" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B479" s="1" t="s">
-        <v>1228</v>
-      </c>
-      <c r="D479" s="1" t="s">
-        <v>1219</v>
-      </c>
-      <c r="E479" s="1" t="s">
-        <v>1229</v>
-      </c>
-      <c r="F479" s="6" t="s">
-        <v>1230</v>
-      </c>
+      <c r="A479" s="7" t="s">
+        <v>1234</v>
+      </c>
+      <c r="F479" s="6"/>
     </row>
     <row r="480" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B480" s="1" t="s">
-        <v>1223</v>
+        <v>1235</v>
       </c>
       <c r="D480" s="1" t="s">
-        <v>1219</v>
+        <v>1236</v>
       </c>
       <c r="E480" s="1" t="s">
-        <v>1222</v>
+        <v>1237</v>
       </c>
       <c r="F480" s="6" t="s">
-        <v>1225</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="481" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B481" s="1" t="s">
-        <v>1224</v>
-      </c>
-      <c r="D481" s="1" t="s">
-        <v>1219</v>
-      </c>
-      <c r="E481" s="1" t="s">
-        <v>1227</v>
-      </c>
-      <c r="F481" s="6" t="s">
-        <v>1226</v>
-      </c>
+      <c r="A481" s="7" t="s">
+        <v>1248</v>
+      </c>
+      <c r="F481" s="6"/>
     </row>
     <row r="482" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A482" s="7" t="s">
-        <v>1243</v>
-      </c>
-      <c r="F482" s="6"/>
+      <c r="B482" s="1" t="s">
+        <v>1245</v>
+      </c>
+      <c r="D482" s="1" t="s">
+        <v>1247</v>
+      </c>
+      <c r="E482" s="1" t="s">
+        <v>1213</v>
+      </c>
+      <c r="F482" s="6" t="s">
+        <v>1246</v>
+      </c>
     </row>
     <row r="483" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B483" s="1" t="s">
-        <v>1244</v>
-      </c>
-      <c r="D483" s="1" t="s">
-        <v>1245</v>
-      </c>
-      <c r="E483" s="1" t="s">
-        <v>1246</v>
-      </c>
-      <c r="F483" s="6" t="s">
-        <v>1247</v>
-      </c>
+      <c r="A483" s="7" t="s">
+        <v>1278</v>
+      </c>
+      <c r="F483" s="6"/>
     </row>
     <row r="484" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A484" s="7" t="s">
-        <v>1257</v>
-      </c>
-      <c r="F484" s="6"/>
+      <c r="B484" s="1" t="s">
+        <v>1279</v>
+      </c>
+      <c r="D484" s="1" t="s">
+        <v>1280</v>
+      </c>
+      <c r="E484" s="1" t="s">
+        <v>1282</v>
+      </c>
+      <c r="F484" s="6" t="s">
+        <v>1281</v>
+      </c>
     </row>
     <row r="485" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B485" s="1" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D485" s="1" t="s">
-        <v>1256</v>
-      </c>
-      <c r="E485" s="1" t="s">
-        <v>1222</v>
-      </c>
-      <c r="F485" s="6" t="s">
-        <v>1255</v>
-      </c>
+      <c r="A485" s="7" t="s">
+        <v>1302</v>
+      </c>
+      <c r="F485" s="6"/>
     </row>
     <row r="486" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A486" s="7" t="s">
-        <v>1287</v>
-      </c>
-      <c r="F486" s="6"/>
+      <c r="B486" s="1" t="s">
+        <v>1300</v>
+      </c>
+      <c r="D486" s="1" t="s">
+        <v>1303</v>
+      </c>
+      <c r="E486" s="1" t="s">
+        <v>1301</v>
+      </c>
+      <c r="F486" s="6" t="s">
+        <v>1304</v>
+      </c>
     </row>
     <row r="487" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B487" s="1" t="s">
-        <v>1288</v>
-      </c>
-      <c r="D487" s="1" t="s">
-        <v>1289</v>
-      </c>
-      <c r="E487" s="1" t="s">
-        <v>1291</v>
-      </c>
-      <c r="F487" s="6" t="s">
-        <v>1290</v>
-      </c>
+      <c r="A487" s="7" t="s">
+        <v>1315</v>
+      </c>
+      <c r="F487" s="6"/>
     </row>
     <row r="488" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A488" s="7" t="s">
+      <c r="B488" s="1" t="s">
+        <v>1319</v>
+      </c>
+      <c r="D488" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="E488" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="F488" s="6" t="s">
+        <v>1318</v>
+      </c>
+    </row>
+    <row r="489" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A489" s="1" t="s">
         <v>1311</v>
       </c>
-      <c r="F488" s="6"/>
-    </row>
-    <row r="489" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B489" s="1" t="s">
-        <v>1309</v>
+        <v>1320</v>
       </c>
       <c r="D489" s="1" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="E489" s="1" t="s">
-        <v>1310</v>
+        <v>1316</v>
       </c>
       <c r="F489" s="6" t="s">
-        <v>1313</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="490" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A490" s="7" t="s">
-        <v>1324</v>
+        <v>1314</v>
       </c>
       <c r="F490" s="6"/>
     </row>
     <row r="491" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B491" s="1" t="s">
-        <v>1328</v>
+        <v>1321</v>
       </c>
       <c r="D491" s="1" t="s">
-        <v>1322</v>
+        <v>1312</v>
       </c>
       <c r="E491" s="1" t="s">
         <v>299</v>
       </c>
       <c r="F491" s="6" t="s">
-        <v>1327</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="492" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A492" s="1" t="s">
-        <v>1320</v>
-      </c>
       <c r="B492" s="1" t="s">
-        <v>1329</v>
+        <v>1324</v>
       </c>
       <c r="D492" s="1" t="s">
-        <v>1322</v>
+        <v>1312</v>
       </c>
       <c r="E492" s="1" t="s">
         <v>1325</v>
       </c>
       <c r="F492" s="6" t="s">
-        <v>1326</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="493" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A493" s="7" t="s">
-        <v>1323</v>
+        <v>1335</v>
       </c>
       <c r="F493" s="6"/>
     </row>
     <row r="494" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B494" s="1" t="s">
-        <v>1330</v>
+        <v>1336</v>
       </c>
       <c r="D494" s="1" t="s">
-        <v>1321</v>
+        <v>1337</v>
       </c>
       <c r="E494" s="1" t="s">
-        <v>299</v>
+        <v>32</v>
       </c>
       <c r="F494" s="6" t="s">
-        <v>1331</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="495" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B495" s="1" t="s">
-        <v>1333</v>
-      </c>
-      <c r="D495" s="1" t="s">
-        <v>1321</v>
-      </c>
-      <c r="E495" s="1" t="s">
-        <v>1334</v>
-      </c>
-      <c r="F495" s="6" t="s">
-        <v>1332</v>
-      </c>
+      <c r="A495" s="7" t="s">
+        <v>1349</v>
+      </c>
+      <c r="F495" s="6"/>
     </row>
     <row r="496" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A496" s="7" t="s">
-        <v>1344</v>
-      </c>
-      <c r="F496" s="6"/>
+      <c r="B496" s="1" t="s">
+        <v>1350</v>
+      </c>
+      <c r="D496" s="1" t="s">
+        <v>1351</v>
+      </c>
+      <c r="E496" s="1" t="s">
+        <v>1352</v>
+      </c>
+      <c r="F496" s="6" t="s">
+        <v>1354</v>
+      </c>
     </row>
     <row r="497" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B497" s="1" t="s">
-        <v>1345</v>
+        <v>1353</v>
       </c>
       <c r="D497" s="1" t="s">
-        <v>1346</v>
+        <v>1351</v>
       </c>
       <c r="E497" s="1" t="s">
-        <v>32</v>
+        <v>1355</v>
       </c>
       <c r="F497" s="6" t="s">
-        <v>1347</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="498" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A498" s="7" t="s">
-        <v>1358</v>
-      </c>
-      <c r="F498" s="6"/>
+      <c r="B498" s="1" t="s">
+        <v>1356</v>
+      </c>
+      <c r="D498" s="1" t="s">
+        <v>1351</v>
+      </c>
+      <c r="E498" s="1" t="s">
+        <v>1357</v>
+      </c>
+      <c r="F498" s="6" t="s">
+        <v>1359</v>
+      </c>
     </row>
     <row r="499" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B499" s="1" t="s">
-        <v>1359</v>
-      </c>
-      <c r="D499" s="1" t="s">
-        <v>1360</v>
-      </c>
-      <c r="E499" s="1" t="s">
-        <v>1361</v>
-      </c>
-      <c r="F499" s="6" t="s">
-        <v>1363</v>
-      </c>
+      <c r="A499" s="7" t="s">
+        <v>1377</v>
+      </c>
+      <c r="F499" s="6"/>
     </row>
     <row r="500" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B500" s="1" t="s">
-        <v>1362</v>
+        <v>1373</v>
       </c>
       <c r="D500" s="1" t="s">
-        <v>1360</v>
+        <v>1375</v>
       </c>
       <c r="E500" s="1" t="s">
-        <v>1364</v>
+        <v>1374</v>
       </c>
       <c r="F500" s="6" t="s">
-        <v>1367</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="501" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B501" s="1" t="s">
-        <v>1365</v>
-      </c>
-      <c r="D501" s="1" t="s">
-        <v>1360</v>
-      </c>
-      <c r="E501" s="1" t="s">
-        <v>1366</v>
-      </c>
-      <c r="F501" s="6" t="s">
-        <v>1368</v>
-      </c>
+      <c r="A501" s="7" t="s">
+        <v>1378</v>
+      </c>
+      <c r="F501" s="6"/>
     </row>
     <row r="502" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A502" s="7" t="s">
-        <v>1386</v>
-      </c>
-      <c r="F502" s="6"/>
+      <c r="B502" s="1" t="s">
+        <v>1379</v>
+      </c>
+      <c r="D502" s="1" t="s">
+        <v>1380</v>
+      </c>
+      <c r="E502" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F502" s="6" t="s">
+        <v>1381</v>
+      </c>
     </row>
     <row r="503" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B503" s="1" t="s">
-        <v>1382</v>
-      </c>
-      <c r="D503" s="1" t="s">
-        <v>1384</v>
-      </c>
-      <c r="E503" s="1" t="s">
-        <v>1383</v>
-      </c>
-      <c r="F503" s="6" t="s">
-        <v>1385</v>
+      <c r="A503" s="3" t="s">
+        <v>511</v>
       </c>
     </row>
     <row r="504" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A504" s="7" t="s">
-        <v>1387</v>
-      </c>
-      <c r="F504" s="6"/>
-    </row>
-    <row r="505" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B505" s="1" t="s">
-        <v>1388</v>
-      </c>
-      <c r="D505" s="1" t="s">
-        <v>1389</v>
-      </c>
-      <c r="E505" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F505" s="6" t="s">
-        <v>1390</v>
-      </c>
-    </row>
-    <row r="506" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A506" s="3" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="507" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B507" s="1" t="s">
+      <c r="B504" s="1" t="s">
         <v>512</v>
       </c>
-      <c r="D507" s="5" t="s">
+      <c r="D504" s="5" t="s">
         <v>513</v>
       </c>
-      <c r="E507" s="1" t="s">
+      <c r="E504" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F507" s="1" t="s">
+      <c r="F504" s="1" t="s">
         <v>514</v>
       </c>
     </row>
-    <row r="510" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="513" spans="6:6" x14ac:dyDescent="0.2">
-      <c r="F513" s="6"/>
+    <row r="507" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="510" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F510" s="6"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/Luban/Config/Datas/#BattleMomentEffectConfig.xlsx
+++ b/Luban/Config/Datas/#BattleMomentEffectConfig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F1A2F74-568B-4A2E-8CDF-D5F0ADDA69F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC5CB4A1-7640-48DD-B7DF-6D72FC4C9E16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
